--- a/Assets/Resource/MagicFight2/Magic.xlsx
+++ b/Assets/Resource/MagicFight2/Magic.xlsx
@@ -49,8 +49,12 @@
     <t>e</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
     <t xml:space="preserve">护盾
-加速</t>
+连击
+此法术的冷却时间减一</t>
   </si>
   <si>
     <t>f</t>
@@ -77,9 +81,6 @@
   </si>
   <si>
     <t>i</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
   <si>
     <t xml:space="preserve">大护盾
@@ -129,7 +130,8 @@
   </si>
   <si>
     <t xml:space="preserve">加速
-使你所有剩余冷却时间为一的法术立刻冷却完毕</t>
+使你所有剩余冷却时间为一的法术立刻冷却完毕
+连击</t>
   </si>
   <si>
     <t>p</t>
@@ -208,8 +210,8 @@
     <t>y</t>
   </si>
   <si>
-    <t xml:space="preserve">连击
-反制：免疫对方当前打出的法术的伤害</t>
+    <t xml:space="preserve">攻击
+移除对方一点护盾或者大护盾（优先护盾）</t>
   </si>
   <si>
     <t>z</t>
@@ -251,7 +253,7 @@
   </si>
   <si>
     <t xml:space="preserve">减速
-光环：当你的攻击对对方造成伤害时获得护盾（不包含重击和击穿）</t>
+光环：当你对对方造成伤害时，获得护盾（一个法术最多获得一点）</t>
   </si>
   <si>
     <t>af</t>
@@ -272,8 +274,8 @@
     <t>ah</t>
   </si>
   <si>
-    <t xml:space="preserve">护盾
-光环：每次受伤最多只损失一点生命值</t>
+    <t xml:space="preserve">连击
+光环：护盾词条可以改为恢复一点生命值（不包括大护盾）</t>
   </si>
   <si>
     <t>ai</t>
@@ -300,7 +302,7 @@
     <t>al</t>
   </si>
   <si>
-    <t xml:space="preserve">攻击
+    <t xml:space="preserve">护盾
 光环：法力+6</t>
   </si>
   <si>
@@ -406,51 +408,51 @@
         <v>10</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" s="0" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="0" t="s">
         <v>8</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C9" s="0" t="s">
         <v>21</v>
@@ -461,7 +463,7 @@
         <v>22</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" s="0" t="s">
         <v>23</v>
@@ -472,7 +474,7 @@
         <v>24</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" s="0" t="s">
         <v>25</v>
@@ -483,7 +485,7 @@
         <v>26</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C12" s="0" t="s">
         <v>27</v>
@@ -494,7 +496,7 @@
         <v>28</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C13" s="0" t="s">
         <v>29</v>
@@ -505,7 +507,7 @@
         <v>30</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C14" s="0" t="s">
         <v>31</v>
@@ -516,7 +518,7 @@
         <v>32</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C15" s="0" t="s">
         <v>33</v>
@@ -527,7 +529,7 @@
         <v>34</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C16" s="0" t="s">
         <v>35</v>
@@ -538,7 +540,7 @@
         <v>36</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C17" s="0" t="s">
         <v>37</v>
@@ -549,7 +551,7 @@
         <v>38</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C18" s="0" t="s">
         <v>39</v>
@@ -560,7 +562,7 @@
         <v>40</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C19" s="0" t="s">
         <v>41</v>
@@ -571,7 +573,7 @@
         <v>42</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C20" s="0" t="s">
         <v>43</v>
@@ -582,7 +584,7 @@
         <v>44</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C21" s="0" t="s">
         <v>45</v>
@@ -593,7 +595,7 @@
         <v>46</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C22" s="0" t="s">
         <v>47</v>
@@ -604,7 +606,7 @@
         <v>48</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C23" s="0" t="s">
         <v>49</v>
@@ -615,7 +617,7 @@
         <v>50</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C24" s="0" t="s">
         <v>51</v>
@@ -626,7 +628,7 @@
         <v>52</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C25" s="0" t="s">
         <v>53</v>
@@ -637,7 +639,7 @@
         <v>54</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C26" s="0" t="s">
         <v>55</v>
@@ -648,7 +650,7 @@
         <v>56</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C27" s="0" t="s">
         <v>57</v>
@@ -659,7 +661,7 @@
         <v>58</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C28" s="0" t="s">
         <v>59</v>
@@ -681,7 +683,7 @@
         <v>62</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C30" s="0" t="s">
         <v>63</v>
@@ -692,7 +694,7 @@
         <v>64</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C31" s="0" t="s">
         <v>65</v>
@@ -703,7 +705,7 @@
         <v>66</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C32" s="0" t="s">
         <v>67</v>
@@ -714,7 +716,7 @@
         <v>68</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C33" s="0" t="s">
         <v>69</v>
@@ -725,7 +727,7 @@
         <v>70</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C34" s="0" t="s">
         <v>71</v>
@@ -736,7 +738,7 @@
         <v>72</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C35" s="0" t="s">
         <v>73</v>
@@ -747,7 +749,7 @@
         <v>74</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C36" s="0" t="s">
         <v>75</v>
@@ -758,7 +760,7 @@
         <v>76</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C37" s="0" t="s">
         <v>77</v>
@@ -769,7 +771,7 @@
         <v>78</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C38" s="0" t="s">
         <v>79</v>
@@ -780,7 +782,7 @@
         <v>80</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C39" s="0" t="s">
         <v>81</v>
@@ -791,7 +793,7 @@
         <v>82</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C40" s="0" t="s">
         <v>83</v>

--- a/Assets/Resource/MagicFight2/Magic.xlsx
+++ b/Assets/Resource/MagicFight2/Magic.xlsx
@@ -12,305 +12,405 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="133">
   <si>
     <t>a</t>
   </si>
   <si>
+    <t>暴风雪</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;减速</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;全体减速</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>冰风暴</t>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
-    <t>攻击</t>
-  </si>
-  <si>
-    <t>b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">加速
-连击</t>
+    <t>&lt;sprite=0&gt;加速</t>
   </si>
   <si>
     <t>c</t>
   </si>
   <si>
-    <t>护盾</t>
+    <t>寒流</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;重置对方一个法术的冷却时间</t>
   </si>
   <si>
     <t>d</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">攻击
-连击</t>
+    <t>陨石</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;加速×2</t>
+  </si>
+  <si>
+    <t>&lt;sprite=1&gt;防御时，力量+3</t>
   </si>
   <si>
     <t>e</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">护盾
-连击
-此法术的冷却时间减一</t>
+    <t>水刃</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;使一张法术立即冷却完成</t>
   </si>
   <si>
     <t>f</t>
   </si>
   <si>
-    <t>重击</t>
+    <t>地震</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;快速回填</t>
+  </si>
+  <si>
+    <t>&lt;sprite=1&gt;守护</t>
   </si>
   <si>
     <t>g</t>
   </si>
   <si>
-    <t xml:space="preserve">攻击
-减速</t>
+    <t>毒刺</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;双发</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;使你的剩余冷却时间为1的法术立即冷却完毕</t>
   </si>
   <si>
     <t>h</t>
   </si>
   <si>
+    <t>飞叶连击</t>
+  </si>
+  <si>
+    <t>i</t>
+  </si>
+  <si>
+    <t>藤蔓</t>
+  </si>
+  <si>
+    <t>j</t>
+  </si>
+  <si>
+    <t>狂躁蘑菇</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;若这是你手中的最后一张法术，则双发</t>
+  </si>
+  <si>
+    <t>k</t>
+  </si>
+  <si>
+    <t>荆棘</t>
+  </si>
+  <si>
     <t>5</t>
   </si>
   <si>
-    <t xml:space="preserve">重击
-连击</t>
-  </si>
-  <si>
-    <t>i</t>
-  </si>
-  <si>
-    <t xml:space="preserve">大护盾
-连击</t>
-  </si>
-  <si>
-    <t>j</t>
-  </si>
-  <si>
-    <t xml:space="preserve">重击
-护盾</t>
-  </si>
-  <si>
-    <t>k</t>
-  </si>
-  <si>
-    <t xml:space="preserve">移除对方一点护盾或者大护盾（优先护盾）
-攻击
-连击</t>
+    <t>&lt;sprite=0&gt;当你上回合防御中损失了生命值时，双发</t>
+  </si>
+  <si>
+    <t>&lt;sprite=1&gt;防御时，攻击法术的力量每比你低2点，冷却时间减一</t>
   </si>
   <si>
     <t>l</t>
   </si>
   <si>
-    <t xml:space="preserve">攻击
-连击
-加速</t>
+    <t>喷泉</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;全体加速</t>
   </si>
   <si>
     <t>m</t>
   </si>
   <si>
-    <t xml:space="preserve">攻击
-减速
-加速</t>
+    <t>木盾</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;光环：免疫力量小于等于4的攻击（包括双发）</t>
   </si>
   <si>
     <t>n</t>
   </si>
   <si>
-    <t xml:space="preserve">攻击
-护盾
-免费</t>
+    <t>雷云</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;随机查看对方一张手牌，力量小于等于4则立即进入冷却</t>
   </si>
   <si>
     <t>o</t>
   </si>
   <si>
-    <t xml:space="preserve">加速
-使你所有剩余冷却时间为一的法术立刻冷却完毕
-连击</t>
+    <t>自燃</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;恢复一点生命值，减少一点生命上限</t>
   </si>
   <si>
     <t>p</t>
   </si>
   <si>
-    <t xml:space="preserve">使你或对方的一个正在冷却的法术立即冷却完毕
-连击</t>
+    <t>灵魂燃烧</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;恢复两点生命值，减少一点生命上限</t>
   </si>
   <si>
     <t>q</t>
   </si>
   <si>
-    <t xml:space="preserve">大护盾
-加速
-连击</t>
+    <t>沉重打击</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;对方无法防御时，将额外减少一点生命</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;光环对此法术提供的攻击力加成减半（向下取整）</t>
   </si>
   <si>
     <t>r</t>
   </si>
   <si>
-    <t xml:space="preserve">大护盾
-大护盾</t>
+    <t>模仿</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;复制对方冷却区当中的一个 无光环并且力量大于等于5的法术 的效果</t>
   </si>
   <si>
     <t>s</t>
   </si>
   <si>
-    <t xml:space="preserve">击穿
-连击</t>
+    <t>闪电</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;连击</t>
+  </si>
+  <si>
+    <t>&lt;sprite=1&gt;防御时，若攻击法术的力量小于等于2，则消除此法术除基础伤害外的所有效果（包括光环附加）</t>
   </si>
   <si>
     <t>t</t>
   </si>
   <si>
-    <t xml:space="preserve">使自己或对方的一个冷却中的法术获得三层减速
-连击</t>
+    <t>电场</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;随机查看对方一张手牌，力量大于等于7则立即进入冷却</t>
   </si>
   <si>
     <t>u</t>
   </si>
   <si>
-    <t xml:space="preserve">攻击
-攻击
-免费</t>
+    <t>雷鸣</t>
+  </si>
+  <si>
+    <t>v</t>
+  </si>
+  <si>
+    <t>磁暴</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;攻击时可以将手中其它法术进入冷却，每冷却一张进攻力量+2</t>
+  </si>
+  <si>
+    <t>w</t>
+  </si>
+  <si>
+    <t>引雷</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;光环：使你的力量小于等于4的法术获得连击（不能叠加）</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>石化</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;光环：免疫力量大于等于7的攻击</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>水镜反射</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;进攻力量+4</t>
+  </si>
+  <si>
+    <t>&lt;sprite=1&gt;防御时会将对方的伤害反弹，对方需要防御（反弹的伤害不附带任何效果）</t>
+  </si>
+  <si>
+    <t>z</t>
+  </si>
+  <si>
+    <t>滚石冲击</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>aa</t>
+  </si>
+  <si>
+    <t>雪球</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;你的冷却区每有一张牌，进攻力量+1</t>
+  </si>
+  <si>
+    <t>ab</t>
+  </si>
+  <si>
+    <t>瀑流</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;使自己冷却区力量小于等于4的所有法术获得加速×2</t>
+  </si>
+  <si>
+    <t>ac</t>
+  </si>
+  <si>
+    <t>大火球</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;对方使用的光环无效，并且清空对方的所有光环</t>
+  </si>
+  <si>
+    <t>&lt;sprite=1&gt;防御时，冷却时间减一</t>
+  </si>
+  <si>
+    <t>ad</t>
+  </si>
+  <si>
+    <t>烈焰斗蓬</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;光环：使法术附带防御时力量+3</t>
+  </si>
+  <si>
+    <t>ae</t>
+  </si>
+  <si>
+    <t>爆燃</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;光环：使法术附带进攻力量+4</t>
+  </si>
+  <si>
+    <t>af</t>
+  </si>
+  <si>
+    <t>淬火</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;光环：使法术附带进攻力量+2</t>
+  </si>
+  <si>
+    <t>ag</t>
+  </si>
+  <si>
+    <t>火雨</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;光环：使法术附带进攻力量+3</t>
+  </si>
+  <si>
+    <t>ah</t>
+  </si>
+  <si>
+    <t>熔岩之甲</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;光环：使法术附带进攻力量+2或防御力量+2</t>
+  </si>
+  <si>
+    <t>ai</t>
+  </si>
+  <si>
+    <t>潮汐</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;光环：使你的一张法术立即冷却完成</t>
+  </si>
+  <si>
+    <t>aj</t>
+  </si>
+  <si>
+    <t>地波</t>
+  </si>
+  <si>
+    <t>&lt;sprite=1&gt;连续抵挡</t>
+  </si>
+  <si>
+    <t>ak</t>
+  </si>
+  <si>
+    <t>沙流</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;当对方的生命值大于你时，进攻力量+2</t>
+  </si>
+  <si>
+    <t>al</t>
+  </si>
+  <si>
+    <t>凝固</t>
+  </si>
+  <si>
+    <t>&lt;sprite=1&gt;防御时，对方法术的力量值锁定为基础值（效果和光环的加成无效）</t>
+  </si>
+  <si>
+    <t>am</t>
+  </si>
+  <si>
+    <t>湍流</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;你的冷却区当中每有两个法术，获得一层快速回填</t>
+  </si>
+  <si>
+    <t>&lt;sprite=1&gt;防御时力量+4</t>
   </si>
   <si>
     <t>an</t>
-  </si>
-  <si>
-    <t xml:space="preserve">攻击
-减速
-连击</t>
-  </si>
-  <si>
-    <t>v</t>
-  </si>
-  <si>
-    <t xml:space="preserve">护盾
-反制：对方当前的打出的卡牌的光环不生效（背面朝上放到冷却区），但冷却时间减一</t>
-  </si>
-  <si>
-    <t>w</t>
-  </si>
-  <si>
-    <t xml:space="preserve">连击
-反制：对方当前的打出的卡牌的光环不生效（背面朝上放到冷却区），但冷却时间减一</t>
-  </si>
-  <si>
-    <t>x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">护盾
-反制：免疫对方当前打出的法术的伤害</t>
-  </si>
-  <si>
-    <t>y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">攻击
-移除对方一点护盾或者大护盾（优先护盾）</t>
-  </si>
-  <si>
-    <t>z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">连击
-反制：对方无法继续出牌</t>
-  </si>
-  <si>
-    <t>aa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">大护盾
-反制：对方无法继续出牌</t>
-  </si>
-  <si>
-    <t>ab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">免费
-光环：对方存在护盾或大护盾时，攻击会再执行一次（不包括重击和击穿）</t>
-  </si>
-  <si>
-    <t>ac</t>
-  </si>
-  <si>
-    <t xml:space="preserve">护盾
-光环：含有攻击/重击/击穿的法术的冷却时间减一（不改变费用）</t>
-  </si>
-  <si>
-    <t>ad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">免费
-光环：当可用法术数量&lt;=4时，攻击升级为重击</t>
-  </si>
-  <si>
-    <t>ae</t>
-  </si>
-  <si>
-    <t xml:space="preserve">减速
-光环：当你对对方造成伤害时，获得护盾（一个法术最多获得一点）</t>
-  </si>
-  <si>
-    <t>af</t>
-  </si>
-  <si>
-    <t xml:space="preserve">护盾
-光环：护盾可以额外抵挡一点伤害</t>
-  </si>
-  <si>
-    <t>ag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">护盾
-免费
-光环：可以消耗一点护盾/大护盾/生命值使攻击升级为重击</t>
-  </si>
-  <si>
-    <t>ah</t>
-  </si>
-  <si>
-    <t xml:space="preserve">连击
-光环：护盾词条可以改为恢复一点生命值（不包括大护盾）</t>
-  </si>
-  <si>
-    <t>ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">重击
-光环：法力+4</t>
-  </si>
-  <si>
-    <t>aj</t>
-  </si>
-  <si>
-    <t xml:space="preserve">击穿
-光环：法力+4</t>
-  </si>
-  <si>
-    <t>ak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">大护盾
-光环：法力+6</t>
-  </si>
-  <si>
-    <t>al</t>
-  </si>
-  <si>
-    <t xml:space="preserve">护盾
-光环：法力+6</t>
-  </si>
-  <si>
-    <t>am</t>
-  </si>
-  <si>
-    <t xml:space="preserve">攻击
-光环：含有护盾/大护盾的法术冷却时间减一（不改变费用）</t>
   </si>
 </sst>
 </file>
@@ -356,7 +456,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -369,434 +469,743 @@
       <c r="C1" s="0" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>4</v>
+        <v>8</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="0" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>6</v>
+        <v>3</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>9</v>
+        <v>16</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="0" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>12</v>
+        <v>21</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>14</v>
+        <v>25</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="0" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="B7" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="0" t="s">
-        <v>16</v>
+      <c r="D7" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="0" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>19</v>
+        <v>2</v>
+      </c>
+      <c r="D8" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="0" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>21</v>
+        <v>12</v>
+      </c>
+      <c r="D9" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="0" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>23</v>
+        <v>21</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" s="0" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>25</v>
+        <v>41</v>
+      </c>
+      <c r="D11" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="0" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>27</v>
+        <v>21</v>
+      </c>
+      <c r="D12" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="0" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>29</v>
+        <v>25</v>
+      </c>
+      <c r="D13" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E13" s="0" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>31</v>
+        <v>16</v>
+      </c>
+      <c r="D14" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="0" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>33</v>
+        <v>12</v>
+      </c>
+      <c r="D15" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="F15" s="0" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>35</v>
+        <v>3</v>
+      </c>
+      <c r="D16" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E16" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="F16" s="0" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>37</v>
+        <v>25</v>
+      </c>
+      <c r="D17" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="F17" s="0" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>39</v>
+        <v>3</v>
+      </c>
+      <c r="D18" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="0" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>41</v>
+        <v>25</v>
+      </c>
+      <c r="D19" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E19" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="F19" s="0" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>43</v>
+        <v>3</v>
+      </c>
+      <c r="D20" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="F20" s="0" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>45</v>
+        <v>12</v>
+      </c>
+      <c r="D21" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E21" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="F21" s="0" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>11</v>
+        <v>76</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>47</v>
+        <v>21</v>
+      </c>
+      <c r="D22" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="F22" s="0" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>18</v>
+        <v>79</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>49</v>
+        <v>16</v>
+      </c>
+      <c r="D23" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" s="0" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>18</v>
+        <v>82</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>51</v>
+        <v>2</v>
+      </c>
+      <c r="D24" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="F24" s="0" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>53</v>
+        <v>12</v>
+      </c>
+      <c r="D25" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E25" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="F25" s="0" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>8</v>
+        <v>89</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>55</v>
+        <v>90</v>
+      </c>
+      <c r="D26" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E26" s="0" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>56</v>
+        <v>91</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>11</v>
+        <v>92</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>57</v>
+        <v>3</v>
+      </c>
+      <c r="D27" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E27" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="F27" s="0" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>18</v>
+        <v>95</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>59</v>
+        <v>41</v>
+      </c>
+      <c r="D28" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E28" s="0" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>8</v>
+        <v>98</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>61</v>
+        <v>21</v>
+      </c>
+      <c r="D29" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E29" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="F29" s="0" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>18</v>
+        <v>102</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>63</v>
+        <v>41</v>
+      </c>
+      <c r="D30" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="E30" s="0" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>11</v>
+        <v>105</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>65</v>
+        <v>8</v>
+      </c>
+      <c r="D31" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E31" s="0" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>66</v>
+        <v>107</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>18</v>
+        <v>108</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>67</v>
+        <v>8</v>
+      </c>
+      <c r="D32" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="0" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
-        <v>68</v>
+        <v>110</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>11</v>
+        <v>111</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>69</v>
+        <v>12</v>
+      </c>
+      <c r="D33" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E33" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="F33" s="0" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>70</v>
+        <v>113</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>18</v>
+        <v>114</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>71</v>
+        <v>3</v>
+      </c>
+      <c r="D34" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="E34" s="0" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>18</v>
+        <v>117</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>73</v>
+        <v>41</v>
+      </c>
+      <c r="D35" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E35" s="0" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>74</v>
+        <v>119</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>11</v>
+        <v>120</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>75</v>
+        <v>41</v>
+      </c>
+      <c r="D36" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="E36" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="F36" s="0" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>76</v>
+        <v>122</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>18</v>
+        <v>123</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>77</v>
+        <v>16</v>
+      </c>
+      <c r="D37" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="E37" s="0" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>78</v>
+        <v>125</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>11</v>
+        <v>126</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>79</v>
+        <v>16</v>
+      </c>
+      <c r="D38" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="E38" s="0" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>80</v>
+        <v>128</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>18</v>
+        <v>129</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>81</v>
+        <v>41</v>
+      </c>
+      <c r="D39" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E39" s="0" t="s">
+        <v>130</v>
+      </c>
+      <c r="F39" s="0" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
-        <v>82</v>
+        <v>132</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>83</v>
+        <v>90</v>
+      </c>
+      <c r="D40" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E40" s="0" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resource/MagicFight2/Magic.xlsx
+++ b/Assets/Resource/MagicFight2/Magic.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="135">
   <si>
     <t>a</t>
   </si>
@@ -29,7 +29,7 @@
     <t>&lt;sprite=0&gt;减速</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;全体减速</t>
+    <t>&lt;sprite=0&gt;区域减速</t>
   </si>
   <si>
     <t>b</t>
@@ -50,6 +50,9 @@
     <t>寒流</t>
   </si>
   <si>
+    <t>5</t>
+  </si>
+  <si>
     <t>3</t>
   </si>
   <si>
@@ -59,358 +62,361 @@
     <t>d</t>
   </si>
   <si>
+    <t>流星</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;减速×2</t>
+  </si>
+  <si>
+    <t>&lt;sprite=1&gt;防御时，力量加4</t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>水刃</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;使一张法术立即冷却完成</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>地震</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>&lt;sprite=1&gt;守护</t>
+  </si>
+  <si>
+    <t>g</t>
+  </si>
+  <si>
+    <t>毒刺</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;双发</t>
+  </si>
+  <si>
+    <t>h</t>
+  </si>
+  <si>
+    <t>飞叶连击</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;快速回填</t>
+  </si>
+  <si>
+    <t>i</t>
+  </si>
+  <si>
+    <t>藤蔓</t>
+  </si>
+  <si>
+    <t>j</t>
+  </si>
+  <si>
+    <t>狂躁蘑菇</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;若手牌数小于等于2，双发</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;使你的 剩余冷却时间为一 的法术立即冷却完成</t>
+  </si>
+  <si>
+    <t>k</t>
+  </si>
+  <si>
+    <t>荆棘</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;对方生命值等于你时，双发</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;你在上回合防御中受伤时，双发（不可叠加）</t>
+  </si>
+  <si>
+    <t>l</t>
+  </si>
+  <si>
+    <t>喷泉</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;区域加速</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>石盾</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;光环：免疫力量小于等于3的攻击（包括双发）</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>雷云</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;随机查看对方一张手牌，力量小于等于4则立即进入冷却</t>
+  </si>
+  <si>
+    <t>o</t>
+  </si>
+  <si>
+    <t>自燃</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;恢复一点生命值，减少一点生命上限</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>灵魂燃烧</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;恢复两点生命值，减少一点生命上限</t>
+  </si>
+  <si>
+    <t>q</t>
+  </si>
+  <si>
+    <t>沉重打击</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;对方无法防御时，将额外减少一点生命</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;光环对此法术提供的攻击力加成减半（向下取整）</t>
+  </si>
+  <si>
+    <t>r</t>
+  </si>
+  <si>
+    <t>模仿</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;复制对方冷却区当中的一个 无光环并且力量大于等于5的法术 的效果</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>闪电</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;连击</t>
+  </si>
+  <si>
+    <t>&lt;sprite=1&gt;防御时，若攻击法术的力量小于等于2，则消除此法术除基础伤害外的所有效果（包括光环附加）</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>电场</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;随机查看对方一张手牌，力量大于等于7则立即进入冷却</t>
+  </si>
+  <si>
+    <t>u</t>
+  </si>
+  <si>
+    <t>雷鸣</t>
+  </si>
+  <si>
+    <t>v</t>
+  </si>
+  <si>
+    <t>磁暴</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;攻击时可以将手中其它法术进入冷却，每冷却一张进攻力量+2</t>
+  </si>
+  <si>
+    <t>w</t>
+  </si>
+  <si>
+    <t>引雷</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;光环：使你的力量小于等于4的法术获得连击（不能叠加）</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>石化</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;光环：免疫力量大于等于7的攻击（包括双发）</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>水镜反射</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;进攻力量+4</t>
+  </si>
+  <si>
+    <t>&lt;sprite=1&gt;防御时会将对方的攻击反弹，对方需要防御（反弹不会附带任何效果）</t>
+  </si>
+  <si>
+    <t>z</t>
+  </si>
+  <si>
+    <t>滚石冲击</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>aa</t>
+  </si>
+  <si>
+    <t>雪球</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;你的冷却区每有一张牌，进攻力量+1</t>
+  </si>
+  <si>
+    <t>ab</t>
+  </si>
+  <si>
+    <t>瀑流</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;使自己冷却区中所有力量小于等于4的法术获得加速</t>
+  </si>
+  <si>
+    <t>ac</t>
+  </si>
+  <si>
+    <t>大火球</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;对方使用的光环无效，并且清空对方的所有光环</t>
+  </si>
+  <si>
+    <t>&lt;sprite=1&gt;防御时，冷却时间减一</t>
+  </si>
+  <si>
+    <t>ad</t>
+  </si>
+  <si>
+    <t>烈焰斗蓬</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;光环：使法术附带防御时力量+3</t>
+  </si>
+  <si>
+    <t>&lt;sprite=1&gt;防御时，力量+4</t>
+  </si>
+  <si>
+    <t>ae</t>
+  </si>
+  <si>
+    <t>爆燃</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;光环：使法术附带进攻力量+4</t>
+  </si>
+  <si>
+    <t>af</t>
+  </si>
+  <si>
+    <t>淬火</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;光环：使法术附带进攻力量+2</t>
+  </si>
+  <si>
+    <t>ag</t>
+  </si>
+  <si>
+    <t>火雨</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;光环：使法术附带进攻力量+3</t>
+  </si>
+  <si>
+    <t>ah</t>
+  </si>
+  <si>
+    <t>熔岩之甲</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;光环：使法术附带进攻力量+2或防御力量+2</t>
+  </si>
+  <si>
+    <t>ai</t>
+  </si>
+  <si>
+    <t>潮汐</t>
+  </si>
+  <si>
+    <t>光环：使一张法术的冷却立即结束</t>
+  </si>
+  <si>
+    <t>aj</t>
+  </si>
+  <si>
+    <t>地波</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;进攻力量+2</t>
+  </si>
+  <si>
+    <t>ak</t>
+  </si>
+  <si>
+    <t>沙流</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;当对方的生命值大于你时，进攻力量+2</t>
+  </si>
+  <si>
+    <t>al</t>
+  </si>
+  <si>
+    <t>凝固</t>
+  </si>
+  <si>
+    <t>&lt;sprite=1&gt;防御时，对方法术的力量值锁定为基础值（效果和光环的加成无效）</t>
+  </si>
+  <si>
+    <t>am</t>
+  </si>
+  <si>
+    <t>湍流</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;你的冷却区当中每有三个法术，获得一层快速回填</t>
+  </si>
+  <si>
+    <t>&lt;sprite=1&gt;连续抵挡</t>
+  </si>
+  <si>
+    <t>an</t>
+  </si>
+  <si>
     <t>陨石</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;加速×2</t>
-  </si>
-  <si>
-    <t>&lt;sprite=1&gt;防御时，力量+3</t>
-  </si>
-  <si>
-    <t>e</t>
-  </si>
-  <si>
-    <t>水刃</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;使一张法术立即冷却完成</t>
-  </si>
-  <si>
-    <t>f</t>
-  </si>
-  <si>
-    <t>地震</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;快速回填</t>
-  </si>
-  <si>
-    <t>&lt;sprite=1&gt;守护</t>
-  </si>
-  <si>
-    <t>g</t>
-  </si>
-  <si>
-    <t>毒刺</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;双发</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;使你的剩余冷却时间为1的法术立即冷却完毕</t>
-  </si>
-  <si>
-    <t>h</t>
-  </si>
-  <si>
-    <t>飞叶连击</t>
-  </si>
-  <si>
-    <t>i</t>
-  </si>
-  <si>
-    <t>藤蔓</t>
-  </si>
-  <si>
-    <t>j</t>
-  </si>
-  <si>
-    <t>狂躁蘑菇</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;若这是你手中的最后一张法术，则双发</t>
-  </si>
-  <si>
-    <t>k</t>
-  </si>
-  <si>
-    <t>荆棘</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;当你上回合防御中损失了生命值时，双发</t>
-  </si>
-  <si>
-    <t>&lt;sprite=1&gt;防御时，攻击法术的力量每比你低2点，冷却时间减一</t>
-  </si>
-  <si>
-    <t>l</t>
-  </si>
-  <si>
-    <t>喷泉</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;全体加速</t>
-  </si>
-  <si>
-    <t>m</t>
-  </si>
-  <si>
-    <t>木盾</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;光环：免疫力量小于等于4的攻击（包括双发）</t>
-  </si>
-  <si>
-    <t>n</t>
-  </si>
-  <si>
-    <t>雷云</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;随机查看对方一张手牌，力量小于等于4则立即进入冷却</t>
-  </si>
-  <si>
-    <t>o</t>
-  </si>
-  <si>
-    <t>自燃</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;恢复一点生命值，减少一点生命上限</t>
-  </si>
-  <si>
-    <t>p</t>
-  </si>
-  <si>
-    <t>灵魂燃烧</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;恢复两点生命值，减少一点生命上限</t>
-  </si>
-  <si>
-    <t>q</t>
-  </si>
-  <si>
-    <t>沉重打击</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;对方无法防御时，将额外减少一点生命</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;光环对此法术提供的攻击力加成减半（向下取整）</t>
-  </si>
-  <si>
-    <t>r</t>
-  </si>
-  <si>
-    <t>模仿</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;复制对方冷却区当中的一个 无光环并且力量大于等于5的法术 的效果</t>
-  </si>
-  <si>
-    <t>s</t>
-  </si>
-  <si>
-    <t>闪电</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;连击</t>
-  </si>
-  <si>
-    <t>&lt;sprite=1&gt;防御时，若攻击法术的力量小于等于2，则消除此法术除基础伤害外的所有效果（包括光环附加）</t>
-  </si>
-  <si>
-    <t>t</t>
-  </si>
-  <si>
-    <t>电场</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;随机查看对方一张手牌，力量大于等于7则立即进入冷却</t>
-  </si>
-  <si>
-    <t>u</t>
-  </si>
-  <si>
-    <t>雷鸣</t>
-  </si>
-  <si>
-    <t>v</t>
-  </si>
-  <si>
-    <t>磁暴</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;攻击时可以将手中其它法术进入冷却，每冷却一张进攻力量+2</t>
-  </si>
-  <si>
-    <t>w</t>
-  </si>
-  <si>
-    <t>引雷</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;光环：使你的力量小于等于4的法术获得连击（不能叠加）</t>
-  </si>
-  <si>
-    <t>x</t>
-  </si>
-  <si>
-    <t>石化</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;光环：免疫力量大于等于7的攻击</t>
-  </si>
-  <si>
-    <t>y</t>
-  </si>
-  <si>
-    <t>水镜反射</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;进攻力量+4</t>
-  </si>
-  <si>
-    <t>&lt;sprite=1&gt;防御时会将对方的伤害反弹，对方需要防御（反弹的伤害不附带任何效果）</t>
-  </si>
-  <si>
-    <t>z</t>
-  </si>
-  <si>
-    <t>滚石冲击</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>aa</t>
-  </si>
-  <si>
-    <t>雪球</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;你的冷却区每有一张牌，进攻力量+1</t>
-  </si>
-  <si>
-    <t>ab</t>
-  </si>
-  <si>
-    <t>瀑流</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;使自己冷却区力量小于等于4的所有法术获得加速×2</t>
-  </si>
-  <si>
-    <t>ac</t>
-  </si>
-  <si>
-    <t>大火球</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;对方使用的光环无效，并且清空对方的所有光环</t>
-  </si>
-  <si>
-    <t>&lt;sprite=1&gt;防御时，冷却时间减一</t>
-  </si>
-  <si>
-    <t>ad</t>
-  </si>
-  <si>
-    <t>烈焰斗蓬</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;光环：使法术附带防御时力量+3</t>
-  </si>
-  <si>
-    <t>ae</t>
-  </si>
-  <si>
-    <t>爆燃</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;光环：使法术附带进攻力量+4</t>
-  </si>
-  <si>
-    <t>af</t>
-  </si>
-  <si>
-    <t>淬火</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;光环：使法术附带进攻力量+2</t>
-  </si>
-  <si>
-    <t>ag</t>
-  </si>
-  <si>
-    <t>火雨</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;光环：使法术附带进攻力量+3</t>
-  </si>
-  <si>
-    <t>ah</t>
-  </si>
-  <si>
-    <t>熔岩之甲</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;光环：使法术附带进攻力量+2或防御力量+2</t>
-  </si>
-  <si>
-    <t>ai</t>
-  </si>
-  <si>
-    <t>潮汐</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;光环：使你的一张法术立即冷却完成</t>
-  </si>
-  <si>
-    <t>aj</t>
-  </si>
-  <si>
-    <t>地波</t>
-  </si>
-  <si>
-    <t>&lt;sprite=1&gt;连续抵挡</t>
-  </si>
-  <si>
-    <t>ak</t>
-  </si>
-  <si>
-    <t>沙流</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;当对方的生命值大于你时，进攻力量+2</t>
-  </si>
-  <si>
-    <t>al</t>
-  </si>
-  <si>
-    <t>凝固</t>
-  </si>
-  <si>
-    <t>&lt;sprite=1&gt;防御时，对方法术的力量值锁定为基础值（效果和光环的加成无效）</t>
-  </si>
-  <si>
-    <t>am</t>
-  </si>
-  <si>
-    <t>湍流</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;你的冷却区当中每有两个法术，获得一层快速回填</t>
-  </si>
-  <si>
-    <t>&lt;sprite=1&gt;防御时力量+4</t>
-  </si>
-  <si>
-    <t>an</t>
   </si>
 </sst>
 </file>
@@ -493,10 +499,10 @@
         <v>3</v>
       </c>
       <c r="E2" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="0" t="s">
         <v>5</v>
-      </c>
-      <c r="F2" s="0" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -507,30 +513,27 @@
         <v>11</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="0" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E4" s="0" t="s">
         <v>17</v>
@@ -550,7 +553,7 @@
         <v>21</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E5" s="0" t="s">
         <v>22</v>
@@ -570,84 +573,84 @@
         <v>3</v>
       </c>
       <c r="E6" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="0" t="s">
         <v>26</v>
-      </c>
-      <c r="F6" s="0" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="C7" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="0" t="s">
         <v>29</v>
-      </c>
-      <c r="C7" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="E7" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" s="0" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" s="0" t="s">
         <v>32</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="0" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="0" t="s">
-        <v>35</v>
-      </c>
       <c r="C9" s="0" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D9" s="0" t="s">
         <v>3</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F9" s="0" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="C10" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="0" t="s">
         <v>37</v>
-      </c>
-      <c r="C10" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" s="0" t="s">
-        <v>26</v>
       </c>
       <c r="F10" s="0" t="s">
         <v>38</v>
@@ -664,7 +667,7 @@
         <v>41</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E11" s="0" t="s">
         <v>42</v>
@@ -681,12 +684,15 @@
         <v>45</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E12" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="0" t="s">
         <v>46</v>
       </c>
     </row>
@@ -715,10 +721,10 @@
         <v>51</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E14" s="0" t="s">
         <v>52</v>
@@ -732,10 +738,10 @@
         <v>54</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E15" s="0" t="s">
         <v>55</v>
@@ -755,13 +761,13 @@
         <v>3</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E16" s="0" t="s">
         <v>58</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17">
@@ -809,7 +815,7 @@
         <v>67</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D19" s="0" t="s">
         <v>3</v>
@@ -832,7 +838,7 @@
         <v>3</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E20" s="0" t="s">
         <v>72</v>
@@ -849,7 +855,7 @@
         <v>74</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D21" s="0" t="s">
         <v>3</v>
@@ -869,10 +875,10 @@
         <v>76</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E22" s="0" t="s">
         <v>77</v>
@@ -889,13 +895,16 @@
         <v>79</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E23" s="0" t="s">
         <v>80</v>
+      </c>
+      <c r="F23" s="0" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="24">
@@ -926,10 +935,10 @@
         <v>85</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E25" s="0" t="s">
         <v>86</v>
@@ -952,7 +961,7 @@
         <v>3</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27">
@@ -963,13 +972,13 @@
         <v>92</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F27" s="0" t="s">
         <v>93</v>
@@ -983,10 +992,10 @@
         <v>95</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E28" s="0" t="s">
         <v>96</v>
@@ -1000,7 +1009,7 @@
         <v>98</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D29" s="0" t="s">
         <v>3</v>
@@ -1023,18 +1032,21 @@
         <v>41</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E30" s="0" t="s">
         <v>103</v>
       </c>
+      <c r="F30" s="0" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C31" s="0" t="s">
         <v>8</v>
@@ -1043,160 +1055,157 @@
         <v>3</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>106</v>
+        <v>9</v>
+      </c>
+      <c r="F31" s="0" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E32" s="0" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E33" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" s="0" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C34" s="0" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E34" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="D35" s="0" t="s">
         <v>3</v>
       </c>
       <c r="E35" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E36" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="F36" s="0" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E37" s="0" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E38" s="0" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C39" s="0" t="s">
         <v>41</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E39" s="0" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>15</v>
+        <v>134</v>
       </c>
       <c r="C40" s="0" t="s">
         <v>90</v>
@@ -1205,7 +1214,7 @@
         <v>3</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resource/MagicFight2/Magic.xlsx
+++ b/Assets/Resource/MagicFight2/Magic.xlsx
@@ -26,64 +26,118 @@
     <t>4</t>
   </si>
   <si>
+    <t>&lt;sprite=0&gt;区域减速</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>冰风暴</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;减速×2</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;加速</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>寒流</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;重置对方一个法术的冷却时间</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>流星</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;进攻力量可以等同于 对方冷却区当中力量值最高 的法术</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;若攻击被防御，则快速回填</t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>水刃</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;使一张法术立即冷却完成</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>潮汐</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;光环：使一个法术立即冷却完毕</t>
+  </si>
+  <si>
+    <t>g</t>
+  </si>
+  <si>
+    <t>毒刺</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;双发</t>
+  </si>
+  <si>
     <t>&lt;sprite=0&gt;减速</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;区域减速</t>
-  </si>
-  <si>
-    <t>b</t>
-  </si>
-  <si>
-    <t>冰风暴</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;加速</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>寒流</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;重置对方一个法术的冷却时间</t>
-  </si>
-  <si>
-    <t>d</t>
-  </si>
-  <si>
-    <t>流星</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;减速×2</t>
-  </si>
-  <si>
-    <t>&lt;sprite=1&gt;防御时，力量加4</t>
-  </si>
-  <si>
-    <t>e</t>
-  </si>
-  <si>
-    <t>水刃</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;使一张法术立即冷却完成</t>
-  </si>
-  <si>
-    <t>f</t>
+    <t>h</t>
+  </si>
+  <si>
+    <t>飞叶连击</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;快速回填</t>
+  </si>
+  <si>
+    <t>i</t>
+  </si>
+  <si>
+    <t>藤蔓</t>
+  </si>
+  <si>
+    <t>&lt;sprite=1&gt;防御时，力量加5</t>
+  </si>
+  <si>
+    <t>j</t>
+  </si>
+  <si>
+    <t>狂躁蘑菇</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;若这是你手中的最后两张法术，双发</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;使你的 剩余冷却时间为一 的法术立即冷却完成</t>
+  </si>
+  <si>
+    <t>k</t>
   </si>
   <si>
     <t>地震</t>
@@ -95,57 +149,6 @@
     <t>&lt;sprite=1&gt;守护</t>
   </si>
   <si>
-    <t>g</t>
-  </si>
-  <si>
-    <t>毒刺</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;双发</t>
-  </si>
-  <si>
-    <t>h</t>
-  </si>
-  <si>
-    <t>飞叶连击</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;快速回填</t>
-  </si>
-  <si>
-    <t>i</t>
-  </si>
-  <si>
-    <t>藤蔓</t>
-  </si>
-  <si>
-    <t>j</t>
-  </si>
-  <si>
-    <t>狂躁蘑菇</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;若手牌数小于等于2，双发</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;使你的 剩余冷却时间为一 的法术立即冷却完成</t>
-  </si>
-  <si>
-    <t>k</t>
-  </si>
-  <si>
-    <t>荆棘</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;对方生命值等于你时，双发</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;你在上回合防御中受伤时，双发（不可叠加）</t>
-  </si>
-  <si>
     <t>l</t>
   </si>
   <si>
@@ -308,15 +311,12 @@
     <t>ac</t>
   </si>
   <si>
-    <t>大火球</t>
+    <t>感电</t>
   </si>
   <si>
     <t>&lt;sprite=0&gt;对方使用的光环无效，并且清空对方的所有光环</t>
   </si>
   <si>
-    <t>&lt;sprite=1&gt;防御时，冷却时间减一</t>
-  </si>
-  <si>
     <t>ad</t>
   </si>
   <si>
@@ -347,6 +347,9 @@
     <t>&lt;sprite=0&gt;光环：使法术附带进攻力量+2</t>
   </si>
   <si>
+    <t>&lt;sprite=1&gt;防御时，攻击法术的力量每比你小2点，冷却时间减1</t>
+  </si>
+  <si>
     <t>ag</t>
   </si>
   <si>
@@ -368,10 +371,10 @@
     <t>ai</t>
   </si>
   <si>
-    <t>潮汐</t>
-  </si>
-  <si>
-    <t>光环：使一张法术的冷却立即结束</t>
+    <t>火灾</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;光环：使法术附带进攻力量+1</t>
   </si>
   <si>
     <t>aj</t>
@@ -389,9 +392,6 @@
     <t>沙流</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;当对方的生命值大于你时，进攻力量+2</t>
-  </si>
-  <si>
     <t>al</t>
   </si>
   <si>
@@ -407,7 +407,7 @@
     <t>湍流</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;你的冷却区当中每有三个法术，获得一层快速回填</t>
+    <t>&lt;sprite=0&gt;加速×2</t>
   </si>
   <si>
     <t>&lt;sprite=1&gt;连续抵挡</t>
@@ -481,28 +481,25 @@
       <c r="E1" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
-        <v>5</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="C2" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="D2" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="0" t="s">
+      <c r="F2" s="0" t="s">
         <v>9</v>
-      </c>
-      <c r="F2" s="0" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -530,52 +527,49 @@
         <v>16</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D4" s="0" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5" s="0" t="s">
         <v>3</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="D6" s="0" t="s">
         <v>3</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="0" t="s">
         <v>26</v>
       </c>
     </row>
@@ -595,16 +589,19 @@
       <c r="E7" s="0" t="s">
         <v>29</v>
       </c>
+      <c r="F7" s="0" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D8" s="0" t="s">
         <v>13</v>
@@ -613,15 +610,15 @@
         <v>29</v>
       </c>
       <c r="F8" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C9" s="0" t="s">
         <v>3</v>
@@ -633,55 +630,55 @@
         <v>29</v>
       </c>
       <c r="F9" s="0" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D10" s="0" t="s">
         <v>13</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F10" s="0" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D11" s="0" t="s">
         <v>3</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C12" s="0" t="s">
         <v>13</v>
@@ -693,69 +690,69 @@
         <v>9</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="D13" s="0" t="s">
         <v>3</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D14" s="0" t="s">
         <v>13</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C16" s="0" t="s">
         <v>3</v>
@@ -764,38 +761,38 @@
         <v>13</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="D17" s="0" t="s">
         <v>3</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C18" s="0" t="s">
         <v>3</v>
@@ -804,75 +801,75 @@
         <v>3</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D19" s="0" t="s">
         <v>3</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F19" s="0" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D20" s="0" t="s">
         <v>13</v>
       </c>
       <c r="E20" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F20" s="0" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D21" s="0" t="s">
         <v>3</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F21" s="0" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C22" s="0" t="s">
         <v>12</v>
@@ -881,38 +878,38 @@
         <v>13</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F22" s="0" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="D23" s="0" t="s">
         <v>3</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F23" s="0" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C24" s="0" t="s">
         <v>2</v>
@@ -921,18 +918,18 @@
         <v>3</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C25" s="0" t="s">
         <v>13</v>
@@ -941,35 +938,35 @@
         <v>13</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D26" s="0" t="s">
         <v>3</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C27" s="0" t="s">
         <v>13</v>
@@ -978,46 +975,43 @@
         <v>13</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F27" s="0" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D28" s="0" t="s">
         <v>13</v>
       </c>
       <c r="E28" s="0" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>99</v>
-      </c>
-      <c r="F29" s="0" t="s">
         <v>100</v>
       </c>
     </row>
@@ -1029,7 +1023,7 @@
         <v>102</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="D30" s="0" t="s">
         <v>3</v>
@@ -1049,7 +1043,7 @@
         <v>106</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D31" s="0" t="s">
         <v>3</v>
@@ -1069,98 +1063,104 @@
         <v>109</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E32" s="0" t="s">
         <v>110</v>
       </c>
+      <c r="F32" s="0" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="D33" s="0" t="s">
         <v>13</v>
       </c>
       <c r="E33" s="0" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C34" s="0" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E34" s="0" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D35" s="0" t="s">
         <v>3</v>
       </c>
       <c r="E35" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
+      </c>
+      <c r="F35" s="0" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C36" s="0" t="s">
         <v>12</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E36" s="0" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E37" s="0" t="s">
-        <v>125</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38">
@@ -1171,12 +1171,15 @@
         <v>127</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D38" s="0" t="s">
         <v>13</v>
       </c>
       <c r="E38" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="F38" s="0" t="s">
         <v>128</v>
       </c>
     </row>
@@ -1188,7 +1191,7 @@
         <v>130</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="D39" s="0" t="s">
         <v>13</v>
@@ -1208,7 +1211,7 @@
         <v>134</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D40" s="0" t="s">
         <v>3</v>

--- a/Assets/Resource/MagicFight2/Magic.xlsx
+++ b/Assets/Resource/MagicFight2/Magic.xlsx
@@ -44,138 +44,141 @@
     <t>&lt;sprite=0&gt;光环：使法术附带防御时力量+2</t>
   </si>
   <si>
-    <t>c</t>
+    <t>‌c</t>
   </si>
   <si>
     <t>水刃</t>
   </si>
   <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;使一张法术立即冷却完成</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>寒流</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;重置对方一个法术的冷却时间</t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>潮汐</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;光环：使一个法术立即冷却完毕</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>滚石冲击</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>&lt;sprite=1&gt;守护</t>
+  </si>
+  <si>
+    <t>g</t>
+  </si>
+  <si>
+    <t>陨石</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;快速回填</t>
+  </si>
+  <si>
+    <t>&lt;sprite=1&gt;连续抵挡</t>
+  </si>
+  <si>
+    <t>‌h</t>
+  </si>
+  <si>
+    <t>沉重打击</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;对方无法防御时，将额外减少一点生命</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;此法术无法获得光环的攻击力量加成</t>
+  </si>
+  <si>
+    <t>i</t>
+  </si>
+  <si>
+    <t>沙流</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;减速</t>
+  </si>
+  <si>
+    <t>j</t>
+  </si>
+  <si>
+    <t>闪电</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;连击</t>
+  </si>
+  <si>
+    <t>‌k</t>
+  </si>
+  <si>
+    <t>电场</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;随机查看对方一张手牌，力量大于等于7则立即进入冷却</t>
+  </si>
+  <si>
+    <t>l</t>
+  </si>
+  <si>
+    <t>磁暴</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;攻击时可以将手中其它法术进入冷却，每冷却一张进攻力量+2</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>雷鸣</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;区域加速</t>
+  </si>
+  <si>
+    <t>‌n</t>
+  </si>
+  <si>
+    <t>引雷</t>
+  </si>
+  <si>
     <t>6</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;使一张法术立即冷却完成</t>
-  </si>
-  <si>
-    <t>d</t>
-  </si>
-  <si>
-    <t>寒流</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;重置对方一个法术的冷却时间</t>
-  </si>
-  <si>
-    <t>e</t>
-  </si>
-  <si>
-    <t>潮汐</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;光环：使一个法术立即冷却完毕</t>
-  </si>
-  <si>
-    <t>f</t>
-  </si>
-  <si>
-    <t>滚石冲击</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>&lt;sprite=1&gt;守护</t>
-  </si>
-  <si>
-    <t>g</t>
-  </si>
-  <si>
-    <t>陨石</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;快速回填</t>
-  </si>
-  <si>
-    <t>&lt;sprite=1&gt;连续抵挡</t>
-  </si>
-  <si>
-    <t>h</t>
-  </si>
-  <si>
-    <t>沉重打击</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;对方无法防御时，将额外减少一点生命</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;光环对此法术提供的攻击力加成减半（向下取整）</t>
-  </si>
-  <si>
-    <t>i</t>
-  </si>
-  <si>
-    <t>沙流</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;减速</t>
-  </si>
-  <si>
-    <t>j</t>
-  </si>
-  <si>
-    <t>闪电</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;连击</t>
-  </si>
-  <si>
-    <t>k</t>
-  </si>
-  <si>
-    <t>电场</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;随机查看对方一张手牌，力量大于等于7则立即进入冷却</t>
-  </si>
-  <si>
-    <t>l</t>
-  </si>
-  <si>
-    <t>磁暴</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;攻击时可以将手中其它法术进入冷却，每冷却一张进攻力量+2</t>
-  </si>
-  <si>
-    <t>m</t>
-  </si>
-  <si>
-    <t>雷鸣</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;区域加速</t>
-  </si>
-  <si>
-    <t>n</t>
-  </si>
-  <si>
-    <t>引雷</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
     <t>&lt;sprite=0&gt;光环：使你的力量小于等于4的法术获得连击（不能叠加）</t>
   </si>
   <si>
+    <t>&lt;sprite=1&gt;防御时，力量+3</t>
+  </si>
+  <si>
     <t>o</t>
   </si>
   <si>
@@ -191,7 +194,7 @@
     <t>&lt;sprite=0&gt;恢复一点生命值，减少一点生命上限</t>
   </si>
   <si>
-    <t>q</t>
+    <t>‌q</t>
   </si>
   <si>
     <t>灵魂燃烧</t>
@@ -200,19 +203,22 @@
     <t>&lt;sprite=0&gt;恢复两点生命值，减少一点生命上限</t>
   </si>
   <si>
+    <t>&lt;sprite=0&gt;若首次使用，连击</t>
+  </si>
+  <si>
     <t>r</t>
   </si>
   <si>
     <t>缠绕</t>
   </si>
   <si>
-    <t>s</t>
+    <t>‌s</t>
   </si>
   <si>
     <t>喷泉</t>
   </si>
   <si>
-    <t>t</t>
+    <t>‌t</t>
   </si>
   <si>
     <t>毒刺</t>
@@ -221,9 +227,6 @@
     <t>&lt;sprite=0&gt;双发</t>
   </si>
   <si>
-    <t>&lt;sprite=1&gt;防御时，消除攻击法术除基础伤害外的所有效果（但不包括光环）</t>
-  </si>
-  <si>
     <t>u</t>
   </si>
   <si>
@@ -284,7 +287,7 @@
     <t>&lt;sprite=0&gt;对方使用的光环无效，并且清空对方的所有光环</t>
   </si>
   <si>
-    <t>ab</t>
+    <t>‌ab</t>
   </si>
   <si>
     <t>湍流</t>
@@ -302,7 +305,7 @@
     <t>&lt;sprite=0&gt;你的冷却区每有一张牌，进攻力量+1</t>
   </si>
   <si>
-    <t>ad</t>
+    <t>‌ad</t>
   </si>
   <si>
     <t>雷云</t>
@@ -323,7 +326,7 @@
     <t>&lt;sprite=0&gt;当你的生命值小于对方时，进攻力量+2</t>
   </si>
   <si>
-    <t>af</t>
+    <t>‌af</t>
   </si>
   <si>
     <t>冰封铠甲</t>
@@ -332,9 +335,6 @@
     <t>&lt;sprite=0&gt;光环：使法术附带防御时力量+3</t>
   </si>
   <si>
-    <t>&lt;sprite=1&gt;防御时，力量+4</t>
-  </si>
-  <si>
     <t>ag</t>
   </si>
   <si>
@@ -353,13 +353,13 @@
     <t>&lt;sprite=0&gt;光环：使法术附带进攻力量+2或防御力量+2</t>
   </si>
   <si>
-    <t>ai</t>
-  </si>
-  <si>
-    <t>火雨</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;光环：使法术附带进攻力量+3</t>
+    <t>‌ai</t>
+  </si>
+  <si>
+    <t>爆燃</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;光环：使法术附带进攻力量+4</t>
   </si>
   <si>
     <t>aj</t>
@@ -371,7 +371,7 @@
     <t>&lt;sprite=0&gt;光环：使法术附带进攻力量+1</t>
   </si>
   <si>
-    <t>ak</t>
+    <t>‌ak</t>
   </si>
   <si>
     <t>石化</t>
@@ -380,7 +380,7 @@
     <t>&lt;sprite=0&gt;光环：免疫力量大于等于7的攻击（包括双发）</t>
   </si>
   <si>
-    <t>al</t>
+    <t>‌al</t>
   </si>
   <si>
     <t>石盾</t>
@@ -389,7 +389,7 @@
     <t>&lt;sprite=0&gt;光环：免疫力量小于等于3的攻击（包括双发）</t>
   </si>
   <si>
-    <t>am</t>
+    <t>‌am</t>
   </si>
   <si>
     <t>充能</t>
@@ -592,7 +592,7 @@
         <v>31</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E8" s="0" t="s">
         <v>32</v>
@@ -646,7 +646,7 @@
         <v>41</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D11" s="0" t="s">
         <v>13</v>
@@ -709,18 +709,21 @@
         <v>52</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E14" s="0" t="s">
         <v>53</v>
       </c>
+      <c r="F14" s="0" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C15" s="0" t="s">
         <v>3</v>
@@ -737,10 +740,10 @@
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C16" s="0" t="s">
         <v>13</v>
@@ -749,7 +752,7 @@
         <v>8</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F16" s="0" t="s">
         <v>49</v>
@@ -757,10 +760,10 @@
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C17" s="0" t="s">
         <v>8</v>
@@ -769,15 +772,18 @@
         <v>2</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="F17" s="0" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C18" s="0" t="s">
         <v>13</v>
@@ -791,13 +797,13 @@
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="D19" s="0" t="s">
         <v>8</v>
@@ -808,10 +814,10 @@
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C20" s="0" t="s">
         <v>13</v>
@@ -820,18 +826,15 @@
         <v>13</v>
       </c>
       <c r="E20" s="0" t="s">
-        <v>68</v>
-      </c>
-      <c r="F20" s="0" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C21" s="0" t="s">
         <v>2</v>
@@ -840,7 +843,7 @@
         <v>13</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F21" s="0" t="s">
         <v>27</v>
@@ -848,10 +851,10 @@
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C22" s="0" t="s">
         <v>45</v>
@@ -860,7 +863,7 @@
         <v>3</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F22" s="0" t="s">
         <v>24</v>
@@ -868,10 +871,10 @@
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C23" s="0" t="s">
         <v>3</v>
@@ -880,18 +883,18 @@
         <v>13</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F23" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C24" s="0" t="s">
         <v>3</v>
@@ -900,15 +903,15 @@
         <v>13</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C25" s="0" t="s">
         <v>3</v>
@@ -917,18 +920,18 @@
         <v>8</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="D26" s="0" t="s">
         <v>13</v>
@@ -937,41 +940,41 @@
         <v>4</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="D27" s="0" t="s">
         <v>13</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="D28" s="0" t="s">
         <v>13</v>
       </c>
       <c r="E28" s="0" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F28" s="0" t="s">
         <v>28</v>
@@ -979,10 +982,10 @@
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C29" s="0" t="s">
         <v>3</v>
@@ -991,32 +994,32 @@
         <v>8</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="D30" s="0" t="s">
         <v>8</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C31" s="0" t="s">
         <v>45</v>
@@ -1025,27 +1028,27 @@
         <v>8</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F31" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D32" s="0" t="s">
         <v>13</v>
       </c>
       <c r="E32" s="0" t="s">
-        <v>105</v>
+        <v>36</v>
       </c>
       <c r="F32" s="0" t="s">
         <v>106</v>
@@ -1059,7 +1062,7 @@
         <v>108</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="D33" s="0" t="s">
         <v>13</v>
@@ -1096,10 +1099,10 @@
         <v>114</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E35" s="0" t="s">
         <v>4</v>
@@ -1136,7 +1139,7 @@
         <v>120</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D37" s="0" t="s">
         <v>13</v>
@@ -1153,7 +1156,7 @@
         <v>123</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="D38" s="0" t="s">
         <v>13</v>
@@ -1170,13 +1173,16 @@
         <v>126</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E39" s="0" t="s">
         <v>127</v>
+      </c>
+      <c r="F39" s="0" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="40">
@@ -1187,16 +1193,16 @@
         <v>129</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="D40" s="0" t="s">
         <v>13</v>
       </c>
       <c r="E40" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="F40" s="0" t="s">
         <v>27</v>
-      </c>
-      <c r="F40" s="0" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resource/MagicFight2/Magic.xlsx
+++ b/Assets/Resource/MagicFight2/Magic.xlsx
@@ -44,7 +44,7 @@
     <t>&lt;sprite=0&gt;光环：使法术附带防御时力量+2</t>
   </si>
   <si>
-    <t>‌c</t>
+    <t>c</t>
   </si>
   <si>
     <t>水刃</t>
@@ -101,7 +101,7 @@
     <t>&lt;sprite=1&gt;连续抵挡</t>
   </si>
   <si>
-    <t>‌h</t>
+    <t>h</t>
   </si>
   <si>
     <t>沉重打击</t>
@@ -134,7 +134,7 @@
     <t>&lt;sprite=0&gt;连击</t>
   </si>
   <si>
-    <t>‌k</t>
+    <t>k</t>
   </si>
   <si>
     <t>电场</t>
@@ -164,7 +164,7 @@
     <t>&lt;sprite=0&gt;区域加速</t>
   </si>
   <si>
-    <t>‌n</t>
+    <t>n</t>
   </si>
   <si>
     <t>引雷</t>
@@ -194,7 +194,7 @@
     <t>&lt;sprite=0&gt;恢复一点生命值，减少一点生命上限</t>
   </si>
   <si>
-    <t>‌q</t>
+    <t>q</t>
   </si>
   <si>
     <t>灵魂燃烧</t>
@@ -203,22 +203,19 @@
     <t>&lt;sprite=0&gt;恢复两点生命值，减少一点生命上限</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;若首次使用，连击</t>
-  </si>
-  <si>
     <t>r</t>
   </si>
   <si>
     <t>缠绕</t>
   </si>
   <si>
-    <t>‌s</t>
+    <t>s</t>
   </si>
   <si>
     <t>喷泉</t>
   </si>
   <si>
-    <t>‌t</t>
+    <t>t</t>
   </si>
   <si>
     <t>毒刺</t>
@@ -287,7 +284,7 @@
     <t>&lt;sprite=0&gt;对方使用的光环无效，并且清空对方的所有光环</t>
   </si>
   <si>
-    <t>‌ab</t>
+    <t>ab</t>
   </si>
   <si>
     <t>湍流</t>
@@ -305,7 +302,7 @@
     <t>&lt;sprite=0&gt;你的冷却区每有一张牌，进攻力量+1</t>
   </si>
   <si>
-    <t>‌ad</t>
+    <t>ad</t>
   </si>
   <si>
     <t>雷云</t>
@@ -326,7 +323,7 @@
     <t>&lt;sprite=0&gt;当你的生命值小于对方时，进攻力量+2</t>
   </si>
   <si>
-    <t>‌af</t>
+    <t>af</t>
   </si>
   <si>
     <t>冰封铠甲</t>
@@ -344,6 +341,9 @@
     <t>&lt;sprite=0&gt;光环：使法术附带进攻力量+2</t>
   </si>
   <si>
+    <t>&lt;sprite=1&gt;防御时，力量+2</t>
+  </si>
+  <si>
     <t>ah</t>
   </si>
   <si>
@@ -371,7 +371,7 @@
     <t>&lt;sprite=0&gt;光环：使法术附带进攻力量+1</t>
   </si>
   <si>
-    <t>‌ak</t>
+    <t>ak</t>
   </si>
   <si>
     <t>石化</t>
@@ -380,7 +380,7 @@
     <t>&lt;sprite=0&gt;光环：免疫力量大于等于7的攻击（包括双发）</t>
   </si>
   <si>
-    <t>‌al</t>
+    <t>al</t>
   </si>
   <si>
     <t>石盾</t>
@@ -774,16 +774,13 @@
       <c r="E17" s="0" t="s">
         <v>62</v>
       </c>
-      <c r="F17" s="0" t="s">
-        <v>63</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" s="0" t="s">
         <v>64</v>
-      </c>
-      <c r="B18" s="0" t="s">
-        <v>65</v>
       </c>
       <c r="C18" s="0" t="s">
         <v>13</v>
@@ -792,15 +789,15 @@
         <v>2</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="B19" s="0" t="s">
         <v>66</v>
-      </c>
-      <c r="B19" s="0" t="s">
-        <v>67</v>
       </c>
       <c r="C19" s="0" t="s">
         <v>45</v>
@@ -814,27 +811,27 @@
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="B20" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="C20" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="0" t="s">
         <v>69</v>
-      </c>
-      <c r="C20" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D20" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="E20" s="0" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" s="0" t="s">
         <v>71</v>
-      </c>
-      <c r="B21" s="0" t="s">
-        <v>72</v>
       </c>
       <c r="C21" s="0" t="s">
         <v>2</v>
@@ -843,7 +840,7 @@
         <v>13</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F21" s="0" t="s">
         <v>27</v>
@@ -851,10 +848,10 @@
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="B22" s="0" t="s">
         <v>73</v>
-      </c>
-      <c r="B22" s="0" t="s">
-        <v>74</v>
       </c>
       <c r="C22" s="0" t="s">
         <v>45</v>
@@ -863,7 +860,7 @@
         <v>3</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F22" s="0" t="s">
         <v>24</v>
@@ -871,47 +868,47 @@
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" s="0" t="s">
         <v>75</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="C23" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="0" t="s">
         <v>76</v>
       </c>
-      <c r="C23" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="E23" s="0" t="s">
+      <c r="F23" s="0" t="s">
         <v>77</v>
-      </c>
-      <c r="F23" s="0" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="B24" s="0" t="s">
         <v>79</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="C24" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" s="0" t="s">
         <v>80</v>
-      </c>
-      <c r="C24" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="E24" s="0" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25" s="0" t="s">
         <v>82</v>
-      </c>
-      <c r="B25" s="0" t="s">
-        <v>83</v>
       </c>
       <c r="C25" s="0" t="s">
         <v>3</v>
@@ -920,15 +917,15 @@
         <v>8</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="B26" s="0" t="s">
         <v>85</v>
-      </c>
-      <c r="B26" s="0" t="s">
-        <v>86</v>
       </c>
       <c r="C26" s="0" t="s">
         <v>12</v>
@@ -937,18 +934,18 @@
         <v>13</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
+        <v>87</v>
+      </c>
+      <c r="B27" s="0" t="s">
         <v>88</v>
-      </c>
-      <c r="B27" s="0" t="s">
-        <v>89</v>
       </c>
       <c r="C27" s="0" t="s">
         <v>52</v>
@@ -957,15 +954,15 @@
         <v>13</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="B28" s="0" t="s">
         <v>91</v>
-      </c>
-      <c r="B28" s="0" t="s">
-        <v>92</v>
       </c>
       <c r="C28" s="0" t="s">
         <v>45</v>
@@ -974,7 +971,7 @@
         <v>13</v>
       </c>
       <c r="E28" s="0" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F28" s="0" t="s">
         <v>28</v>
@@ -982,10 +979,10 @@
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="B29" s="0" t="s">
         <v>94</v>
-      </c>
-      <c r="B29" s="0" t="s">
-        <v>95</v>
       </c>
       <c r="C29" s="0" t="s">
         <v>3</v>
@@ -994,15 +991,15 @@
         <v>8</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="B30" s="0" t="s">
         <v>97</v>
-      </c>
-      <c r="B30" s="0" t="s">
-        <v>98</v>
       </c>
       <c r="C30" s="0" t="s">
         <v>45</v>
@@ -1011,15 +1008,15 @@
         <v>8</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="B31" s="0" t="s">
         <v>100</v>
-      </c>
-      <c r="B31" s="0" t="s">
-        <v>101</v>
       </c>
       <c r="C31" s="0" t="s">
         <v>45</v>
@@ -1028,18 +1025,18 @@
         <v>8</v>
       </c>
       <c r="E31" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="F31" s="0" t="s">
         <v>102</v>
-      </c>
-      <c r="F31" s="0" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
+        <v>103</v>
+      </c>
+      <c r="B32" s="0" t="s">
         <v>104</v>
-      </c>
-      <c r="B32" s="0" t="s">
-        <v>105</v>
       </c>
       <c r="C32" s="0" t="s">
         <v>52</v>
@@ -1051,15 +1048,15 @@
         <v>36</v>
       </c>
       <c r="F32" s="0" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
+        <v>106</v>
+      </c>
+      <c r="B33" s="0" t="s">
         <v>107</v>
-      </c>
-      <c r="B33" s="0" t="s">
-        <v>108</v>
       </c>
       <c r="C33" s="0" t="s">
         <v>12</v>
@@ -1068,6 +1065,9 @@
         <v>13</v>
       </c>
       <c r="E33" s="0" t="s">
+        <v>108</v>
+      </c>
+      <c r="F33" s="0" t="s">
         <v>109</v>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
         <v>13</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="F40" s="0" t="s">
         <v>27</v>

--- a/Assets/Resource/MagicFight2/Magic.xlsx
+++ b/Assets/Resource/MagicFight2/Magic.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="132">
   <si>
     <t>a</t>
   </si>
@@ -50,228 +50,234 @@
     <t>水刃</t>
   </si>
   <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;使一张法术立即冷却完成</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>寒流</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;重置对方一个法术的冷却时间</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;快速回填</t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>潮汐</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;光环：使一个法术立即冷却完毕</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>滚石冲击</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>&lt;sprite=1&gt;守护</t>
+  </si>
+  <si>
+    <t>g</t>
+  </si>
+  <si>
+    <t>陨石</t>
+  </si>
+  <si>
+    <t>&lt;sprite=1&gt;连续抵挡</t>
+  </si>
+  <si>
+    <t>h</t>
+  </si>
+  <si>
+    <t>沉重打击</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;对方无法防御时，将额外减少一点生命</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;此法术无法获得光环的攻击力量加成</t>
+  </si>
+  <si>
+    <t>i</t>
+  </si>
+  <si>
+    <t>沙流</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;减速</t>
+  </si>
+  <si>
+    <t>j</t>
+  </si>
+  <si>
+    <t>闪电</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;连击</t>
+  </si>
+  <si>
+    <t>k</t>
+  </si>
+  <si>
+    <t>电场</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;随机查看对方一张手牌，力量大于等于7则立即进入冷却</t>
+  </si>
+  <si>
+    <t>l</t>
+  </si>
+  <si>
+    <t>磁暴</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;攻击时可以将手中其它法术进入冷却，每冷却一张进攻力量+2</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>雷鸣</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;区域加速</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>引雷</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;光环：使你的基础力量小于等于4的法术获得连击（不能叠加）</t>
+  </si>
+  <si>
+    <t>&lt;sprite=1&gt;防御时，力量+3</t>
+  </si>
+  <si>
+    <t>o</t>
+  </si>
+  <si>
+    <t>流星</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>自燃</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;恢复一点生命值，减少一点生命上限</t>
+  </si>
+  <si>
+    <t>q</t>
+  </si>
+  <si>
+    <t>灵魂燃烧</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;恢复两点生命值，减少一点生命上限</t>
+  </si>
+  <si>
+    <t>r</t>
+  </si>
+  <si>
+    <t>缠绕</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;减速×2</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;每剩余一张手牌，冷却时间加一，最多为4</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>喷泉</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>毒刺</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;双发</t>
+  </si>
+  <si>
+    <t>u</t>
+  </si>
+  <si>
+    <t>飞叶连击</t>
+  </si>
+  <si>
+    <t>v</t>
+  </si>
+  <si>
+    <t>藤蔓</t>
+  </si>
+  <si>
+    <t>w</t>
+  </si>
+  <si>
+    <t>狂躁蘑菇</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;若这是你手中的最后两张法术，双发</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;使你的 剩余冷却时间为一 的法术立即冷却完成</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>模仿</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;复制对方冷却区当中的一个 无光环并且力量大于等于5的法术 的效果</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>瀑流</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;使自己冷却区中所有力量小于等于4的法术获得加速</t>
+  </si>
+  <si>
+    <t>z</t>
+  </si>
+  <si>
+    <t>凝固</t>
+  </si>
+  <si>
     <t>7</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;使一张法术立即冷却完成</t>
-  </si>
-  <si>
-    <t>d</t>
-  </si>
-  <si>
-    <t>寒流</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;重置对方一个法术的冷却时间</t>
-  </si>
-  <si>
-    <t>e</t>
-  </si>
-  <si>
-    <t>潮汐</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;光环：使一个法术立即冷却完毕</t>
-  </si>
-  <si>
-    <t>f</t>
-  </si>
-  <si>
-    <t>滚石冲击</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>&lt;sprite=1&gt;守护</t>
-  </si>
-  <si>
-    <t>g</t>
-  </si>
-  <si>
-    <t>陨石</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;快速回填</t>
-  </si>
-  <si>
-    <t>&lt;sprite=1&gt;连续抵挡</t>
-  </si>
-  <si>
-    <t>h</t>
-  </si>
-  <si>
-    <t>沉重打击</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;对方无法防御时，将额外减少一点生命</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;此法术无法获得光环的攻击力量加成</t>
-  </si>
-  <si>
-    <t>i</t>
-  </si>
-  <si>
-    <t>沙流</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;减速</t>
-  </si>
-  <si>
-    <t>j</t>
-  </si>
-  <si>
-    <t>闪电</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;连击</t>
-  </si>
-  <si>
-    <t>k</t>
-  </si>
-  <si>
-    <t>电场</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;随机查看对方一张手牌，力量大于等于7则立即进入冷却</t>
-  </si>
-  <si>
-    <t>l</t>
-  </si>
-  <si>
-    <t>磁暴</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;攻击时可以将手中其它法术进入冷却，每冷却一张进攻力量+2</t>
-  </si>
-  <si>
-    <t>m</t>
-  </si>
-  <si>
-    <t>雷鸣</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;区域加速</t>
-  </si>
-  <si>
-    <t>n</t>
-  </si>
-  <si>
-    <t>引雷</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;光环：使你的力量小于等于4的法术获得连击（不能叠加）</t>
-  </si>
-  <si>
-    <t>&lt;sprite=1&gt;防御时，力量+3</t>
-  </si>
-  <si>
-    <t>o</t>
-  </si>
-  <si>
-    <t>流星</t>
-  </si>
-  <si>
-    <t>p</t>
-  </si>
-  <si>
-    <t>自燃</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;恢复一点生命值，减少一点生命上限</t>
-  </si>
-  <si>
-    <t>q</t>
-  </si>
-  <si>
-    <t>灵魂燃烧</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;恢复两点生命值，减少一点生命上限</t>
-  </si>
-  <si>
-    <t>r</t>
-  </si>
-  <si>
-    <t>缠绕</t>
-  </si>
-  <si>
-    <t>s</t>
-  </si>
-  <si>
-    <t>喷泉</t>
-  </si>
-  <si>
-    <t>t</t>
-  </si>
-  <si>
-    <t>毒刺</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;双发</t>
-  </si>
-  <si>
-    <t>u</t>
-  </si>
-  <si>
-    <t>飞叶连击</t>
-  </si>
-  <si>
-    <t>v</t>
-  </si>
-  <si>
-    <t>藤蔓</t>
-  </si>
-  <si>
-    <t>w</t>
-  </si>
-  <si>
-    <t>狂躁蘑菇</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;若这是你手中的最后两张法术，双发</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;使你的 剩余冷却时间为一 的法术立即冷却完成</t>
-  </si>
-  <si>
-    <t>x</t>
-  </si>
-  <si>
-    <t>模仿</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;复制对方冷却区当中的一个 无光环并且力量大于等于5的法术 的效果</t>
-  </si>
-  <si>
-    <t>y</t>
-  </si>
-  <si>
-    <t>瀑流</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;使自己冷却区中所有力量小于等于4的法术获得加速</t>
-  </si>
-  <si>
-    <t>z</t>
-  </si>
-  <si>
-    <t>凝固</t>
-  </si>
-  <si>
     <t>&lt;sprite=1&gt;防御时，对方法术的力量值锁定为基础值（效果和光环的加成无效）</t>
   </si>
   <si>
@@ -317,10 +323,7 @@
     <t>地波</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;进攻力量+1</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;当你的生命值小于对方时，进攻力量+2</t>
+    <t>&lt;sprite=0&gt;你每损失一点生命值（相较于初始值），进攻力量+2，总计最多+5</t>
   </si>
   <si>
     <t>af</t>
@@ -396,6 +399,9 @@
   </si>
   <si>
     <t>&lt;sprite=0&gt;使你冷却区中 所有法术的剩余冷却 最多为2</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;若攻击时将手中一张其它法术进入冷却，加速</t>
   </si>
   <si>
     <t>an</t>
@@ -523,13 +529,16 @@
       <c r="E4" s="0" t="s">
         <v>17</v>
       </c>
+      <c r="F4" s="0" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" s="0" t="s">
         <v>2</v>
@@ -538,18 +547,18 @@
         <v>3</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" s="0" t="s">
         <v>3</v>
@@ -558,24 +567,24 @@
         <v>4</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7" s="0" t="s">
         <v>3</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F7" s="0" t="s">
         <v>28</v>
@@ -635,7 +644,7 @@
         <v>39</v>
       </c>
       <c r="F10" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11">
@@ -706,24 +715,24 @@
         <v>51</v>
       </c>
       <c r="C14" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="0" t="s">
         <v>52</v>
       </c>
-      <c r="D14" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="0" t="s">
+      <c r="F14" s="0" t="s">
         <v>53</v>
-      </c>
-      <c r="F14" s="0" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" s="0" t="s">
         <v>55</v>
-      </c>
-      <c r="B15" s="0" t="s">
-        <v>56</v>
       </c>
       <c r="C15" s="0" t="s">
         <v>3</v>
@@ -740,10 +749,10 @@
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" s="0" t="s">
         <v>57</v>
-      </c>
-      <c r="B16" s="0" t="s">
-        <v>58</v>
       </c>
       <c r="C16" s="0" t="s">
         <v>13</v>
@@ -752,7 +761,7 @@
         <v>8</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F16" s="0" t="s">
         <v>49</v>
@@ -760,10 +769,10 @@
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" s="0" t="s">
         <v>60</v>
-      </c>
-      <c r="B17" s="0" t="s">
-        <v>61</v>
       </c>
       <c r="C17" s="0" t="s">
         <v>8</v>
@@ -772,15 +781,15 @@
         <v>2</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="B18" s="0" t="s">
         <v>63</v>
-      </c>
-      <c r="B18" s="0" t="s">
-        <v>64</v>
       </c>
       <c r="C18" s="0" t="s">
         <v>13</v>
@@ -789,15 +798,18 @@
         <v>2</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>36</v>
+        <v>64</v>
+      </c>
+      <c r="F18" s="0" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C19" s="0" t="s">
         <v>45</v>
@@ -811,10 +823,10 @@
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C20" s="0" t="s">
         <v>13</v>
@@ -823,15 +835,15 @@
         <v>13</v>
       </c>
       <c r="E20" s="0" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C21" s="0" t="s">
         <v>2</v>
@@ -840,18 +852,18 @@
         <v>13</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F21" s="0" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C22" s="0" t="s">
         <v>45</v>
@@ -860,18 +872,18 @@
         <v>3</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F22" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C23" s="0" t="s">
         <v>3</v>
@@ -880,18 +892,18 @@
         <v>13</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F23" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C24" s="0" t="s">
         <v>3</v>
@@ -900,69 +912,69 @@
         <v>13</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="D25" s="0" t="s">
         <v>8</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>12</v>
+        <v>87</v>
       </c>
       <c r="D26" s="0" t="s">
         <v>13</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="D27" s="0" t="s">
         <v>13</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C28" s="0" t="s">
         <v>45</v>
@@ -971,7 +983,7 @@
         <v>13</v>
       </c>
       <c r="E28" s="0" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F28" s="0" t="s">
         <v>28</v>
@@ -979,10 +991,10 @@
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C29" s="0" t="s">
         <v>3</v>
@@ -991,15 +1003,15 @@
         <v>8</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C30" s="0" t="s">
         <v>45</v>
@@ -1008,38 +1020,35 @@
         <v>8</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="D31" s="0" t="s">
         <v>8</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>101</v>
-      </c>
-      <c r="F31" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="D32" s="0" t="s">
         <v>13</v>
@@ -1048,35 +1057,35 @@
         <v>36</v>
       </c>
       <c r="F32" s="0" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>12</v>
+        <v>87</v>
       </c>
       <c r="D33" s="0" t="s">
         <v>13</v>
       </c>
       <c r="E33" s="0" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F33" s="0" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C34" s="0" t="s">
         <v>13</v>
@@ -1088,18 +1097,18 @@
         <v>36</v>
       </c>
       <c r="F34" s="0" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="D35" s="0" t="s">
         <v>3</v>
@@ -1108,15 +1117,15 @@
         <v>4</v>
       </c>
       <c r="F35" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C36" s="0" t="s">
         <v>31</v>
@@ -1125,18 +1134,18 @@
         <v>3</v>
       </c>
       <c r="E36" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F36" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C37" s="0" t="s">
         <v>13</v>
@@ -1145,64 +1154,64 @@
         <v>13</v>
       </c>
       <c r="E37" s="0" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>12</v>
+        <v>87</v>
       </c>
       <c r="D38" s="0" t="s">
         <v>13</v>
       </c>
       <c r="E38" s="0" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="D39" s="0" t="s">
         <v>13</v>
       </c>
       <c r="E39" s="0" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>27</v>
+        <v>129</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>12</v>
+        <v>87</v>
       </c>
       <c r="D40" s="0" t="s">
         <v>13</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="F40" s="0" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resource/MagicFight2/Magic.xlsx
+++ b/Assets/Resource/MagicFight2/Magic.xlsx
@@ -50,54 +50,57 @@
     <t>水刃</t>
   </si>
   <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;使一张法术立即冷却完成</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>寒流</t>
+  </si>
+  <si>
     <t>6</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;使一张法术立即冷却完成</t>
-  </si>
-  <si>
-    <t>d</t>
-  </si>
-  <si>
-    <t>寒流</t>
-  </si>
-  <si>
     <t>&lt;sprite=0&gt;重置对方一个法术的冷却时间</t>
   </si>
   <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>潮汐</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;光环：使一个法术立即冷却完毕</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>滚石冲击</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>&lt;sprite=1&gt;守护</t>
+  </si>
+  <si>
+    <t>g</t>
+  </si>
+  <si>
+    <t>陨石</t>
+  </si>
+  <si>
     <t>&lt;sprite=0&gt;快速回填</t>
   </si>
   <si>
-    <t>e</t>
-  </si>
-  <si>
-    <t>潮汐</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;光环：使一个法术立即冷却完毕</t>
-  </si>
-  <si>
-    <t>f</t>
-  </si>
-  <si>
-    <t>滚石冲击</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>&lt;sprite=1&gt;守护</t>
-  </si>
-  <si>
-    <t>g</t>
-  </si>
-  <si>
-    <t>陨石</t>
-  </si>
-  <si>
     <t>&lt;sprite=1&gt;连续抵挡</t>
   </si>
   <si>
@@ -149,9 +152,6 @@
     <t>磁暴</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>&lt;sprite=0&gt;攻击时可以将手中其它法术进入冷却，每冷却一张进攻力量+2</t>
   </si>
   <si>
@@ -209,7 +209,7 @@
     <t>&lt;sprite=0&gt;减速×2</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;每剩余一张手牌，冷却时间加一，最多为4</t>
+    <t>&lt;sprite=0&gt;进攻时，冷却时间额外+3</t>
   </si>
   <si>
     <t>s</t>
@@ -323,7 +323,10 @@
     <t>地波</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;你每损失一点生命值（相较于初始值），进攻力量+2，总计最多+5</t>
+    <t>&lt;sprite=0&gt;每损失一点生命值（相较于初始值），进攻力量+2，总计最多+5</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;造成伤害时，冷却额外+1</t>
   </si>
   <si>
     <t>af</t>
@@ -398,10 +401,7 @@
     <t>充能</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;使你冷却区中 所有法术的剩余冷却 最多为2</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;若攻击时将手中一张其它法术进入冷却，加速</t>
+    <t>&lt;sprite=0&gt;攻击时可以将手中其它法术进入冷却，每冷却一张获得一层加速</t>
   </si>
   <si>
     <t>an</t>
@@ -521,15 +521,12 @@
         <v>16</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D4" s="0" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="0" t="s">
         <v>18</v>
       </c>
     </row>
@@ -584,64 +581,64 @@
         <v>3</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D8" s="0" t="s">
         <v>3</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F8" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D9" s="0" t="s">
         <v>13</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D10" s="0" t="s">
         <v>3</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F10" s="0" t="s">
         <v>25</v>
@@ -649,10 +646,10 @@
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C11" s="0" t="s">
         <v>8</v>
@@ -661,21 +658,21 @@
         <v>13</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="D12" s="0" t="s">
         <v>13</v>
@@ -684,7 +681,7 @@
         <v>46</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
@@ -704,7 +701,7 @@
         <v>49</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
@@ -715,7 +712,7 @@
         <v>51</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D14" s="0" t="s">
         <v>13</v>
@@ -735,7 +732,7 @@
         <v>55</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D15" s="0" t="s">
         <v>13</v>
@@ -812,7 +809,7 @@
         <v>67</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="D19" s="0" t="s">
         <v>8</v>
@@ -855,7 +852,7 @@
         <v>70</v>
       </c>
       <c r="F21" s="0" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22">
@@ -866,7 +863,7 @@
         <v>74</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="D22" s="0" t="s">
         <v>3</v>
@@ -923,7 +920,7 @@
         <v>83</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="D25" s="0" t="s">
         <v>8</v>
@@ -960,7 +957,7 @@
         <v>90</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D27" s="0" t="s">
         <v>13</v>
@@ -977,7 +974,7 @@
         <v>93</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="D28" s="0" t="s">
         <v>13</v>
@@ -986,7 +983,7 @@
         <v>94</v>
       </c>
       <c r="F28" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29">
@@ -1014,7 +1011,7 @@
         <v>99</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="D30" s="0" t="s">
         <v>8</v>
@@ -1039,33 +1036,36 @@
       <c r="E31" s="0" t="s">
         <v>103</v>
       </c>
+      <c r="F31" s="0" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D32" s="0" t="s">
         <v>13</v>
       </c>
       <c r="E32" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F32" s="0" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C33" s="0" t="s">
         <v>87</v>
@@ -1074,41 +1074,41 @@
         <v>13</v>
       </c>
       <c r="E33" s="0" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F33" s="0" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D34" s="0" t="s">
         <v>8</v>
       </c>
       <c r="E34" s="0" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="F34" s="0" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D35" s="0" t="s">
         <v>3</v>
@@ -1117,52 +1117,52 @@
         <v>4</v>
       </c>
       <c r="F35" s="0" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D36" s="0" t="s">
         <v>3</v>
       </c>
       <c r="E36" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F36" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C37" s="0" t="s">
         <v>13</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E37" s="0" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C38" s="0" t="s">
         <v>87</v>
@@ -1171,15 +1171,15 @@
         <v>13</v>
       </c>
       <c r="E38" s="0" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C39" s="0" t="s">
         <v>87</v>
@@ -1188,7 +1188,7 @@
         <v>13</v>
       </c>
       <c r="E39" s="0" t="s">
-        <v>128</v>
+        <v>4</v>
       </c>
       <c r="F39" s="0" t="s">
         <v>129</v>
@@ -1208,10 +1208,10 @@
         <v>13</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F40" s="0" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resource/MagicFight2/Magic.xlsx
+++ b/Assets/Resource/MagicFight2/Magic.xlsx
@@ -110,21 +110,24 @@
     <t>沉重打击</t>
   </si>
   <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;对方无法防御时，将额外减少一点生命</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;此法术无法获得光环的攻击力量加成</t>
+  </si>
+  <si>
+    <t>i</t>
+  </si>
+  <si>
+    <t>沙流</t>
+  </si>
+  <si>
     <t>8</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;对方无法防御时，将额外减少一点生命</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;此法术无法获得光环的攻击力量加成</t>
-  </si>
-  <si>
-    <t>i</t>
-  </si>
-  <si>
-    <t>沙流</t>
-  </si>
-  <si>
     <t>&lt;sprite=0&gt;减速</t>
   </si>
   <si>
@@ -275,9 +278,6 @@
     <t>凝固</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
     <t>&lt;sprite=1&gt;防御时，对方法术的力量值锁定为基础值（效果和光环的加成无效）</t>
   </si>
   <si>
@@ -347,9 +347,6 @@
     <t>&lt;sprite=0&gt;光环：使法术附带进攻力量+2</t>
   </si>
   <si>
-    <t>&lt;sprite=1&gt;防御时，力量+2</t>
-  </si>
-  <si>
     <t>ah</t>
   </si>
   <si>
@@ -408,6 +405,9 @@
   </si>
   <si>
     <t>地震</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;使自己和对方的剩余冷却为1的法术都获得减速</t>
   </si>
 </sst>
 </file>
@@ -598,7 +598,7 @@
         <v>32</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E8" s="0" t="s">
         <v>33</v>
@@ -615,30 +615,30 @@
         <v>36</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D9" s="0" t="s">
         <v>13</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D10" s="0" t="s">
         <v>3</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F10" s="0" t="s">
         <v>25</v>
@@ -646,10 +646,10 @@
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" s="0" t="s">
         <v>8</v>
@@ -658,18 +658,18 @@
         <v>13</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C12" s="0" t="s">
         <v>12</v>
@@ -678,18 +678,18 @@
         <v>13</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C13" s="0" t="s">
         <v>8</v>
@@ -698,18 +698,18 @@
         <v>3</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C14" s="0" t="s">
         <v>17</v>
@@ -718,18 +718,18 @@
         <v>13</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C15" s="0" t="s">
         <v>13</v>
@@ -741,15 +741,15 @@
         <v>4</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C16" s="0" t="s">
         <v>13</v>
@@ -758,18 +758,18 @@
         <v>8</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C17" s="0" t="s">
         <v>8</v>
@@ -778,15 +778,15 @@
         <v>2</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C18" s="0" t="s">
         <v>13</v>
@@ -795,18 +795,18 @@
         <v>2</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F18" s="0" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C19" s="0" t="s">
         <v>3</v>
@@ -815,15 +815,15 @@
         <v>8</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C20" s="0" t="s">
         <v>13</v>
@@ -832,15 +832,15 @@
         <v>13</v>
       </c>
       <c r="E20" s="0" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C21" s="0" t="s">
         <v>2</v>
@@ -849,7 +849,7 @@
         <v>13</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F21" s="0" t="s">
         <v>28</v>
@@ -857,10 +857,10 @@
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C22" s="0" t="s">
         <v>12</v>
@@ -869,7 +869,7 @@
         <v>3</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F22" s="0" t="s">
         <v>25</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C23" s="0" t="s">
         <v>3</v>
@@ -889,18 +889,18 @@
         <v>13</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F23" s="0" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C24" s="0" t="s">
         <v>3</v>
@@ -909,15 +909,15 @@
         <v>13</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C25" s="0" t="s">
         <v>12</v>
@@ -926,24 +926,24 @@
         <v>8</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>87</v>
+        <v>32</v>
       </c>
       <c r="D26" s="0" t="s">
         <v>13</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="F26" s="0" t="s">
         <v>88</v>
@@ -1054,7 +1054,7 @@
         <v>13</v>
       </c>
       <c r="E32" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F32" s="0" t="s">
         <v>107</v>
@@ -1068,7 +1068,7 @@
         <v>109</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>87</v>
+        <v>32</v>
       </c>
       <c r="D33" s="0" t="s">
         <v>13</v>
@@ -1076,16 +1076,13 @@
       <c r="E33" s="0" t="s">
         <v>110</v>
       </c>
-      <c r="F33" s="0" t="s">
-        <v>111</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
+        <v>111</v>
+      </c>
+      <c r="B34" s="0" t="s">
         <v>112</v>
-      </c>
-      <c r="B34" s="0" t="s">
-        <v>113</v>
       </c>
       <c r="C34" s="0" t="s">
         <v>3</v>
@@ -1094,18 +1091,18 @@
         <v>8</v>
       </c>
       <c r="E34" s="0" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F34" s="0" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
+        <v>114</v>
+      </c>
+      <c r="B35" s="0" t="s">
         <v>115</v>
-      </c>
-      <c r="B35" s="0" t="s">
-        <v>116</v>
       </c>
       <c r="C35" s="0" t="s">
         <v>17</v>
@@ -1117,72 +1114,72 @@
         <v>4</v>
       </c>
       <c r="F35" s="0" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="B36" s="0" t="s">
         <v>118</v>
       </c>
-      <c r="B36" s="0" t="s">
+      <c r="C36" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="D36" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E36" s="0" t="s">
         <v>119</v>
       </c>
-      <c r="C36" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="D36" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="E36" s="0" t="s">
-        <v>120</v>
-      </c>
       <c r="F36" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
+        <v>120</v>
+      </c>
+      <c r="B37" s="0" t="s">
         <v>121</v>
       </c>
-      <c r="B37" s="0" t="s">
+      <c r="C37" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E37" s="0" t="s">
         <v>122</v>
-      </c>
-      <c r="C37" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D37" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="E37" s="0" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="B38" s="0" t="s">
         <v>124</v>
       </c>
-      <c r="B38" s="0" t="s">
+      <c r="C38" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="D38" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E38" s="0" t="s">
         <v>125</v>
-      </c>
-      <c r="C38" s="0" t="s">
-        <v>87</v>
-      </c>
-      <c r="D38" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="E38" s="0" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="B39" s="0" t="s">
         <v>127</v>
       </c>
-      <c r="B39" s="0" t="s">
-        <v>128</v>
-      </c>
       <c r="C39" s="0" t="s">
-        <v>87</v>
+        <v>32</v>
       </c>
       <c r="D39" s="0" t="s">
         <v>13</v>
@@ -1191,27 +1188,24 @@
         <v>4</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
+        <v>129</v>
+      </c>
+      <c r="B40" s="0" t="s">
         <v>130</v>
       </c>
-      <c r="B40" s="0" t="s">
+      <c r="C40" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="D40" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E40" s="0" t="s">
         <v>131</v>
-      </c>
-      <c r="C40" s="0" t="s">
-        <v>87</v>
-      </c>
-      <c r="D40" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="E40" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="F40" s="0" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resource/MagicFight2/Magic.xlsx
+++ b/Assets/Resource/MagicFight2/Magic.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="134">
   <si>
     <t>a</t>
   </si>
@@ -203,6 +203,9 @@
     <t>&lt;sprite=0&gt;恢复两点生命值，减少一点生命上限</t>
   </si>
   <si>
+    <t>&lt;sprite=0&gt;若首次使用，连击</t>
+  </si>
+  <si>
     <t>r</t>
   </si>
   <si>
@@ -287,7 +290,7 @@
     <t>大火球</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;对方使用的光环无效，并且清空对方的所有光环</t>
+    <t>&lt;sprite=0&gt;使对方 已激活但仍未使用的 所有光环失效</t>
   </si>
   <si>
     <t>ab</t>
@@ -314,7 +317,7 @@
     <t>雷云</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;随机查看对方一张手牌，力量小于等于4则立即进入冷却</t>
+    <t>&lt;sprite=0&gt;随机查看对方一张手牌，力量小于等于4则立即进入冷却，冷却时间至少为3</t>
   </si>
   <si>
     <t>ae</t>
@@ -323,10 +326,10 @@
     <t>地波</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;每损失一点生命值（相较于初始值），进攻力量+2，总计最多+5</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;造成伤害时，冷却额外+1</t>
+    <t>&lt;sprite=0&gt;你每损失一点生命值（相较初始值），进攻力量+1</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;被攻击玩家每损失一点生命值（相较初始值），进攻力量+1</t>
   </si>
   <si>
     <t>af</t>
@@ -335,7 +338,10 @@
     <t>冰封铠甲</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;光环：使法术附带防御时力量+3</t>
+    <t>&lt;sprite=0&gt;光环：使法术附带防御时力量+4</t>
+  </si>
+  <si>
+    <t>&lt;sprite=1&gt;防御时，冷却减1</t>
   </si>
   <si>
     <t>ag</t>
@@ -407,7 +413,7 @@
     <t>地震</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;使自己和对方的剩余冷却为1的法术都获得减速</t>
+    <t>&lt;sprite=0&gt;使自己和对方的 冷却区中剩余冷却为1的法术 都获得减速</t>
   </si>
 </sst>
 </file>
@@ -780,13 +786,16 @@
       <c r="E17" s="0" t="s">
         <v>62</v>
       </c>
+      <c r="F17" s="0" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C18" s="0" t="s">
         <v>13</v>
@@ -795,18 +804,18 @@
         <v>2</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F18" s="0" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C19" s="0" t="s">
         <v>3</v>
@@ -820,10 +829,10 @@
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C20" s="0" t="s">
         <v>13</v>
@@ -832,15 +841,15 @@
         <v>13</v>
       </c>
       <c r="E20" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C21" s="0" t="s">
         <v>2</v>
@@ -849,7 +858,7 @@
         <v>13</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F21" s="0" t="s">
         <v>28</v>
@@ -857,10 +866,10 @@
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C22" s="0" t="s">
         <v>12</v>
@@ -869,7 +878,7 @@
         <v>3</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F22" s="0" t="s">
         <v>25</v>
@@ -877,10 +886,10 @@
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C23" s="0" t="s">
         <v>3</v>
@@ -889,18 +898,18 @@
         <v>13</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F23" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C24" s="0" t="s">
         <v>3</v>
@@ -909,15 +918,15 @@
         <v>13</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C25" s="0" t="s">
         <v>12</v>
@@ -926,15 +935,15 @@
         <v>8</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C26" s="0" t="s">
         <v>32</v>
@@ -946,15 +955,15 @@
         <v>28</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C27" s="0" t="s">
         <v>17</v>
@@ -963,15 +972,18 @@
         <v>13</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>91</v>
+        <v>38</v>
+      </c>
+      <c r="F27" s="0" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C28" s="0" t="s">
         <v>12</v>
@@ -980,7 +992,7 @@
         <v>13</v>
       </c>
       <c r="E28" s="0" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F28" s="0" t="s">
         <v>29</v>
@@ -988,10 +1000,10 @@
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C29" s="0" t="s">
         <v>3</v>
@@ -1000,15 +1012,15 @@
         <v>8</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C30" s="0" t="s">
         <v>12</v>
@@ -1017,15 +1029,15 @@
         <v>8</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C31" s="0" t="s">
         <v>3</v>
@@ -1034,18 +1046,18 @@
         <v>8</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F31" s="0" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C32" s="0" t="s">
         <v>17</v>
@@ -1054,18 +1066,18 @@
         <v>13</v>
       </c>
       <c r="E32" s="0" t="s">
-        <v>38</v>
+        <v>108</v>
       </c>
       <c r="F32" s="0" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C33" s="0" t="s">
         <v>32</v>
@@ -1074,15 +1086,15 @@
         <v>13</v>
       </c>
       <c r="E33" s="0" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C34" s="0" t="s">
         <v>3</v>
@@ -1094,15 +1106,15 @@
         <v>38</v>
       </c>
       <c r="F34" s="0" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C35" s="0" t="s">
         <v>17</v>
@@ -1114,15 +1126,15 @@
         <v>4</v>
       </c>
       <c r="F35" s="0" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C36" s="0" t="s">
         <v>37</v>
@@ -1131,18 +1143,18 @@
         <v>3</v>
       </c>
       <c r="E36" s="0" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F36" s="0" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C37" s="0" t="s">
         <v>13</v>
@@ -1151,15 +1163,15 @@
         <v>3</v>
       </c>
       <c r="E37" s="0" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C38" s="0" t="s">
         <v>37</v>
@@ -1168,15 +1180,15 @@
         <v>3</v>
       </c>
       <c r="E38" s="0" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C39" s="0" t="s">
         <v>32</v>
@@ -1188,15 +1200,15 @@
         <v>4</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C40" s="0" t="s">
         <v>32</v>
@@ -1205,7 +1217,7 @@
         <v>3</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resource/MagicFight2/Magic.xlsx
+++ b/Assets/Resource/MagicFight2/Magic.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="135">
   <si>
     <t>a</t>
   </si>
@@ -80,6 +80,9 @@
     <t>&lt;sprite=0&gt;光环：使一个法术立即冷却完毕</t>
   </si>
   <si>
+    <t>&lt;sprite=0&gt;此光环仅能在 轮到你进攻并且出牌之前 使用</t>
+  </si>
+  <si>
     <t>f</t>
   </si>
   <si>
@@ -116,7 +119,7 @@
     <t>&lt;sprite=0&gt;对方无法防御时，将额外减少一点生命</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;此法术无法获得光环的攻击力量加成</t>
+    <t>&lt;sprite=0&gt;此法术的进攻力量无法增加</t>
   </si>
   <si>
     <t>i</t>
@@ -272,7 +275,10 @@
     <t>瀑流</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;使自己冷却区中所有力量小于等于4的法术获得加速</t>
+    <t>&lt;sprite=0&gt;加速一张力量小于等于4的法术</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;可以再打出一张手牌，但其不能造成伤害</t>
   </si>
   <si>
     <t>z</t>
@@ -290,7 +296,7 @@
     <t>大火球</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;使对方 已激活但仍未使用的 所有光环失效</t>
+    <t>&lt;sprite=0&gt;使对方 仍未使用的所有光环 失效</t>
   </si>
   <si>
     <t>ab</t>
@@ -326,10 +332,7 @@
     <t>地波</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;你每损失一点生命值（相较初始值），进攻力量+1</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;被攻击玩家每损失一点生命值（相较初始值），进攻力量+1</t>
+    <t>&lt;sprite=0&gt;你或对方每损失一点生命值（相较初始值），都会进攻力量+1</t>
   </si>
   <si>
     <t>af</t>
@@ -404,7 +407,7 @@
     <t>充能</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;攻击时可以将手中其它法术进入冷却，每冷却一张获得一层加速</t>
+    <t>&lt;sprite=0&gt;攻击时可以将手中其它法术进入冷却，每冷却一张获得一次加速</t>
   </si>
   <si>
     <t>an</t>
@@ -413,7 +416,7 @@
     <t>地震</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;使自己和对方的 冷却区中剩余冷却为1的法术 都获得减速</t>
+    <t>&lt;sprite=0&gt;使自己和对方的 冷却区中剩余冷却为1的法术 都被减速</t>
   </si>
 </sst>
 </file>
@@ -552,16 +555,19 @@
       <c r="E5" s="0" t="s">
         <v>21</v>
       </c>
+      <c r="F5" s="0" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D6" s="0" t="s">
         <v>3</v>
@@ -570,92 +576,92 @@
         <v>4</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D7" s="0" t="s">
         <v>3</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D8" s="0" t="s">
         <v>13</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F8" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D9" s="0" t="s">
         <v>13</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D10" s="0" t="s">
         <v>3</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F10" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C11" s="0" t="s">
         <v>8</v>
@@ -664,18 +670,18 @@
         <v>13</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C12" s="0" t="s">
         <v>12</v>
@@ -684,18 +690,18 @@
         <v>13</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C13" s="0" t="s">
         <v>8</v>
@@ -704,18 +710,18 @@
         <v>3</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C14" s="0" t="s">
         <v>17</v>
@@ -724,18 +730,18 @@
         <v>13</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C15" s="0" t="s">
         <v>13</v>
@@ -747,15 +753,15 @@
         <v>4</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C16" s="0" t="s">
         <v>13</v>
@@ -764,18 +770,18 @@
         <v>8</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C17" s="0" t="s">
         <v>8</v>
@@ -784,18 +790,18 @@
         <v>2</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C18" s="0" t="s">
         <v>13</v>
@@ -804,18 +810,18 @@
         <v>2</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F18" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C19" s="0" t="s">
         <v>3</v>
@@ -824,15 +830,15 @@
         <v>8</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C20" s="0" t="s">
         <v>13</v>
@@ -841,15 +847,15 @@
         <v>13</v>
       </c>
       <c r="E20" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C21" s="0" t="s">
         <v>2</v>
@@ -858,18 +864,18 @@
         <v>13</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F21" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C22" s="0" t="s">
         <v>12</v>
@@ -878,18 +884,18 @@
         <v>3</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F22" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C23" s="0" t="s">
         <v>3</v>
@@ -898,18 +904,18 @@
         <v>13</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F23" s="0" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C24" s="0" t="s">
         <v>3</v>
@@ -918,15 +924,15 @@
         <v>13</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C25" s="0" t="s">
         <v>12</v>
@@ -935,35 +941,38 @@
         <v>8</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="F25" s="0" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D26" s="0" t="s">
         <v>13</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C27" s="0" t="s">
         <v>17</v>
@@ -972,18 +981,18 @@
         <v>13</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F27" s="0" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C28" s="0" t="s">
         <v>12</v>
@@ -992,18 +1001,18 @@
         <v>13</v>
       </c>
       <c r="E28" s="0" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F28" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C29" s="0" t="s">
         <v>3</v>
@@ -1012,15 +1021,15 @@
         <v>8</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C30" s="0" t="s">
         <v>12</v>
@@ -1029,15 +1038,15 @@
         <v>8</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C31" s="0" t="s">
         <v>3</v>
@@ -1046,18 +1055,15 @@
         <v>8</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>104</v>
-      </c>
-      <c r="F31" s="0" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C32" s="0" t="s">
         <v>17</v>
@@ -1066,35 +1072,35 @@
         <v>13</v>
       </c>
       <c r="E32" s="0" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F32" s="0" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D33" s="0" t="s">
         <v>13</v>
       </c>
       <c r="E33" s="0" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C34" s="0" t="s">
         <v>3</v>
@@ -1103,18 +1109,18 @@
         <v>8</v>
       </c>
       <c r="E34" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F34" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C35" s="0" t="s">
         <v>17</v>
@@ -1126,35 +1132,35 @@
         <v>4</v>
       </c>
       <c r="F35" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D36" s="0" t="s">
         <v>3</v>
       </c>
       <c r="E36" s="0" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F36" s="0" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C37" s="0" t="s">
         <v>13</v>
@@ -1163,35 +1169,35 @@
         <v>3</v>
       </c>
       <c r="E37" s="0" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D38" s="0" t="s">
         <v>3</v>
       </c>
       <c r="E38" s="0" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D39" s="0" t="s">
         <v>13</v>
@@ -1200,24 +1206,24 @@
         <v>4</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D40" s="0" t="s">
         <v>3</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resource/MagicFight2/Magic.xlsx
+++ b/Assets/Resource/MagicFight2/Magic.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="133">
   <si>
     <t>a</t>
   </si>
@@ -119,7 +119,7 @@
     <t>&lt;sprite=0&gt;对方无法防御时，将额外减少一点生命</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;此法术的进攻力量无法增加</t>
+    <t>&lt;sprite=0&gt;此法术的进攻力量不能增加</t>
   </si>
   <si>
     <t>i</t>
@@ -179,126 +179,123 @@
     <t>&lt;sprite=0&gt;光环：使你的基础力量小于等于4的法术获得连击（不能叠加）</t>
   </si>
   <si>
+    <t>o</t>
+  </si>
+  <si>
+    <t>流星</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>自燃</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;恢复一点生命值，减少一点生命上限</t>
+  </si>
+  <si>
+    <t>q</t>
+  </si>
+  <si>
+    <t>灵魂燃烧</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;恢复两点生命值，减少一点生命上限</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;若首次使用，连击</t>
+  </si>
+  <si>
+    <t>r</t>
+  </si>
+  <si>
+    <t>缠绕</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;减速×2</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;进攻时，冷却时间额外+3</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>喷泉</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>毒刺</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;双发</t>
+  </si>
+  <si>
+    <t>u</t>
+  </si>
+  <si>
+    <t>飞叶连击</t>
+  </si>
+  <si>
+    <t>v</t>
+  </si>
+  <si>
+    <t>藤蔓</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;若这是你的最后三张手牌之一或更少，快速回填×2</t>
+  </si>
+  <si>
+    <t>w</t>
+  </si>
+  <si>
+    <t>狂躁蘑菇</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>模仿</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;复制对方冷却区当中的一个 无光环并且力量大于等于5的法术 的效果</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>瀑流</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;加速一张力量小于等于4的法术</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;可以再打出一张手牌，但其不能造成伤害</t>
+  </si>
+  <si>
+    <t>z</t>
+  </si>
+  <si>
+    <t>凝固</t>
+  </si>
+  <si>
+    <t>&lt;sprite=1&gt;防御时，对方法术的力量值锁定为基础值（效果和光环的加成无效）</t>
+  </si>
+  <si>
+    <t>aa</t>
+  </si>
+  <si>
+    <t>大火球</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;对方无法使用光环，并且使其所有光环失效</t>
+  </si>
+  <si>
     <t>&lt;sprite=1&gt;防御时，力量+3</t>
   </si>
   <si>
-    <t>o</t>
-  </si>
-  <si>
-    <t>流星</t>
-  </si>
-  <si>
-    <t>p</t>
-  </si>
-  <si>
-    <t>自燃</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;恢复一点生命值，减少一点生命上限</t>
-  </si>
-  <si>
-    <t>q</t>
-  </si>
-  <si>
-    <t>灵魂燃烧</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;恢复两点生命值，减少一点生命上限</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;若首次使用，连击</t>
-  </si>
-  <si>
-    <t>r</t>
-  </si>
-  <si>
-    <t>缠绕</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;减速×2</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;进攻时，冷却时间额外+3</t>
-  </si>
-  <si>
-    <t>s</t>
-  </si>
-  <si>
-    <t>喷泉</t>
-  </si>
-  <si>
-    <t>t</t>
-  </si>
-  <si>
-    <t>毒刺</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;双发</t>
-  </si>
-  <si>
-    <t>u</t>
-  </si>
-  <si>
-    <t>飞叶连击</t>
-  </si>
-  <si>
-    <t>v</t>
-  </si>
-  <si>
-    <t>藤蔓</t>
-  </si>
-  <si>
-    <t>w</t>
-  </si>
-  <si>
-    <t>狂躁蘑菇</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;若这是你手中的最后两张法术，双发</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;使你的 剩余冷却时间为一 的法术立即冷却完成</t>
-  </si>
-  <si>
-    <t>x</t>
-  </si>
-  <si>
-    <t>模仿</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;复制对方冷却区当中的一个 无光环并且力量大于等于5的法术 的效果</t>
-  </si>
-  <si>
-    <t>y</t>
-  </si>
-  <si>
-    <t>瀑流</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;加速一张力量小于等于4的法术</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;可以再打出一张手牌，但其不能造成伤害</t>
-  </si>
-  <si>
-    <t>z</t>
-  </si>
-  <si>
-    <t>凝固</t>
-  </si>
-  <si>
-    <t>&lt;sprite=1&gt;防御时，对方法术的力量值锁定为基础值（效果和光环的加成无效）</t>
-  </si>
-  <si>
-    <t>aa</t>
-  </si>
-  <si>
-    <t>大火球</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;使对方 仍未使用的所有光环 失效</t>
-  </si>
-  <si>
     <t>ab</t>
   </si>
   <si>
@@ -341,12 +338,6 @@
     <t>冰封铠甲</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;光环：使法术附带防御时力量+4</t>
-  </si>
-  <si>
-    <t>&lt;sprite=1&gt;防御时，冷却减1</t>
-  </si>
-  <si>
     <t>ag</t>
   </si>
   <si>
@@ -354,6 +345,9 @@
   </si>
   <si>
     <t>&lt;sprite=0&gt;光环：使法术附带进攻力量+2</t>
+  </si>
+  <si>
+    <t>&lt;sprite=1&gt;防御 力量小于等于4的攻击 时，冷却减1</t>
   </si>
   <si>
     <t>ah</t>
@@ -652,9 +646,6 @@
       <c r="E10" s="0" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="0" t="s">
-        <v>26</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
@@ -732,16 +723,13 @@
       <c r="E14" s="0" t="s">
         <v>54</v>
       </c>
-      <c r="F14" s="0" t="s">
-        <v>55</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" s="0" t="s">
         <v>56</v>
-      </c>
-      <c r="B15" s="0" t="s">
-        <v>57</v>
       </c>
       <c r="C15" s="0" t="s">
         <v>13</v>
@@ -758,10 +746,10 @@
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16" s="0" t="s">
         <v>58</v>
-      </c>
-      <c r="B16" s="0" t="s">
-        <v>59</v>
       </c>
       <c r="C16" s="0" t="s">
         <v>13</v>
@@ -770,7 +758,7 @@
         <v>8</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F16" s="0" t="s">
         <v>51</v>
@@ -778,10 +766,10 @@
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" s="0" t="s">
         <v>61</v>
-      </c>
-      <c r="B17" s="0" t="s">
-        <v>62</v>
       </c>
       <c r="C17" s="0" t="s">
         <v>8</v>
@@ -790,18 +778,18 @@
         <v>2</v>
       </c>
       <c r="E17" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="F17" s="0" t="s">
         <v>63</v>
-      </c>
-      <c r="F17" s="0" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" s="0" t="s">
         <v>65</v>
-      </c>
-      <c r="B18" s="0" t="s">
-        <v>66</v>
       </c>
       <c r="C18" s="0" t="s">
         <v>13</v>
@@ -810,18 +798,18 @@
         <v>2</v>
       </c>
       <c r="E18" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="F18" s="0" t="s">
         <v>67</v>
-      </c>
-      <c r="F18" s="0" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="B19" s="0" t="s">
         <v>69</v>
-      </c>
-      <c r="B19" s="0" t="s">
-        <v>70</v>
       </c>
       <c r="C19" s="0" t="s">
         <v>3</v>
@@ -835,47 +823,47 @@
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" s="0" t="s">
         <v>71</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="C20" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="0" t="s">
         <v>72</v>
-      </c>
-      <c r="C20" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D20" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="E20" s="0" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" s="0" t="s">
         <v>74</v>
-      </c>
-      <c r="B21" s="0" t="s">
-        <v>75</v>
       </c>
       <c r="C21" s="0" t="s">
         <v>2</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F21" s="0" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="B22" s="0" t="s">
         <v>76</v>
-      </c>
-      <c r="B22" s="0" t="s">
-        <v>77</v>
       </c>
       <c r="C22" s="0" t="s">
         <v>12</v>
@@ -884,10 +872,10 @@
         <v>3</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F22" s="0" t="s">
-        <v>26</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23">
@@ -898,41 +886,41 @@
         <v>79</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D23" s="0" t="s">
         <v>13</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="F23" s="0" t="s">
-        <v>81</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" s="0" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" s="0" t="s">
         <v>82</v>
-      </c>
-      <c r="B24" s="0" t="s">
-        <v>83</v>
-      </c>
-      <c r="C24" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="E24" s="0" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C25" s="0" t="s">
         <v>12</v>
@@ -941,18 +929,18 @@
         <v>8</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C26" s="0" t="s">
         <v>33</v>
@@ -964,35 +952,35 @@
         <v>29</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C27" s="0" t="s">
         <v>17</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>39</v>
+        <v>92</v>
       </c>
       <c r="F27" s="0" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="B28" s="0" t="s">
         <v>95</v>
-      </c>
-      <c r="B28" s="0" t="s">
-        <v>96</v>
       </c>
       <c r="C28" s="0" t="s">
         <v>12</v>
@@ -1001,7 +989,7 @@
         <v>13</v>
       </c>
       <c r="E28" s="0" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F28" s="0" t="s">
         <v>30</v>
@@ -1009,10 +997,10 @@
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="B29" s="0" t="s">
         <v>98</v>
-      </c>
-      <c r="B29" s="0" t="s">
-        <v>99</v>
       </c>
       <c r="C29" s="0" t="s">
         <v>3</v>
@@ -1021,15 +1009,15 @@
         <v>8</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="B30" s="0" t="s">
         <v>101</v>
-      </c>
-      <c r="B30" s="0" t="s">
-        <v>102</v>
       </c>
       <c r="C30" s="0" t="s">
         <v>12</v>
@@ -1038,15 +1026,15 @@
         <v>8</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
+        <v>103</v>
+      </c>
+      <c r="B31" s="0" t="s">
         <v>104</v>
-      </c>
-      <c r="B31" s="0" t="s">
-        <v>105</v>
       </c>
       <c r="C31" s="0" t="s">
         <v>3</v>
@@ -1055,15 +1043,15 @@
         <v>8</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
+        <v>106</v>
+      </c>
+      <c r="B32" s="0" t="s">
         <v>107</v>
-      </c>
-      <c r="B32" s="0" t="s">
-        <v>108</v>
       </c>
       <c r="C32" s="0" t="s">
         <v>17</v>
@@ -1072,18 +1060,18 @@
         <v>13</v>
       </c>
       <c r="E32" s="0" t="s">
-        <v>109</v>
+        <v>9</v>
       </c>
       <c r="F32" s="0" t="s">
-        <v>110</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C33" s="0" t="s">
         <v>33</v>
@@ -1092,15 +1080,18 @@
         <v>13</v>
       </c>
       <c r="E33" s="0" t="s">
-        <v>113</v>
+        <v>110</v>
+      </c>
+      <c r="F33" s="0" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C34" s="0" t="s">
         <v>3</v>
@@ -1109,38 +1100,35 @@
         <v>8</v>
       </c>
       <c r="E34" s="0" t="s">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="F34" s="0" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C35" s="0" t="s">
         <v>17</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E35" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="F35" s="0" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C36" s="0" t="s">
         <v>38</v>
@@ -1149,35 +1137,38 @@
         <v>3</v>
       </c>
       <c r="E36" s="0" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F36" s="0" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="B37" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="C37" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E37" s="0" t="s">
         <v>123</v>
       </c>
-      <c r="B37" s="0" t="s">
-        <v>124</v>
-      </c>
-      <c r="C37" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D37" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="E37" s="0" t="s">
-        <v>125</v>
+      <c r="F37" s="0" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C38" s="0" t="s">
         <v>38</v>
@@ -1186,15 +1177,18 @@
         <v>3</v>
       </c>
       <c r="E38" s="0" t="s">
-        <v>128</v>
+        <v>126</v>
+      </c>
+      <c r="F38" s="0" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C39" s="0" t="s">
         <v>33</v>
@@ -1206,15 +1200,15 @@
         <v>4</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C40" s="0" t="s">
         <v>33</v>
@@ -1223,7 +1217,7 @@
         <v>3</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resource/MagicFight2/Magic.xlsx
+++ b/Assets/Resource/MagicFight2/Magic.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="129">
   <si>
     <t>a</t>
   </si>
@@ -203,9 +203,6 @@
     <t>&lt;sprite=0&gt;恢复两点生命值，减少一点生命上限</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;若首次使用，连击</t>
-  </si>
-  <si>
     <t>r</t>
   </si>
   <si>
@@ -245,9 +242,6 @@
     <t>藤蔓</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;若这是你的最后三张手牌之一或更少，快速回填×2</t>
-  </si>
-  <si>
     <t>w</t>
   </si>
   <si>
@@ -269,10 +263,7 @@
     <t>瀑流</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;加速一张力量小于等于4的法术</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;可以再打出一张手牌，但其不能造成伤害</t>
+    <t>&lt;sprite=0&gt;加速冷却区中所有 力量小于等于5 的法术，但不能超过两个</t>
   </si>
   <si>
     <t>z</t>
@@ -345,9 +336,6 @@
   </si>
   <si>
     <t>&lt;sprite=0&gt;光环：使法术附带进攻力量+2</t>
-  </si>
-  <si>
-    <t>&lt;sprite=1&gt;防御 力量小于等于4的攻击 时，冷却减1</t>
   </si>
   <si>
     <t>ah</t>
@@ -775,21 +763,21 @@
         <v>8</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E17" s="0" t="s">
         <v>62</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" s="0" t="s">
         <v>64</v>
-      </c>
-      <c r="B18" s="0" t="s">
-        <v>65</v>
       </c>
       <c r="C18" s="0" t="s">
         <v>13</v>
@@ -798,18 +786,18 @@
         <v>2</v>
       </c>
       <c r="E18" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="F18" s="0" t="s">
         <v>66</v>
-      </c>
-      <c r="F18" s="0" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" s="0" t="s">
         <v>68</v>
-      </c>
-      <c r="B19" s="0" t="s">
-        <v>69</v>
       </c>
       <c r="C19" s="0" t="s">
         <v>3</v>
@@ -823,27 +811,30 @@
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" s="0" t="s">
         <v>70</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="C20" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="0" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="E20" s="0" t="s">
-        <v>72</v>
+      <c r="F20" s="0" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" s="0" t="s">
         <v>73</v>
-      </c>
-      <c r="B21" s="0" t="s">
-        <v>74</v>
       </c>
       <c r="C21" s="0" t="s">
         <v>2</v>
@@ -852,7 +843,7 @@
         <v>8</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F21" s="0" t="s">
         <v>39</v>
@@ -860,39 +851,36 @@
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" s="0" t="s">
         <v>75</v>
-      </c>
-      <c r="B22" s="0" t="s">
-        <v>76</v>
       </c>
       <c r="C22" s="0" t="s">
         <v>12</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>72</v>
-      </c>
-      <c r="F22" s="0" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D23" s="0" t="s">
         <v>13</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F23" s="0" t="s">
         <v>4</v>
@@ -900,27 +888,27 @@
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="B24" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="C24" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" s="0" t="s">
         <v>80</v>
-      </c>
-      <c r="B24" s="0" t="s">
-        <v>81</v>
-      </c>
-      <c r="C24" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="E24" s="0" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C25" s="0" t="s">
         <v>12</v>
@@ -929,18 +917,15 @@
         <v>8</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>85</v>
-      </c>
-      <c r="F25" s="0" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C26" s="0" t="s">
         <v>33</v>
@@ -952,15 +937,15 @@
         <v>29</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C27" s="0" t="s">
         <v>17</v>
@@ -969,18 +954,18 @@
         <v>3</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F27" s="0" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C28" s="0" t="s">
         <v>12</v>
@@ -989,7 +974,7 @@
         <v>13</v>
       </c>
       <c r="E28" s="0" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F28" s="0" t="s">
         <v>30</v>
@@ -997,10 +982,10 @@
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C29" s="0" t="s">
         <v>3</v>
@@ -1009,15 +994,15 @@
         <v>8</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C30" s="0" t="s">
         <v>12</v>
@@ -1026,15 +1011,15 @@
         <v>8</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C31" s="0" t="s">
         <v>3</v>
@@ -1043,15 +1028,15 @@
         <v>8</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C32" s="0" t="s">
         <v>17</v>
@@ -1068,10 +1053,10 @@
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C33" s="0" t="s">
         <v>33</v>
@@ -1080,18 +1065,18 @@
         <v>13</v>
       </c>
       <c r="E33" s="0" t="s">
-        <v>110</v>
+        <v>39</v>
       </c>
       <c r="F33" s="0" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C34" s="0" t="s">
         <v>3</v>
@@ -1103,15 +1088,15 @@
         <v>4</v>
       </c>
       <c r="F34" s="0" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C35" s="0" t="s">
         <v>17</v>
@@ -1120,15 +1105,15 @@
         <v>13</v>
       </c>
       <c r="E35" s="0" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C36" s="0" t="s">
         <v>38</v>
@@ -1137,18 +1122,18 @@
         <v>3</v>
       </c>
       <c r="E36" s="0" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F36" s="0" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C37" s="0" t="s">
         <v>13</v>
@@ -1157,7 +1142,7 @@
         <v>3</v>
       </c>
       <c r="E37" s="0" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F37" s="0" t="s">
         <v>26</v>
@@ -1165,10 +1150,10 @@
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C38" s="0" t="s">
         <v>38</v>
@@ -1177,7 +1162,7 @@
         <v>3</v>
       </c>
       <c r="E38" s="0" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F38" s="0" t="s">
         <v>26</v>
@@ -1185,10 +1170,10 @@
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C39" s="0" t="s">
         <v>33</v>
@@ -1200,15 +1185,15 @@
         <v>4</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C40" s="0" t="s">
         <v>33</v>
@@ -1217,7 +1202,7 @@
         <v>3</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resource/MagicFight2/Magic.xlsx
+++ b/Assets/Resource/MagicFight2/Magic.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="128">
   <si>
     <t>a</t>
   </si>
@@ -198,9 +198,6 @@
   </si>
   <si>
     <t>灵魂燃烧</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;恢复两点生命值，减少一点生命上限</t>
   </si>
   <si>
     <t>r</t>
@@ -740,7 +737,7 @@
         <v>58</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D16" s="0" t="s">
         <v>8</v>
@@ -760,13 +757,13 @@
         <v>61</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D17" s="0" t="s">
         <v>8</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F17" s="0" t="s">
         <v>42</v>
@@ -774,10 +771,10 @@
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="B18" s="0" t="s">
         <v>63</v>
-      </c>
-      <c r="B18" s="0" t="s">
-        <v>64</v>
       </c>
       <c r="C18" s="0" t="s">
         <v>13</v>
@@ -786,18 +783,18 @@
         <v>2</v>
       </c>
       <c r="E18" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="F18" s="0" t="s">
         <v>65</v>
-      </c>
-      <c r="F18" s="0" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="B19" s="0" t="s">
         <v>67</v>
-      </c>
-      <c r="B19" s="0" t="s">
-        <v>68</v>
       </c>
       <c r="C19" s="0" t="s">
         <v>3</v>
@@ -811,19 +808,19 @@
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="B20" s="0" t="s">
         <v>69</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="C20" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="0" t="s">
         <v>70</v>
-      </c>
-      <c r="C20" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D20" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="E20" s="0" t="s">
-        <v>71</v>
       </c>
       <c r="F20" s="0" t="s">
         <v>29</v>
@@ -831,10 +828,10 @@
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="B21" s="0" t="s">
         <v>72</v>
-      </c>
-      <c r="B21" s="0" t="s">
-        <v>73</v>
       </c>
       <c r="C21" s="0" t="s">
         <v>2</v>
@@ -843,7 +840,7 @@
         <v>8</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F21" s="0" t="s">
         <v>39</v>
@@ -851,10 +848,10 @@
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" s="0" t="s">
         <v>74</v>
-      </c>
-      <c r="B22" s="0" t="s">
-        <v>75</v>
       </c>
       <c r="C22" s="0" t="s">
         <v>12</v>
@@ -863,16 +860,16 @@
         <v>13</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="B23" s="0" t="s">
         <v>76</v>
       </c>
-      <c r="B23" s="0" t="s">
-        <v>77</v>
-      </c>
       <c r="C23" s="0" t="s">
         <v>3</v>
       </c>
@@ -880,7 +877,7 @@
         <v>13</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F23" s="0" t="s">
         <v>4</v>
@@ -888,27 +885,27 @@
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="B24" s="0" t="s">
         <v>78</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="C24" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" s="0" t="s">
         <v>79</v>
-      </c>
-      <c r="C24" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="E24" s="0" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="B25" s="0" t="s">
         <v>81</v>
-      </c>
-      <c r="B25" s="0" t="s">
-        <v>82</v>
       </c>
       <c r="C25" s="0" t="s">
         <v>12</v>
@@ -917,15 +914,15 @@
         <v>8</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="B26" s="0" t="s">
         <v>84</v>
-      </c>
-      <c r="B26" s="0" t="s">
-        <v>85</v>
       </c>
       <c r="C26" s="0" t="s">
         <v>33</v>
@@ -937,15 +934,15 @@
         <v>29</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="B27" s="0" t="s">
         <v>87</v>
-      </c>
-      <c r="B27" s="0" t="s">
-        <v>88</v>
       </c>
       <c r="C27" s="0" t="s">
         <v>17</v>
@@ -954,18 +951,18 @@
         <v>3</v>
       </c>
       <c r="E27" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="F27" s="0" t="s">
         <v>89</v>
-      </c>
-      <c r="F27" s="0" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="B28" s="0" t="s">
         <v>91</v>
-      </c>
-      <c r="B28" s="0" t="s">
-        <v>92</v>
       </c>
       <c r="C28" s="0" t="s">
         <v>12</v>
@@ -974,7 +971,7 @@
         <v>13</v>
       </c>
       <c r="E28" s="0" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F28" s="0" t="s">
         <v>30</v>
@@ -982,10 +979,10 @@
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="B29" s="0" t="s">
         <v>94</v>
-      </c>
-      <c r="B29" s="0" t="s">
-        <v>95</v>
       </c>
       <c r="C29" s="0" t="s">
         <v>3</v>
@@ -994,15 +991,15 @@
         <v>8</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="B30" s="0" t="s">
         <v>97</v>
-      </c>
-      <c r="B30" s="0" t="s">
-        <v>98</v>
       </c>
       <c r="C30" s="0" t="s">
         <v>12</v>
@@ -1011,15 +1008,15 @@
         <v>8</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="B31" s="0" t="s">
         <v>100</v>
-      </c>
-      <c r="B31" s="0" t="s">
-        <v>101</v>
       </c>
       <c r="C31" s="0" t="s">
         <v>3</v>
@@ -1028,15 +1025,15 @@
         <v>8</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="B32" s="0" t="s">
         <v>103</v>
-      </c>
-      <c r="B32" s="0" t="s">
-        <v>104</v>
       </c>
       <c r="C32" s="0" t="s">
         <v>17</v>
@@ -1053,10 +1050,10 @@
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="B33" s="0" t="s">
         <v>105</v>
-      </c>
-      <c r="B33" s="0" t="s">
-        <v>106</v>
       </c>
       <c r="C33" s="0" t="s">
         <v>33</v>
@@ -1068,15 +1065,15 @@
         <v>39</v>
       </c>
       <c r="F33" s="0" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
+        <v>107</v>
+      </c>
+      <c r="B34" s="0" t="s">
         <v>108</v>
-      </c>
-      <c r="B34" s="0" t="s">
-        <v>109</v>
       </c>
       <c r="C34" s="0" t="s">
         <v>3</v>
@@ -1088,15 +1085,15 @@
         <v>4</v>
       </c>
       <c r="F34" s="0" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
+        <v>110</v>
+      </c>
+      <c r="B35" s="0" t="s">
         <v>111</v>
-      </c>
-      <c r="B35" s="0" t="s">
-        <v>112</v>
       </c>
       <c r="C35" s="0" t="s">
         <v>17</v>
@@ -1105,15 +1102,15 @@
         <v>13</v>
       </c>
       <c r="E35" s="0" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="B36" s="0" t="s">
         <v>114</v>
-      </c>
-      <c r="B36" s="0" t="s">
-        <v>115</v>
       </c>
       <c r="C36" s="0" t="s">
         <v>38</v>
@@ -1122,27 +1119,27 @@
         <v>3</v>
       </c>
       <c r="E36" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F36" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
+        <v>116</v>
+      </c>
+      <c r="B37" s="0" t="s">
         <v>117</v>
       </c>
-      <c r="B37" s="0" t="s">
+      <c r="C37" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E37" s="0" t="s">
         <v>118</v>
-      </c>
-      <c r="C37" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D37" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="E37" s="0" t="s">
-        <v>119</v>
       </c>
       <c r="F37" s="0" t="s">
         <v>26</v>
@@ -1150,10 +1147,10 @@
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
+        <v>119</v>
+      </c>
+      <c r="B38" s="0" t="s">
         <v>120</v>
-      </c>
-      <c r="B38" s="0" t="s">
-        <v>121</v>
       </c>
       <c r="C38" s="0" t="s">
         <v>38</v>
@@ -1162,7 +1159,7 @@
         <v>3</v>
       </c>
       <c r="E38" s="0" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F38" s="0" t="s">
         <v>26</v>
@@ -1170,10 +1167,10 @@
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="B39" s="0" t="s">
         <v>123</v>
-      </c>
-      <c r="B39" s="0" t="s">
-        <v>124</v>
       </c>
       <c r="C39" s="0" t="s">
         <v>33</v>
@@ -1185,15 +1182,15 @@
         <v>4</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
+        <v>125</v>
+      </c>
+      <c r="B40" s="0" t="s">
         <v>126</v>
-      </c>
-      <c r="B40" s="0" t="s">
-        <v>127</v>
       </c>
       <c r="C40" s="0" t="s">
         <v>33</v>
@@ -1202,7 +1199,7 @@
         <v>3</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resource/MagicFight2/Magic.xlsx
+++ b/Assets/Resource/MagicFight2/Magic.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="129">
   <si>
     <t>a</t>
   </si>
@@ -182,24 +182,27 @@
     <t>o</t>
   </si>
   <si>
+    <t>感电</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;若你的冷却区中至少有4张法术，快速回填</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>自燃</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;恢复一点生命值，减少一点生命上限</t>
+  </si>
+  <si>
+    <t>q</t>
+  </si>
+  <si>
     <t>流星</t>
   </si>
   <si>
-    <t>p</t>
-  </si>
-  <si>
-    <t>自燃</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;恢复一点生命值，减少一点生命上限</t>
-  </si>
-  <si>
-    <t>q</t>
-  </si>
-  <si>
-    <t>灵魂燃烧</t>
-  </si>
-  <si>
     <t>r</t>
   </si>
   <si>
@@ -269,7 +272,7 @@
     <t>凝固</t>
   </si>
   <si>
-    <t>&lt;sprite=1&gt;防御时，对方法术的力量值锁定为基础值（效果和光环的加成无效）</t>
+    <t>&lt;sprite=0&gt;快速回填×2</t>
   </si>
   <si>
     <t>aa</t>
@@ -640,7 +643,7 @@
         <v>44</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D11" s="0" t="s">
         <v>13</v>
@@ -723,18 +726,18 @@
         <v>13</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C16" s="0" t="s">
         <v>8</v>
@@ -743,7 +746,7 @@
         <v>8</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F16" s="0" t="s">
         <v>51</v>
@@ -751,30 +754,30 @@
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C18" s="0" t="s">
         <v>13</v>
@@ -783,18 +786,18 @@
         <v>2</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F18" s="0" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C19" s="0" t="s">
         <v>3</v>
@@ -808,10 +811,10 @@
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C20" s="0" t="s">
         <v>13</v>
@@ -820,7 +823,7 @@
         <v>13</v>
       </c>
       <c r="E20" s="0" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F20" s="0" t="s">
         <v>29</v>
@@ -828,10 +831,10 @@
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C21" s="0" t="s">
         <v>2</v>
@@ -840,7 +843,7 @@
         <v>8</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F21" s="0" t="s">
         <v>39</v>
@@ -848,10 +851,10 @@
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C22" s="0" t="s">
         <v>12</v>
@@ -860,15 +863,15 @@
         <v>13</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C23" s="0" t="s">
         <v>3</v>
@@ -877,7 +880,7 @@
         <v>13</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F23" s="0" t="s">
         <v>4</v>
@@ -885,10 +888,10 @@
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C24" s="0" t="s">
         <v>3</v>
@@ -897,15 +900,18 @@
         <v>13</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="F24" s="0" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C25" s="0" t="s">
         <v>12</v>
@@ -914,35 +920,35 @@
         <v>8</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C26" s="0" t="s">
         <v>33</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>29</v>
+        <v>86</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>85</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C27" s="0" t="s">
         <v>17</v>
@@ -951,18 +957,18 @@
         <v>3</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F27" s="0" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C28" s="0" t="s">
         <v>12</v>
@@ -971,18 +977,15 @@
         <v>13</v>
       </c>
       <c r="E28" s="0" t="s">
-        <v>92</v>
-      </c>
-      <c r="F28" s="0" t="s">
-        <v>30</v>
+        <v>93</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C29" s="0" t="s">
         <v>3</v>
@@ -991,15 +994,15 @@
         <v>8</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C30" s="0" t="s">
         <v>12</v>
@@ -1008,15 +1011,15 @@
         <v>8</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C31" s="0" t="s">
         <v>3</v>
@@ -1025,15 +1028,15 @@
         <v>8</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C32" s="0" t="s">
         <v>17</v>
@@ -1050,10 +1053,10 @@
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C33" s="0" t="s">
         <v>33</v>
@@ -1065,15 +1068,15 @@
         <v>39</v>
       </c>
       <c r="F33" s="0" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C34" s="0" t="s">
         <v>3</v>
@@ -1085,15 +1088,15 @@
         <v>4</v>
       </c>
       <c r="F34" s="0" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C35" s="0" t="s">
         <v>17</v>
@@ -1102,15 +1105,15 @@
         <v>13</v>
       </c>
       <c r="E35" s="0" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C36" s="0" t="s">
         <v>38</v>
@@ -1119,18 +1122,18 @@
         <v>3</v>
       </c>
       <c r="E36" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F36" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C37" s="0" t="s">
         <v>13</v>
@@ -1139,7 +1142,7 @@
         <v>3</v>
       </c>
       <c r="E37" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F37" s="0" t="s">
         <v>26</v>
@@ -1147,10 +1150,10 @@
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C38" s="0" t="s">
         <v>38</v>
@@ -1159,7 +1162,7 @@
         <v>3</v>
       </c>
       <c r="E38" s="0" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F38" s="0" t="s">
         <v>26</v>
@@ -1167,10 +1170,10 @@
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C39" s="0" t="s">
         <v>33</v>
@@ -1182,15 +1185,15 @@
         <v>4</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C40" s="0" t="s">
         <v>33</v>
@@ -1199,7 +1202,7 @@
         <v>3</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resource/MagicFight2/Magic.xlsx
+++ b/Assets/Resource/MagicFight2/Magic.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="128">
   <si>
     <t>a</t>
   </si>
@@ -104,9 +104,6 @@
     <t>&lt;sprite=0&gt;快速回填</t>
   </si>
   <si>
-    <t>&lt;sprite=1&gt;连续抵挡</t>
-  </si>
-  <si>
     <t>h</t>
   </si>
   <si>
@@ -182,10 +179,10 @@
     <t>o</t>
   </si>
   <si>
-    <t>感电</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;若你的冷却区中至少有4张法术，快速回填</t>
+    <t>灵魂燃烧</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;恢复一点生命值，减少一点生命上限</t>
   </si>
   <si>
     <t>p</t>
@@ -194,9 +191,6 @@
     <t>自燃</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;恢复一点生命值，减少一点生命上限</t>
-  </si>
-  <si>
     <t>q</t>
   </si>
   <si>
@@ -251,10 +245,13 @@
     <t>x</t>
   </si>
   <si>
-    <t>模仿</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;复制对方冷却区当中的一个 无光环并且力量大于等于5的法术 的效果</t>
+    <t>催化</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;加速，你每损失一点生命值，额外加速一个不同的法术</t>
+  </si>
+  <si>
+    <t>&lt;sprite=1&gt;防御时，冷却减一</t>
   </si>
   <si>
     <t>y</t>
@@ -275,6 +272,9 @@
     <t>&lt;sprite=0&gt;快速回填×2</t>
   </si>
   <si>
+    <t>&lt;sprite=1&gt;防御时，力量+1</t>
+  </si>
+  <si>
     <t>aa</t>
   </si>
   <si>
@@ -282,9 +282,6 @@
   </si>
   <si>
     <t>&lt;sprite=0&gt;对方无法使用光环，并且使其所有光环失效</t>
-  </si>
-  <si>
-    <t>&lt;sprite=1&gt;防御时，力量+3</t>
   </si>
   <si>
     <t>ab</t>
@@ -577,90 +574,87 @@
       <c r="E7" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="0" t="s">
-        <v>30</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="C8" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="D8" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="0" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" s="0" t="s">
+      <c r="F8" s="0" t="s">
         <v>34</v>
-      </c>
-      <c r="F8" s="0" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="C9" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="D9" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="0" t="s">
         <v>38</v>
-      </c>
-      <c r="D9" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" s="0" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="0" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="C10" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="0" t="s">
         <v>41</v>
-      </c>
-      <c r="C10" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="0" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="0" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="C11" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="0" t="s">
-        <v>45</v>
-      </c>
       <c r="F11" s="0" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="0" t="s">
         <v>46</v>
-      </c>
-      <c r="B12" s="0" t="s">
-        <v>47</v>
       </c>
       <c r="C12" s="0" t="s">
         <v>12</v>
@@ -669,18 +663,18 @@
         <v>13</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="0" t="s">
         <v>49</v>
-      </c>
-      <c r="B13" s="0" t="s">
-        <v>50</v>
       </c>
       <c r="C13" s="0" t="s">
         <v>8</v>
@@ -689,18 +683,18 @@
         <v>3</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" s="0" t="s">
         <v>52</v>
-      </c>
-      <c r="B14" s="0" t="s">
-        <v>53</v>
       </c>
       <c r="C14" s="0" t="s">
         <v>17</v>
@@ -709,75 +703,75 @@
         <v>13</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" s="0" t="s">
         <v>55</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="C15" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="0" t="s">
         <v>56</v>
       </c>
-      <c r="C15" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D15" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" s="0" t="s">
-        <v>57</v>
-      </c>
       <c r="F15" s="0" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16" s="0" t="s">
         <v>58</v>
       </c>
-      <c r="B16" s="0" t="s">
-        <v>59</v>
-      </c>
       <c r="C16" s="0" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D16" s="0" t="s">
         <v>8</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E17" s="0" t="s">
         <v>4</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C18" s="0" t="s">
         <v>13</v>
@@ -786,44 +780,44 @@
         <v>2</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F18" s="0" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D19" s="0" t="s">
         <v>8</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="0" t="s">
         <v>69</v>
-      </c>
-      <c r="B20" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="C20" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D20" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="E20" s="0" t="s">
-        <v>71</v>
       </c>
       <c r="F20" s="0" t="s">
         <v>29</v>
@@ -831,10 +825,10 @@
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C21" s="0" t="s">
         <v>2</v>
@@ -843,18 +837,18 @@
         <v>8</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F21" s="0" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C22" s="0" t="s">
         <v>12</v>
@@ -863,15 +857,15 @@
         <v>13</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C23" s="0" t="s">
         <v>3</v>
@@ -880,7 +874,7 @@
         <v>13</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F23" s="0" t="s">
         <v>4</v>
@@ -888,30 +882,30 @@
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="B24" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="C24" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" s="0" t="s">
         <v>78</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="F24" s="0" t="s">
         <v>79</v>
-      </c>
-      <c r="C24" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="E24" s="0" t="s">
-        <v>80</v>
-      </c>
-      <c r="F24" s="0" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="B25" s="0" t="s">
         <v>81</v>
-      </c>
-      <c r="B25" s="0" t="s">
-        <v>82</v>
       </c>
       <c r="C25" s="0" t="s">
         <v>12</v>
@@ -920,27 +914,27 @@
         <v>8</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="B26" s="0" t="s">
         <v>84</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="C26" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="D26" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E26" s="0" t="s">
         <v>85</v>
       </c>
-      <c r="C26" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="D26" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="E26" s="0" t="s">
+      <c r="F26" s="0" t="s">
         <v>86</v>
-      </c>
-      <c r="F26" s="0" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="27">
@@ -960,15 +954,15 @@
         <v>89</v>
       </c>
       <c r="F27" s="0" t="s">
-        <v>90</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="B28" s="0" t="s">
         <v>91</v>
-      </c>
-      <c r="B28" s="0" t="s">
-        <v>92</v>
       </c>
       <c r="C28" s="0" t="s">
         <v>12</v>
@@ -977,15 +971,15 @@
         <v>13</v>
       </c>
       <c r="E28" s="0" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="B29" s="0" t="s">
         <v>94</v>
-      </c>
-      <c r="B29" s="0" t="s">
-        <v>95</v>
       </c>
       <c r="C29" s="0" t="s">
         <v>3</v>
@@ -994,15 +988,15 @@
         <v>8</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="B30" s="0" t="s">
         <v>97</v>
-      </c>
-      <c r="B30" s="0" t="s">
-        <v>98</v>
       </c>
       <c r="C30" s="0" t="s">
         <v>12</v>
@@ -1011,15 +1005,15 @@
         <v>8</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="B31" s="0" t="s">
         <v>100</v>
-      </c>
-      <c r="B31" s="0" t="s">
-        <v>101</v>
       </c>
       <c r="C31" s="0" t="s">
         <v>3</v>
@@ -1028,15 +1022,15 @@
         <v>8</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="B32" s="0" t="s">
         <v>103</v>
-      </c>
-      <c r="B32" s="0" t="s">
-        <v>104</v>
       </c>
       <c r="C32" s="0" t="s">
         <v>17</v>
@@ -1053,30 +1047,30 @@
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="B33" s="0" t="s">
         <v>105</v>
       </c>
-      <c r="B33" s="0" t="s">
+      <c r="C33" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="D33" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="F33" s="0" t="s">
         <v>106</v>
-      </c>
-      <c r="C33" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="D33" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="E33" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="F33" s="0" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
+        <v>107</v>
+      </c>
+      <c r="B34" s="0" t="s">
         <v>108</v>
-      </c>
-      <c r="B34" s="0" t="s">
-        <v>109</v>
       </c>
       <c r="C34" s="0" t="s">
         <v>3</v>
@@ -1088,15 +1082,15 @@
         <v>4</v>
       </c>
       <c r="F34" s="0" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
+        <v>110</v>
+      </c>
+      <c r="B35" s="0" t="s">
         <v>111</v>
-      </c>
-      <c r="B35" s="0" t="s">
-        <v>112</v>
       </c>
       <c r="C35" s="0" t="s">
         <v>17</v>
@@ -1105,44 +1099,44 @@
         <v>13</v>
       </c>
       <c r="E35" s="0" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="B36" s="0" t="s">
         <v>114</v>
       </c>
-      <c r="B36" s="0" t="s">
+      <c r="C36" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="D36" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E36" s="0" t="s">
         <v>115</v>
       </c>
-      <c r="C36" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="D36" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="E36" s="0" t="s">
-        <v>116</v>
-      </c>
       <c r="F36" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
+        <v>116</v>
+      </c>
+      <c r="B37" s="0" t="s">
         <v>117</v>
       </c>
-      <c r="B37" s="0" t="s">
+      <c r="C37" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E37" s="0" t="s">
         <v>118</v>
-      </c>
-      <c r="C37" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D37" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="E37" s="0" t="s">
-        <v>119</v>
       </c>
       <c r="F37" s="0" t="s">
         <v>26</v>
@@ -1150,19 +1144,19 @@
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
+        <v>119</v>
+      </c>
+      <c r="B38" s="0" t="s">
         <v>120</v>
       </c>
-      <c r="B38" s="0" t="s">
+      <c r="C38" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="D38" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E38" s="0" t="s">
         <v>121</v>
-      </c>
-      <c r="C38" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="D38" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="E38" s="0" t="s">
-        <v>122</v>
       </c>
       <c r="F38" s="0" t="s">
         <v>26</v>
@@ -1170,13 +1164,13 @@
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="B39" s="0" t="s">
         <v>123</v>
       </c>
-      <c r="B39" s="0" t="s">
-        <v>124</v>
-      </c>
       <c r="C39" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D39" s="0" t="s">
         <v>13</v>
@@ -1185,24 +1179,24 @@
         <v>4</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
+        <v>125</v>
+      </c>
+      <c r="B40" s="0" t="s">
         <v>126</v>
       </c>
-      <c r="B40" s="0" t="s">
+      <c r="C40" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="D40" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E40" s="0" t="s">
         <v>127</v>
-      </c>
-      <c r="C40" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="D40" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="E40" s="0" t="s">
-        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resource/MagicFight2/Magic.xlsx
+++ b/Assets/Resource/MagicFight2/Magic.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="127">
   <si>
     <t>a</t>
   </si>
@@ -267,9 +267,6 @@
   </si>
   <si>
     <t>凝固</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;快速回填×2</t>
   </si>
   <si>
     <t>&lt;sprite=1&gt;防御时，力量+1</t>
@@ -928,21 +925,21 @@
         <v>32</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E26" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F26" s="0" t="s">
         <v>85</v>
-      </c>
-      <c r="F26" s="0" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="B27" s="0" t="s">
         <v>87</v>
-      </c>
-      <c r="B27" s="0" t="s">
-        <v>88</v>
       </c>
       <c r="C27" s="0" t="s">
         <v>17</v>
@@ -951,7 +948,7 @@
         <v>3</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F27" s="0" t="s">
         <v>26</v>
@@ -959,10 +956,10 @@
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="B28" s="0" t="s">
         <v>90</v>
-      </c>
-      <c r="B28" s="0" t="s">
-        <v>91</v>
       </c>
       <c r="C28" s="0" t="s">
         <v>12</v>
@@ -971,15 +968,15 @@
         <v>13</v>
       </c>
       <c r="E28" s="0" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="B29" s="0" t="s">
         <v>93</v>
-      </c>
-      <c r="B29" s="0" t="s">
-        <v>94</v>
       </c>
       <c r="C29" s="0" t="s">
         <v>3</v>
@@ -988,15 +985,15 @@
         <v>8</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="B30" s="0" t="s">
         <v>96</v>
-      </c>
-      <c r="B30" s="0" t="s">
-        <v>97</v>
       </c>
       <c r="C30" s="0" t="s">
         <v>12</v>
@@ -1005,15 +1002,15 @@
         <v>8</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
+        <v>98</v>
+      </c>
+      <c r="B31" s="0" t="s">
         <v>99</v>
-      </c>
-      <c r="B31" s="0" t="s">
-        <v>100</v>
       </c>
       <c r="C31" s="0" t="s">
         <v>3</v>
@@ -1022,15 +1019,15 @@
         <v>8</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="B32" s="0" t="s">
         <v>102</v>
-      </c>
-      <c r="B32" s="0" t="s">
-        <v>103</v>
       </c>
       <c r="C32" s="0" t="s">
         <v>17</v>
@@ -1047,10 +1044,10 @@
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
+        <v>103</v>
+      </c>
+      <c r="B33" s="0" t="s">
         <v>104</v>
-      </c>
-      <c r="B33" s="0" t="s">
-        <v>105</v>
       </c>
       <c r="C33" s="0" t="s">
         <v>32</v>
@@ -1062,15 +1059,15 @@
         <v>38</v>
       </c>
       <c r="F33" s="0" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
+        <v>106</v>
+      </c>
+      <c r="B34" s="0" t="s">
         <v>107</v>
-      </c>
-      <c r="B34" s="0" t="s">
-        <v>108</v>
       </c>
       <c r="C34" s="0" t="s">
         <v>3</v>
@@ -1082,15 +1079,15 @@
         <v>4</v>
       </c>
       <c r="F34" s="0" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
+        <v>109</v>
+      </c>
+      <c r="B35" s="0" t="s">
         <v>110</v>
-      </c>
-      <c r="B35" s="0" t="s">
-        <v>111</v>
       </c>
       <c r="C35" s="0" t="s">
         <v>17</v>
@@ -1099,15 +1096,15 @@
         <v>13</v>
       </c>
       <c r="E35" s="0" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="B36" s="0" t="s">
         <v>113</v>
-      </c>
-      <c r="B36" s="0" t="s">
-        <v>114</v>
       </c>
       <c r="C36" s="0" t="s">
         <v>37</v>
@@ -1116,27 +1113,27 @@
         <v>3</v>
       </c>
       <c r="E36" s="0" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F36" s="0" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
+        <v>115</v>
+      </c>
+      <c r="B37" s="0" t="s">
         <v>116</v>
       </c>
-      <c r="B37" s="0" t="s">
+      <c r="C37" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E37" s="0" t="s">
         <v>117</v>
-      </c>
-      <c r="C37" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D37" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="E37" s="0" t="s">
-        <v>118</v>
       </c>
       <c r="F37" s="0" t="s">
         <v>26</v>
@@ -1144,10 +1141,10 @@
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
+        <v>118</v>
+      </c>
+      <c r="B38" s="0" t="s">
         <v>119</v>
-      </c>
-      <c r="B38" s="0" t="s">
-        <v>120</v>
       </c>
       <c r="C38" s="0" t="s">
         <v>37</v>
@@ -1156,7 +1153,7 @@
         <v>3</v>
       </c>
       <c r="E38" s="0" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F38" s="0" t="s">
         <v>26</v>
@@ -1164,10 +1161,10 @@
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="B39" s="0" t="s">
         <v>122</v>
-      </c>
-      <c r="B39" s="0" t="s">
-        <v>123</v>
       </c>
       <c r="C39" s="0" t="s">
         <v>32</v>
@@ -1179,15 +1176,15 @@
         <v>4</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="B40" s="0" t="s">
         <v>125</v>
-      </c>
-      <c r="B40" s="0" t="s">
-        <v>126</v>
       </c>
       <c r="C40" s="0" t="s">
         <v>32</v>
@@ -1196,7 +1193,7 @@
         <v>3</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resource/MagicFight2/Magic.xlsx
+++ b/Assets/Resource/MagicFight2/Magic.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="151">
   <si>
     <t>a</t>
   </si>
@@ -393,6 +393,78 @@
   </si>
   <si>
     <t>&lt;sprite=0&gt;使自己和对方的 冷却区中剩余冷却为1的法术 都被减速</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>回响</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;光环：使法术的基础效果触发两次（双发、连击、光环、形态等无法叠加，光环、形态的附加效果不会双倍生效）</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>深渊吐息</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;可以移除一张手牌，然后再随机抽一张法术，新获得的法术将会立即进入冷却，并且剩余冷却时间为1</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>雷龙</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;形态：你的所有法术都额外获得连击，但是进攻时冷却加1（冷却最多为4），并且攻击造成伤害后无法再出牌[强制]</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>海妖</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;形态：轮到你进攻时，所有法术的剩余冷却从减1改为减2（除了此法术），但是你的所有法术防御力量减2（力量最低为1）[强制]</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>石头人</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;形态：攻击你的法术的所有效果失效（只有基础攻击力），但是你在防御前无法看到对方的法术，出牌防御失败也会进入冷却[强制]</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>雪怪</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;形态：你的所有法术都获得减速×2，但是要选择你的冷却区中的一张法术翻面（其冷却时间不能改变，直到形态结束翻回）[强制]</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>恶魔</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;形态：你的所有法术造成伤害时，都会额外增加一点伤害，并且防御力量+1，但是你受到法术伤害时，伤害也会增加一点[强制]</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>火鬼</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;形态：你的所有法术都获得进攻时力量+2，但进攻时无法看见手牌，只能从中随机抽牌打出[强制]</t>
   </si>
 </sst>
 </file>
@@ -438,7 +510,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1196,6 +1268,142 @@
         <v>126</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="0" t="s">
+        <v>127</v>
+      </c>
+      <c r="B41" s="0" t="s">
+        <v>128</v>
+      </c>
+      <c r="C41" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="D41" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E41" s="0" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="0" t="s">
+        <v>130</v>
+      </c>
+      <c r="B42" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="C42" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D42" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E42" s="0" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="0" t="s">
+        <v>133</v>
+      </c>
+      <c r="B43" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="C43" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="0" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="B44" s="0" t="s">
+        <v>137</v>
+      </c>
+      <c r="C44" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="D44" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="0" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="B45" s="0" t="s">
+        <v>140</v>
+      </c>
+      <c r="C45" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="D45" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="0" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="0" t="s">
+        <v>142</v>
+      </c>
+      <c r="B46" s="0" t="s">
+        <v>143</v>
+      </c>
+      <c r="C46" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="D46" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E46" s="0" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="0" t="s">
+        <v>145</v>
+      </c>
+      <c r="B47" s="0" t="s">
+        <v>146</v>
+      </c>
+      <c r="C47" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="D47" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="0" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="0" t="s">
+        <v>148</v>
+      </c>
+      <c r="B48" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="C48" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="D48" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E48" s="0" t="s">
+        <v>150</v>
+      </c>
+    </row>
   </sheetData>
   <headerFooter/>
 </worksheet>

--- a/Assets/Resource/MagicFight2/Magic.xlsx
+++ b/Assets/Resource/MagicFight2/Magic.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="150">
   <si>
     <t>a</t>
   </si>
@@ -182,7 +182,7 @@
     <t>灵魂燃烧</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;恢复一点生命值，减少一点生命上限</t>
+    <t>&lt;sprite=0&gt;恢复一点生命值，减少一点生命上限[强制]</t>
   </si>
   <si>
     <t>p</t>
@@ -245,13 +245,10 @@
     <t>x</t>
   </si>
   <si>
-    <t>催化</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;加速，你每损失一点生命值，额外加速一个不同的法术</t>
-  </si>
-  <si>
-    <t>&lt;sprite=1&gt;防御时，冷却减一</t>
+    <t>模仿</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;复制你的冷却区中的一个 力量大于等于5的法术 的效果，若被模仿的法术具有光环，则激活光环</t>
   </si>
   <si>
     <t>y</t>
@@ -260,7 +257,7 @@
     <t>瀑流</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;加速冷却区中所有 力量小于等于5 的法术，但不能超过两个</t>
+    <t>&lt;sprite=0&gt;你每损失一点生命值，额外加速一个不同的法术</t>
   </si>
   <si>
     <t>z</t>
@@ -275,10 +272,10 @@
     <t>aa</t>
   </si>
   <si>
-    <t>大火球</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;对方无法使用光环，并且使其所有光环失效</t>
+    <t>水镜</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;交换你的两个冷却区中的所有法术</t>
   </si>
   <si>
     <t>ab</t>
@@ -335,10 +332,10 @@
     <t>ah</t>
   </si>
   <si>
-    <t>烈焰斗篷</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;光环：使法术附带进攻力量+2或防御力量+2</t>
+    <t>蒸汽锅炉</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;光环：使法术附带进攻力量+3或防御力量+3</t>
   </si>
   <si>
     <t>‌ai</t>
@@ -392,7 +389,7 @@
     <t>地震</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;使自己和对方的 冷却区中剩余冷却为1的法术 都被减速</t>
+    <t>&lt;sprite=0&gt;使自己和对方的 冷却区中剩余冷却为1的法术 都被减速[强制]</t>
   </si>
   <si>
     <t>41</t>
@@ -965,33 +962,33 @@
       <c r="E24" s="0" t="s">
         <v>78</v>
       </c>
-      <c r="F24" s="0" t="s">
-        <v>79</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="B25" s="0" t="s">
         <v>80</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="C25" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="F25" s="0" t="s">
         <v>81</v>
-      </c>
-      <c r="C25" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="D25" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" s="0" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" s="0" t="s">
         <v>83</v>
-      </c>
-      <c r="B26" s="0" t="s">
-        <v>84</v>
       </c>
       <c r="C26" s="0" t="s">
         <v>32</v>
@@ -1003,35 +1000,32 @@
         <v>29</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="B27" s="0" t="s">
         <v>86</v>
       </c>
-      <c r="B27" s="0" t="s">
+      <c r="C27" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="0" t="s">
         <v>87</v>
-      </c>
-      <c r="C27" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D27" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="E27" s="0" t="s">
-        <v>88</v>
-      </c>
-      <c r="F27" s="0" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="B28" s="0" t="s">
         <v>89</v>
-      </c>
-      <c r="B28" s="0" t="s">
-        <v>90</v>
       </c>
       <c r="C28" s="0" t="s">
         <v>12</v>
@@ -1040,15 +1034,15 @@
         <v>13</v>
       </c>
       <c r="E28" s="0" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="B29" s="0" t="s">
         <v>92</v>
-      </c>
-      <c r="B29" s="0" t="s">
-        <v>93</v>
       </c>
       <c r="C29" s="0" t="s">
         <v>3</v>
@@ -1057,15 +1051,15 @@
         <v>8</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="B30" s="0" t="s">
         <v>95</v>
-      </c>
-      <c r="B30" s="0" t="s">
-        <v>96</v>
       </c>
       <c r="C30" s="0" t="s">
         <v>12</v>
@@ -1074,15 +1068,15 @@
         <v>8</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="B31" s="0" t="s">
         <v>98</v>
-      </c>
-      <c r="B31" s="0" t="s">
-        <v>99</v>
       </c>
       <c r="C31" s="0" t="s">
         <v>3</v>
@@ -1091,15 +1085,15 @@
         <v>8</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="B32" s="0" t="s">
         <v>101</v>
-      </c>
-      <c r="B32" s="0" t="s">
-        <v>102</v>
       </c>
       <c r="C32" s="0" t="s">
         <v>17</v>
@@ -1116,10 +1110,10 @@
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="B33" s="0" t="s">
         <v>103</v>
-      </c>
-      <c r="B33" s="0" t="s">
-        <v>104</v>
       </c>
       <c r="C33" s="0" t="s">
         <v>32</v>
@@ -1131,35 +1125,35 @@
         <v>38</v>
       </c>
       <c r="F33" s="0" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
+        <v>105</v>
+      </c>
+      <c r="B34" s="0" t="s">
         <v>106</v>
       </c>
-      <c r="B34" s="0" t="s">
-        <v>107</v>
-      </c>
       <c r="C34" s="0" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E34" s="0" t="s">
         <v>4</v>
       </c>
       <c r="F34" s="0" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
+        <v>108</v>
+      </c>
+      <c r="B35" s="0" t="s">
         <v>109</v>
-      </c>
-      <c r="B35" s="0" t="s">
-        <v>110</v>
       </c>
       <c r="C35" s="0" t="s">
         <v>17</v>
@@ -1168,15 +1162,15 @@
         <v>13</v>
       </c>
       <c r="E35" s="0" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
+        <v>111</v>
+      </c>
+      <c r="B36" s="0" t="s">
         <v>112</v>
-      </c>
-      <c r="B36" s="0" t="s">
-        <v>113</v>
       </c>
       <c r="C36" s="0" t="s">
         <v>37</v>
@@ -1185,27 +1179,27 @@
         <v>3</v>
       </c>
       <c r="E36" s="0" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F36" s="0" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
+        <v>114</v>
+      </c>
+      <c r="B37" s="0" t="s">
         <v>115</v>
       </c>
-      <c r="B37" s="0" t="s">
+      <c r="C37" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E37" s="0" t="s">
         <v>116</v>
-      </c>
-      <c r="C37" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D37" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="E37" s="0" t="s">
-        <v>117</v>
       </c>
       <c r="F37" s="0" t="s">
         <v>26</v>
@@ -1213,10 +1207,10 @@
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="B38" s="0" t="s">
         <v>118</v>
-      </c>
-      <c r="B38" s="0" t="s">
-        <v>119</v>
       </c>
       <c r="C38" s="0" t="s">
         <v>37</v>
@@ -1225,7 +1219,7 @@
         <v>3</v>
       </c>
       <c r="E38" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F38" s="0" t="s">
         <v>26</v>
@@ -1233,10 +1227,10 @@
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
+        <v>120</v>
+      </c>
+      <c r="B39" s="0" t="s">
         <v>121</v>
-      </c>
-      <c r="B39" s="0" t="s">
-        <v>122</v>
       </c>
       <c r="C39" s="0" t="s">
         <v>32</v>
@@ -1248,15 +1242,15 @@
         <v>4</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="B40" s="0" t="s">
         <v>124</v>
-      </c>
-      <c r="B40" s="0" t="s">
-        <v>125</v>
       </c>
       <c r="C40" s="0" t="s">
         <v>32</v>
@@ -1265,15 +1259,15 @@
         <v>3</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="B41" s="0" t="s">
         <v>127</v>
-      </c>
-      <c r="B41" s="0" t="s">
-        <v>128</v>
       </c>
       <c r="C41" s="0" t="s">
         <v>32</v>
@@ -1282,15 +1276,15 @@
         <v>3</v>
       </c>
       <c r="E41" s="0" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="s">
+        <v>129</v>
+      </c>
+      <c r="B42" s="0" t="s">
         <v>130</v>
-      </c>
-      <c r="B42" s="0" t="s">
-        <v>131</v>
       </c>
       <c r="C42" s="0" t="s">
         <v>25</v>
@@ -1299,15 +1293,15 @@
         <v>3</v>
       </c>
       <c r="E42" s="0" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="B43" s="0" t="s">
         <v>133</v>
-      </c>
-      <c r="B43" s="0" t="s">
-        <v>134</v>
       </c>
       <c r="C43" s="0" t="s">
         <v>8</v>
@@ -1316,32 +1310,32 @@
         <v>3</v>
       </c>
       <c r="E43" s="0" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="B44" s="0" t="s">
         <v>136</v>
       </c>
-      <c r="B44" s="0" t="s">
+      <c r="C44" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="D44" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="0" t="s">
         <v>137</v>
-      </c>
-      <c r="C44" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D44" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="E44" s="0" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="B45" s="0" t="s">
         <v>139</v>
-      </c>
-      <c r="B45" s="0" t="s">
-        <v>140</v>
       </c>
       <c r="C45" s="0" t="s">
         <v>12</v>
@@ -1350,32 +1344,32 @@
         <v>3</v>
       </c>
       <c r="E45" s="0" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="s">
+        <v>141</v>
+      </c>
+      <c r="B46" s="0" t="s">
         <v>142</v>
       </c>
-      <c r="B46" s="0" t="s">
+      <c r="C46" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="D46" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E46" s="0" t="s">
         <v>143</v>
-      </c>
-      <c r="C46" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="D46" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="E46" s="0" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="s">
+        <v>144</v>
+      </c>
+      <c r="B47" s="0" t="s">
         <v>145</v>
-      </c>
-      <c r="B47" s="0" t="s">
-        <v>146</v>
       </c>
       <c r="C47" s="0" t="s">
         <v>17</v>
@@ -1384,15 +1378,15 @@
         <v>3</v>
       </c>
       <c r="E47" s="0" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="B48" s="0" t="s">
         <v>148</v>
-      </c>
-      <c r="B48" s="0" t="s">
-        <v>149</v>
       </c>
       <c r="C48" s="0" t="s">
         <v>37</v>
@@ -1401,7 +1395,7 @@
         <v>3</v>
       </c>
       <c r="E48" s="0" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resource/MagicFight2/Magic.xlsx
+++ b/Assets/Resource/MagicFight2/Magic.xlsx
@@ -275,7 +275,7 @@
     <t>水镜</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;交换你的两个冷却区中的所有法术</t>
+    <t>&lt;sprite=0&gt;可以交换你的两个冷却区中的所有法术</t>
   </si>
   <si>
     <t>ab</t>
@@ -398,7 +398,7 @@
     <t>回响</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;光环：使法术的基础效果触发两次（双发、连击、光环、形态等无法叠加，光环、形态的附加效果不会双倍生效）</t>
+    <t>&lt;sprite=0&gt;光环：使法术的基础效果触发两次（双发、连击、光环、形态等无法叠加，光环、形态的附加效果不会二次触发）</t>
   </si>
   <si>
     <t>42</t>
@@ -443,7 +443,7 @@
     <t>雪怪</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;形态：你的所有法术都获得减速×2，但是要选择你的冷却区中的一张法术翻面（其冷却时间不能改变，直到形态结束翻回）[强制]</t>
+    <t>&lt;sprite=0&gt;形态：你的所有法术额外拥有减速×2，但需要将你的冷却区中的一张法术翻面（冷却时间不能改变，直到形态结束翻回）[强制]</t>
   </si>
   <si>
     <t>47</t>
@@ -1019,6 +1019,9 @@
       <c r="E27" s="0" t="s">
         <v>87</v>
       </c>
+      <c r="F27" s="0" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">

--- a/Assets/Resource/MagicFight2/Magic.xlsx
+++ b/Assets/Resource/MagicFight2/Magic.xlsx
@@ -275,7 +275,7 @@
     <t>水镜</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;可以交换你的两个冷却区中的所有法术</t>
+    <t>&lt;sprite=0&gt;可以交换你的两个冷却区中的所有法术（另一个冷却区可以是空的）</t>
   </si>
   <si>
     <t>ab</t>
@@ -416,7 +416,7 @@
     <t>雷龙</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;形态：你的所有法术都额外获得连击，但是进攻时冷却加1（冷却最多为4），并且攻击造成伤害后无法再出牌[强制]</t>
+    <t>&lt;sprite=0&gt;形态：你的所有法术都拥有连击（除了此法术），但是进攻时冷却+1（冷却最多为4），并且造成伤害后本回合无法再出牌[强制]</t>
   </si>
   <si>
     <t>44</t>

--- a/Assets/Resource/MagicFight2/Magic.xlsx
+++ b/Assets/Resource/MagicFight2/Magic.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="163">
   <si>
     <t>a</t>
   </si>
@@ -71,7 +71,7 @@
     <t>&lt;sprite=0&gt;重置对方一个法术的冷却时间</t>
   </si>
   <si>
-    <t>e</t>
+    <t>‌e</t>
   </si>
   <si>
     <t>潮汐</t>
@@ -80,7 +80,7 @@
     <t>&lt;sprite=0&gt;光环：使一个法术立即冷却完毕</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;此光环仅能在 轮到你进攻并且出牌之前 使用</t>
+    <t>&lt;sprite=0&gt;此光环仅能在 你的进攻回合内 使用</t>
   </si>
   <si>
     <t>f</t>
@@ -119,10 +119,10 @@
     <t>&lt;sprite=0&gt;此法术的进攻力量不能增加</t>
   </si>
   <si>
-    <t>i</t>
-  </si>
-  <si>
-    <t>沙流</t>
+    <t>‌i</t>
+  </si>
+  <si>
+    <t>地震</t>
   </si>
   <si>
     <t>8</t>
@@ -140,10 +140,10 @@
     <t>&lt;sprite=0&gt;连击</t>
   </si>
   <si>
-    <t>k</t>
-  </si>
-  <si>
-    <t>电场</t>
+    <t>‌k</t>
+  </si>
+  <si>
+    <t>电弧</t>
   </si>
   <si>
     <t>&lt;sprite=0&gt;随机查看对方一张手牌，力量大于等于7则立即进入冷却</t>
@@ -176,10 +176,10 @@
     <t>&lt;sprite=0&gt;光环：使你的基础力量小于等于4的法术获得连击（不能叠加）</t>
   </si>
   <si>
-    <t>o</t>
-  </si>
-  <si>
-    <t>灵魂燃烧</t>
+    <t>‌o</t>
+  </si>
+  <si>
+    <t>过载</t>
   </si>
   <si>
     <t>&lt;sprite=0&gt;恢复一点生命值，减少一点生命上限[强制]</t>
@@ -191,10 +191,10 @@
     <t>自燃</t>
   </si>
   <si>
-    <t>q</t>
-  </si>
-  <si>
-    <t>流星</t>
+    <t>‌q</t>
+  </si>
+  <si>
+    <t>海涌</t>
   </si>
   <si>
     <t>r</t>
@@ -230,7 +230,7 @@
     <t>飞叶连击</t>
   </si>
   <si>
-    <t>v</t>
+    <t>‌v</t>
   </si>
   <si>
     <t>藤蔓</t>
@@ -248,7 +248,7 @@
     <t>模仿</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;复制你的冷却区中的一个 力量大于等于5的法术 的效果，若被模仿的法术具有光环，则激活光环</t>
+    <t>复制你的冷却区中的一个 力量大于等于5的法术 的效果，若被模仿的法术具有光环，则激活光环</t>
   </si>
   <si>
     <t>y</t>
@@ -260,10 +260,10 @@
     <t>&lt;sprite=0&gt;你每损失一点生命值，额外加速一个不同的法术</t>
   </si>
   <si>
-    <t>z</t>
-  </si>
-  <si>
-    <t>凝固</t>
+    <t>‌z</t>
+  </si>
+  <si>
+    <t>地动波</t>
   </si>
   <si>
     <t>&lt;sprite=1&gt;防御时，力量+1</t>
@@ -272,7 +272,7 @@
     <t>aa</t>
   </si>
   <si>
-    <t>水镜</t>
+    <t>漩涡</t>
   </si>
   <si>
     <t>&lt;sprite=0&gt;可以交换你的两个冷却区中的所有法术（另一个冷却区可以是空的）</t>
@@ -305,10 +305,10 @@
     <t>&lt;sprite=0&gt;随机查看对方一张手牌，力量小于等于4则立即进入冷却，冷却时间至少为3</t>
   </si>
   <si>
-    <t>ae</t>
-  </si>
-  <si>
-    <t>地波</t>
+    <t>‌ae</t>
+  </si>
+  <si>
+    <t>灼烧</t>
   </si>
   <si>
     <t>&lt;sprite=0&gt;你或对方每损失一点生命值（相较初始值），都会进攻力量+1</t>
@@ -320,6 +320,9 @@
     <t>冰封铠甲</t>
   </si>
   <si>
+    <t>&lt;sprite=0&gt;光环：使法术附带防御力量+2</t>
+  </si>
+  <si>
     <t>ag</t>
   </si>
   <si>
@@ -329,16 +332,16 @@
     <t>&lt;sprite=0&gt;光环：使法术附带进攻力量+2</t>
   </si>
   <si>
-    <t>ah</t>
-  </si>
-  <si>
-    <t>蒸汽锅炉</t>
+    <t>‌ah</t>
+  </si>
+  <si>
+    <t>烈焰斗篷</t>
   </si>
   <si>
     <t>&lt;sprite=0&gt;光环：使法术附带进攻力量+3或防御力量+3</t>
   </si>
   <si>
-    <t>‌ai</t>
+    <t>ai</t>
   </si>
   <si>
     <t>爆燃</t>
@@ -374,7 +377,7 @@
     <t>&lt;sprite=0&gt;光环：免疫力量小于等于3的攻击（包括双发）</t>
   </si>
   <si>
-    <t>‌am</t>
+    <t>am</t>
   </si>
   <si>
     <t>充能</t>
@@ -383,85 +386,121 @@
     <t>&lt;sprite=0&gt;攻击时可以将手中其它法术进入冷却，每冷却一张获得一次加速</t>
   </si>
   <si>
-    <t>an</t>
-  </si>
-  <si>
-    <t>地震</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;使自己和对方的 冷却区中剩余冷却为1的法术 都被减速[强制]</t>
+    <t>‌an</t>
+  </si>
+  <si>
+    <t>雪崩</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;使自己和对方的 冷却区中剩余冷却为1的法术 都被减速[强制]</t>
   </si>
   <si>
     <t>41</t>
   </si>
   <si>
-    <t>回响</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;光环：使法术的基础效果触发两次（双发、连击、光环、形态等无法叠加，光环、形态的附加效果不会二次触发）</t>
+    <t>电</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;形态：你的所有法术都拥有连击（除了此法术），但是进攻时冷却+1（最多为4），并且造成伤害后本回合无法再出牌[强制]</t>
   </si>
   <si>
     <t>42</t>
   </si>
   <si>
-    <t>深渊吐息</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;可以移除一张手牌，然后再随机抽一张法术，新获得的法术将会立即进入冷却，并且剩余冷却时间为1</t>
+    <t>水</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;形态：轮到你进攻时，所有法术的剩余冷却从减1改为减2（除了此法术），但是你所有法术的防御力量减1（力量最低为1）[强制]</t>
   </si>
   <si>
     <t>43</t>
   </si>
   <si>
-    <t>雷龙</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;形态：你的所有法术都拥有连击（除了此法术），但是进攻时冷却+1（冷却最多为4），并且造成伤害后本回合无法再出牌[强制]</t>
+    <t>石</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;形态：攻击你的法术的所有效果失效（只有基础攻击力），但是你在防御前无法看到对方的法术，出牌防御失败也会进入冷却[强制]</t>
   </si>
   <si>
     <t>44</t>
   </si>
   <si>
-    <t>海妖</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;形态：轮到你进攻时，所有法术的剩余冷却从减1改为减2（除了此法术），但是你的所有法术防御力量减2（力量最低为1）[强制]</t>
+    <t>冰</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;形态：你的所有法术额外拥有减速（除了此法术）</t>
   </si>
   <si>
     <t>45</t>
   </si>
   <si>
-    <t>石头人</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;形态：攻击你的法术的所有效果失效（只有基础攻击力），但是你在防御前无法看到对方的法术，出牌防御失败也会进入冷却[强制]</t>
+    <t>草</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;形态：当你的法术攻击造成伤害时，你恢复一点生命值（除了此法术）</t>
   </si>
   <si>
     <t>46</t>
   </si>
   <si>
-    <t>雪怪</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;形态：你的所有法术额外拥有减速×2，但需要将你的冷却区中的一张法术翻面（冷却时间不能改变，直到形态结束翻回）[强制]</t>
+    <t>火</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;形态：你的所有法术都获得进攻时力量+2，但进攻时无法看见手牌，只能从中随机抽牌打出[强制]</t>
   </si>
   <si>
     <t>47</t>
   </si>
   <si>
-    <t>恶魔</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;形态：你的所有法术造成伤害时，都会额外增加一点伤害，并且防御力量+1，但是你受到法术伤害时，伤害也会增加一点[强制]</t>
+    <t>次声波</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;强化×2</t>
+  </si>
+  <si>
+    <t>&lt;sprite=1&gt;强化</t>
   </si>
   <si>
     <t>48</t>
   </si>
   <si>
-    <t>火鬼</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;形态：你的所有法术都获得进攻时力量+2，但进攻时无法看见手牌，只能从中随机抽牌打出[强制]</t>
+    <t>共鸣</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;强化</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;光环：法术额外附带进攻力量+（当前强化值）</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>回声</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>飓风</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;备用法术</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>风暴吐息</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;备用法术×2</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>空袭</t>
   </si>
 </sst>
 </file>
@@ -507,7 +546,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -703,7 +742,7 @@
         <v>43</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D11" s="0" t="s">
         <v>13</v>
@@ -1105,18 +1144,18 @@
         <v>13</v>
       </c>
       <c r="E32" s="0" t="s">
-        <v>9</v>
+        <v>102</v>
       </c>
       <c r="F32" s="0" t="s">
-        <v>9</v>
+        <v>102</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C33" s="0" t="s">
         <v>32</v>
@@ -1128,15 +1167,15 @@
         <v>38</v>
       </c>
       <c r="F33" s="0" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C34" s="0" t="s">
         <v>12</v>
@@ -1148,15 +1187,15 @@
         <v>4</v>
       </c>
       <c r="F34" s="0" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C35" s="0" t="s">
         <v>17</v>
@@ -1165,15 +1204,15 @@
         <v>13</v>
       </c>
       <c r="E35" s="0" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C36" s="0" t="s">
         <v>37</v>
@@ -1182,18 +1221,18 @@
         <v>3</v>
       </c>
       <c r="E36" s="0" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F36" s="0" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C37" s="0" t="s">
         <v>13</v>
@@ -1202,7 +1241,7 @@
         <v>3</v>
       </c>
       <c r="E37" s="0" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F37" s="0" t="s">
         <v>26</v>
@@ -1210,10 +1249,10 @@
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C38" s="0" t="s">
         <v>37</v>
@@ -1222,7 +1261,7 @@
         <v>3</v>
       </c>
       <c r="E38" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F38" s="0" t="s">
         <v>26</v>
@@ -1230,10 +1269,10 @@
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C39" s="0" t="s">
         <v>32</v>
@@ -1245,15 +1284,15 @@
         <v>4</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C40" s="0" t="s">
         <v>32</v>
@@ -1262,143 +1301,223 @@
         <v>3</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="D41" s="0" t="s">
         <v>3</v>
       </c>
       <c r="E41" s="0" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D42" s="0" t="s">
         <v>3</v>
       </c>
       <c r="E42" s="0" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D43" s="0" t="s">
         <v>3</v>
       </c>
       <c r="E43" s="0" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D44" s="0" t="s">
         <v>3</v>
       </c>
       <c r="E44" s="0" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D45" s="0" t="s">
         <v>3</v>
       </c>
       <c r="E45" s="0" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="D46" s="0" t="s">
         <v>3</v>
       </c>
       <c r="E46" s="0" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E47" s="0" t="s">
-        <v>146</v>
+        <v>147</v>
+      </c>
+      <c r="F47" s="0" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E48" s="0" t="s">
-        <v>149</v>
+        <v>151</v>
+      </c>
+      <c r="F48" s="0" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="0" t="s">
+        <v>153</v>
+      </c>
+      <c r="B49" s="0" t="s">
+        <v>154</v>
+      </c>
+      <c r="C49" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="D49" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E49" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="F49" s="0" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="0" t="s">
+        <v>155</v>
+      </c>
+      <c r="B50" s="0" t="s">
+        <v>156</v>
+      </c>
+      <c r="C50" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D50" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E50" s="0" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="0" t="s">
+        <v>158</v>
+      </c>
+      <c r="B51" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="C51" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="D51" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E51" s="0" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="B52" s="0" t="s">
+        <v>162</v>
+      </c>
+      <c r="C52" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="D52" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="E52" s="0" t="s">
+        <v>157</v>
+      </c>
+      <c r="F52" s="0" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resource/MagicFight2/Magic.xlsx
+++ b/Assets/Resource/MagicFight2/Magic.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="129">
   <si>
     <t>a</t>
   </si>
@@ -47,168 +47,168 @@
     <t>c</t>
   </si>
   <si>
+    <t>冻结</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;减速×2</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;进攻时，冷却时间额外+1</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>寒流</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;重置对方一个法术的冷却时间</t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>潮汐</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;光环：使一个法术立即冷却完毕</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;此光环仅能在 你的进攻回合内 使用</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>滚石冲击</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>&lt;sprite=1&gt;守护</t>
+  </si>
+  <si>
+    <t>g</t>
+  </si>
+  <si>
+    <t>陨石</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;快速回填</t>
+  </si>
+  <si>
+    <t>h</t>
+  </si>
+  <si>
+    <t>沉重打击</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;对方无法防御时，将额外减少一点生命值</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;此法术的进攻力量不能增加</t>
+  </si>
+  <si>
+    <t>i</t>
+  </si>
+  <si>
+    <t>地震</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;减速</t>
+  </si>
+  <si>
+    <t>j</t>
+  </si>
+  <si>
+    <t>闪电</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;连击</t>
+  </si>
+  <si>
+    <t>k</t>
+  </si>
+  <si>
+    <t>电弧</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;随机查看对方一张手牌，力量大于等于7则立即进入冷却</t>
+  </si>
+  <si>
+    <t>l</t>
+  </si>
+  <si>
+    <t>磁暴</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;攻击时可以将手中其它法术进入冷却，每冷却一张进攻力量+2</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>雷鸣</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;区域加速</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>引雷</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;光环：使你的基础力量小于等于4的法术获得连击（不能叠加）</t>
+  </si>
+  <si>
+    <t>o</t>
+  </si>
+  <si>
+    <t>过载</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;恢复一点生命值，减少一点生命上限[强制]</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>自燃</t>
+  </si>
+  <si>
+    <t>q</t>
+  </si>
+  <si>
+    <t>海涌</t>
+  </si>
+  <si>
+    <t>r</t>
+  </si>
+  <si>
     <t>水刃</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>&lt;sprite=0&gt;使一张法术立即冷却完成</t>
   </si>
   <si>
-    <t>d</t>
-  </si>
-  <si>
-    <t>寒流</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;重置对方一个法术的冷却时间</t>
-  </si>
-  <si>
-    <t>‌e</t>
-  </si>
-  <si>
-    <t>潮汐</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;光环：使一个法术立即冷却完毕</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;此光环仅能在 你的进攻回合内 使用</t>
-  </si>
-  <si>
-    <t>f</t>
-  </si>
-  <si>
-    <t>滚石冲击</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>&lt;sprite=1&gt;守护</t>
-  </si>
-  <si>
-    <t>g</t>
-  </si>
-  <si>
-    <t>陨石</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;快速回填</t>
-  </si>
-  <si>
-    <t>h</t>
-  </si>
-  <si>
-    <t>沉重打击</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;对方无法防御时，将额外减少一点生命</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;此法术的进攻力量不能增加</t>
-  </si>
-  <si>
-    <t>‌i</t>
-  </si>
-  <si>
-    <t>地震</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;减速</t>
-  </si>
-  <si>
-    <t>j</t>
-  </si>
-  <si>
-    <t>闪电</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;连击</t>
-  </si>
-  <si>
-    <t>‌k</t>
-  </si>
-  <si>
-    <t>电弧</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;随机查看对方一张手牌，力量大于等于7则立即进入冷却</t>
-  </si>
-  <si>
-    <t>l</t>
-  </si>
-  <si>
-    <t>磁暴</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;攻击时可以将手中其它法术进入冷却，每冷却一张进攻力量+2</t>
-  </si>
-  <si>
-    <t>m</t>
-  </si>
-  <si>
-    <t>雷鸣</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;区域加速</t>
-  </si>
-  <si>
-    <t>n</t>
-  </si>
-  <si>
-    <t>引雷</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;光环：使你的基础力量小于等于4的法术获得连击（不能叠加）</t>
-  </si>
-  <si>
-    <t>‌o</t>
-  </si>
-  <si>
-    <t>过载</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;恢复一点生命值，减少一点生命上限[强制]</t>
-  </si>
-  <si>
-    <t>p</t>
-  </si>
-  <si>
-    <t>自燃</t>
-  </si>
-  <si>
-    <t>‌q</t>
-  </si>
-  <si>
-    <t>海涌</t>
-  </si>
-  <si>
-    <t>r</t>
-  </si>
-  <si>
-    <t>缠绕</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;减速×2</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;进攻时，冷却时间额外+3</t>
-  </si>
-  <si>
     <t>s</t>
   </si>
   <si>
@@ -218,19 +218,25 @@
     <t>t</t>
   </si>
   <si>
-    <t>毒刺</t>
+    <t>荆棘</t>
   </si>
   <si>
     <t>&lt;sprite=0&gt;双发</t>
   </si>
   <si>
+    <t>&lt;sprite=0&gt;对方无法防御时，获得 快速回填×2</t>
+  </si>
+  <si>
     <t>u</t>
   </si>
   <si>
     <t>飞叶连击</t>
   </si>
   <si>
-    <t>‌v</t>
+    <t>&lt;sprite=0&gt;此法术获得的 额外进攻力量 翻倍</t>
+  </si>
+  <si>
+    <t>v</t>
   </si>
   <si>
     <t>藤蔓</t>
@@ -245,10 +251,10 @@
     <t>x</t>
   </si>
   <si>
-    <t>模仿</t>
-  </si>
-  <si>
-    <t>复制你的冷却区中的一个 力量大于等于5的法术 的效果，若被模仿的法术具有光环，则激活光环</t>
+    <t>自愈</t>
+  </si>
+  <si>
+    <t>&lt;sprite=2&gt;此法术冷却完毕时，选择:（恢复一点生命值，减少一点生命上限）/（恢复一点生命上限，但不超过初始值）</t>
   </si>
   <si>
     <t>y</t>
@@ -257,10 +263,10 @@
     <t>瀑流</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;你每损失一点生命值，额外加速一个不同的法术</t>
-  </si>
-  <si>
-    <t>‌z</t>
+    <t>&lt;sprite=0&gt;你每损失一点生命值（相较初始值），额外加速一个不同的法术</t>
+  </si>
+  <si>
+    <t>z</t>
   </si>
   <si>
     <t>地动波</t>
@@ -275,7 +281,7 @@
     <t>漩涡</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;可以交换你的两个冷却区中的所有法术（另一个冷却区可以是空的）</t>
+    <t>&lt;sprite=0&gt;可以将你的冷却区中的一张法术永久移出游戏，获得 加速×该法术的基础冷却值</t>
   </si>
   <si>
     <t>ab</t>
@@ -302,10 +308,10 @@
     <t>雷云</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;随机查看对方一张手牌，力量小于等于4则立即进入冷却，冷却时间至少为3</t>
-  </si>
-  <si>
-    <t>‌ae</t>
+    <t>&lt;sprite=0&gt;随机查看对方一张手牌，力量小于等于4则立即进入冷却</t>
+  </si>
+  <si>
+    <t>ae</t>
   </si>
   <si>
     <t>灼烧</t>
@@ -332,7 +338,7 @@
     <t>&lt;sprite=0&gt;光环：使法术附带进攻力量+2</t>
   </si>
   <si>
-    <t>‌ah</t>
+    <t>ah</t>
   </si>
   <si>
     <t>烈焰斗篷</t>
@@ -386,121 +392,13 @@
     <t>&lt;sprite=0&gt;攻击时可以将手中其它法术进入冷却，每冷却一张获得一次加速</t>
   </si>
   <si>
-    <t>‌an</t>
+    <t>an</t>
   </si>
   <si>
     <t>雪崩</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;使自己和对方的 冷却区中剩余冷却为1的法术 都被减速[强制]</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>电</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;形态：你的所有法术都拥有连击（除了此法术），但是进攻时冷却+1（最多为4），并且造成伤害后本回合无法再出牌[强制]</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>水</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;形态：轮到你进攻时，所有法术的剩余冷却从减1改为减2（除了此法术），但是你所有法术的防御力量减1（力量最低为1）[强制]</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>石</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;形态：攻击你的法术的所有效果失效（只有基础攻击力），但是你在防御前无法看到对方的法术，出牌防御失败也会进入冷却[强制]</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>冰</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;形态：你的所有法术额外拥有减速（除了此法术）</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>草</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;形态：当你的法术攻击造成伤害时，你恢复一点生命值（除了此法术）</t>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>火</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;形态：你的所有法术都获得进攻时力量+2，但进攻时无法看见手牌，只能从中随机抽牌打出[强制]</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>次声波</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;强化×2</t>
-  </si>
-  <si>
-    <t>&lt;sprite=1&gt;强化</t>
-  </si>
-  <si>
-    <t>48</t>
-  </si>
-  <si>
-    <t>共鸣</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;强化</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;光环：法术额外附带进攻力量+（当前强化值）</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>回声</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>飓风</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;备用法术</t>
-  </si>
-  <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>风暴吐息</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;备用法术×2</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>空袭</t>
+    <t>&lt;sprite=0&gt;使自己和对方的 冷却区中剩余冷却为1的法术 都被减速[强制]</t>
   </si>
 </sst>
 </file>
@@ -546,7 +444,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,9 +498,12 @@
         <v>12</v>
       </c>
       <c r="D3" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="F3" s="0" t="s">
         <v>14</v>
       </c>
     </row>
@@ -617,7 +518,7 @@
         <v>17</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E4" s="0" t="s">
         <v>18</v>
@@ -691,7 +592,7 @@
         <v>32</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E8" s="0" t="s">
         <v>33</v>
@@ -711,7 +612,7 @@
         <v>37</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E9" s="0" t="s">
         <v>38</v>
@@ -745,7 +646,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E11" s="0" t="s">
         <v>44</v>
@@ -762,13 +663,13 @@
         <v>46</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F12" s="0" t="s">
         <v>41</v>
@@ -776,10 +677,10 @@
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C13" s="0" t="s">
         <v>8</v>
@@ -788,7 +689,7 @@
         <v>3</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F13" s="0" t="s">
         <v>41</v>
@@ -796,27 +697,27 @@
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C14" s="0" t="s">
         <v>17</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C15" s="0" t="s">
         <v>8</v>
@@ -825,7 +726,7 @@
         <v>8</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F15" s="0" t="s">
         <v>41</v>
@@ -833,30 +734,30 @@
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D16" s="0" t="s">
         <v>8</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C17" s="0" t="s">
         <v>3</v>
@@ -868,26 +769,23 @@
         <v>4</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>63</v>
-      </c>
-      <c r="F18" s="0" t="s">
         <v>64</v>
       </c>
     </row>
@@ -899,13 +797,13 @@
         <v>66</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D19" s="0" t="s">
         <v>8</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20">
@@ -916,24 +814,24 @@
         <v>68</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E20" s="0" t="s">
         <v>69</v>
       </c>
       <c r="F20" s="0" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C21" s="0" t="s">
         <v>2</v>
@@ -945,21 +843,21 @@
         <v>69</v>
       </c>
       <c r="F21" s="0" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E22" s="0" t="s">
         <v>69</v>
@@ -967,16 +865,16 @@
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C23" s="0" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E23" s="0" t="s">
         <v>69</v>
@@ -987,104 +885,101 @@
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C25" s="0" t="s">
         <v>17</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E25" s="0" t="s">
         <v>4</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C26" s="0" t="s">
         <v>32</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E26" s="0" t="s">
         <v>29</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C27" s="0" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>87</v>
-      </c>
-      <c r="F27" s="0" t="s">
-        <v>29</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E28" s="0" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C29" s="0" t="s">
         <v>3</v>
@@ -1093,32 +988,35 @@
         <v>8</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>96</v>
+        <v>38</v>
+      </c>
+      <c r="F30" s="0" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C31" s="0" t="s">
         <v>3</v>
@@ -1127,92 +1025,92 @@
         <v>8</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E32" s="0" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F32" s="0" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C33" s="0" t="s">
         <v>32</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E33" s="0" t="s">
         <v>38</v>
       </c>
       <c r="F33" s="0" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E34" s="0" t="s">
         <v>4</v>
       </c>
       <c r="F34" s="0" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C35" s="0" t="s">
         <v>17</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E35" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C36" s="0" t="s">
         <v>37</v>
@@ -1221,27 +1119,27 @@
         <v>3</v>
       </c>
       <c r="E36" s="0" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F36" s="0" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D37" s="0" t="s">
         <v>3</v>
       </c>
       <c r="E37" s="0" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F37" s="0" t="s">
         <v>26</v>
@@ -1249,10 +1147,10 @@
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C38" s="0" t="s">
         <v>37</v>
@@ -1261,7 +1159,7 @@
         <v>3</v>
       </c>
       <c r="E38" s="0" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F38" s="0" t="s">
         <v>26</v>
@@ -1269,30 +1167,30 @@
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C39" s="0" t="s">
         <v>32</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E39" s="0" t="s">
         <v>4</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C40" s="0" t="s">
         <v>32</v>
@@ -1301,223 +1199,7 @@
         <v>3</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="0" t="s">
-        <v>127</v>
-      </c>
-      <c r="B41" s="0" t="s">
         <v>128</v>
-      </c>
-      <c r="C41" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="D41" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="E41" s="0" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="0" t="s">
-        <v>130</v>
-      </c>
-      <c r="B42" s="0" t="s">
-        <v>131</v>
-      </c>
-      <c r="C42" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D42" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="E42" s="0" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="0" t="s">
-        <v>133</v>
-      </c>
-      <c r="B43" s="0" t="s">
-        <v>134</v>
-      </c>
-      <c r="C43" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="D43" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="E43" s="0" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="B44" s="0" t="s">
-        <v>137</v>
-      </c>
-      <c r="C44" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="D44" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="E44" s="0" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="0" t="s">
-        <v>139</v>
-      </c>
-      <c r="B45" s="0" t="s">
-        <v>140</v>
-      </c>
-      <c r="C45" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D45" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="E45" s="0" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="0" t="s">
-        <v>142</v>
-      </c>
-      <c r="B46" s="0" t="s">
-        <v>143</v>
-      </c>
-      <c r="C46" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="D46" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="E46" s="0" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="0" t="s">
-        <v>145</v>
-      </c>
-      <c r="B47" s="0" t="s">
-        <v>146</v>
-      </c>
-      <c r="C47" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="D47" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E47" s="0" t="s">
-        <v>147</v>
-      </c>
-      <c r="F47" s="0" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="0" t="s">
-        <v>149</v>
-      </c>
-      <c r="B48" s="0" t="s">
-        <v>150</v>
-      </c>
-      <c r="C48" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="D48" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="E48" s="0" t="s">
-        <v>151</v>
-      </c>
-      <c r="F48" s="0" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="0" t="s">
-        <v>153</v>
-      </c>
-      <c r="B49" s="0" t="s">
-        <v>154</v>
-      </c>
-      <c r="C49" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D49" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="E49" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="F49" s="0" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="0" t="s">
-        <v>155</v>
-      </c>
-      <c r="B50" s="0" t="s">
-        <v>156</v>
-      </c>
-      <c r="C50" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="D50" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="E50" s="0" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="0" t="s">
-        <v>158</v>
-      </c>
-      <c r="B51" s="0" t="s">
-        <v>159</v>
-      </c>
-      <c r="C51" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="D51" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="E51" s="0" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="0" t="s">
-        <v>161</v>
-      </c>
-      <c r="B52" s="0" t="s">
-        <v>162</v>
-      </c>
-      <c r="C52" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D52" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="E52" s="0" t="s">
-        <v>157</v>
-      </c>
-      <c r="F52" s="0" t="s">
-        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resource/MagicFight2/Magic.xlsx
+++ b/Assets/Resource/MagicFight2/Magic.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="131">
   <si>
     <t>a</t>
   </si>
@@ -47,7 +47,7 @@
     <t>c</t>
   </si>
   <si>
-    <t>冻结</t>
+    <t>凝固</t>
   </si>
   <si>
     <t>3</t>
@@ -251,10 +251,16 @@
     <t>x</t>
   </si>
   <si>
-    <t>自愈</t>
-  </si>
-  <si>
-    <t>&lt;sprite=2&gt;此法术冷却完毕时，选择:（恢复一点生命值，减少一点生命上限）/（恢复一点生命上限，但不超过初始值）</t>
+    <t>模仿</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;复制你的冷却区中一个 基础冷却小于等于3且无光环 的法术的力量和效果</t>
+  </si>
+  <si>
+    <t>&lt;sprite=2&gt;未复制或其他情况下力量视为1</t>
   </si>
   <si>
     <t>y</t>
@@ -891,21 +897,24 @@
         <v>79</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="D24" s="0" t="s">
         <v>3</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="F24" s="0" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C25" s="0" t="s">
         <v>17</v>
@@ -917,15 +926,15 @@
         <v>4</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C26" s="0" t="s">
         <v>32</v>
@@ -937,15 +946,15 @@
         <v>29</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C27" s="0" t="s">
         <v>3</v>
@@ -954,15 +963,15 @@
         <v>12</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C28" s="0" t="s">
         <v>47</v>
@@ -971,15 +980,15 @@
         <v>12</v>
       </c>
       <c r="E28" s="0" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C29" s="0" t="s">
         <v>3</v>
@@ -988,15 +997,15 @@
         <v>8</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C30" s="0" t="s">
         <v>17</v>
@@ -1008,15 +1017,15 @@
         <v>38</v>
       </c>
       <c r="F30" s="0" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C31" s="0" t="s">
         <v>3</v>
@@ -1025,15 +1034,15 @@
         <v>8</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C32" s="0" t="s">
         <v>47</v>
@@ -1042,18 +1051,18 @@
         <v>12</v>
       </c>
       <c r="E32" s="0" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F32" s="0" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C33" s="0" t="s">
         <v>32</v>
@@ -1065,15 +1074,15 @@
         <v>38</v>
       </c>
       <c r="F33" s="0" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C34" s="0" t="s">
         <v>47</v>
@@ -1085,15 +1094,15 @@
         <v>4</v>
       </c>
       <c r="F34" s="0" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C35" s="0" t="s">
         <v>17</v>
@@ -1102,15 +1111,15 @@
         <v>12</v>
       </c>
       <c r="E35" s="0" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C36" s="0" t="s">
         <v>37</v>
@@ -1119,27 +1128,27 @@
         <v>3</v>
       </c>
       <c r="E36" s="0" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F36" s="0" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D37" s="0" t="s">
         <v>3</v>
       </c>
       <c r="E37" s="0" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F37" s="0" t="s">
         <v>26</v>
@@ -1147,10 +1156,10 @@
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C38" s="0" t="s">
         <v>37</v>
@@ -1159,7 +1168,7 @@
         <v>3</v>
       </c>
       <c r="E38" s="0" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F38" s="0" t="s">
         <v>26</v>
@@ -1167,10 +1176,10 @@
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C39" s="0" t="s">
         <v>32</v>
@@ -1182,15 +1191,15 @@
         <v>4</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C40" s="0" t="s">
         <v>32</v>
@@ -1199,7 +1208,7 @@
         <v>3</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resource/MagicFight2/Magic.xlsx
+++ b/Assets/Resource/MagicFight2/Magic.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="160">
   <si>
     <t>a</t>
   </si>
@@ -405,6 +405,93 @@
   </si>
   <si>
     <t>&lt;sprite=0&gt;使自己和对方的 冷却区中剩余冷却为1的法术 都被减速[强制]</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>次声波</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;强化×2（只会获得一次力量加成，但是叠加两点强化值）</t>
+  </si>
+  <si>
+    <t>&lt;sprite=1&gt;强化</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>共振</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;强化</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;光环：使法术附带进攻力量+当前强化值</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>振荡</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>剧毒种子</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;中毒×2</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>毒刺</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;中毒</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>裂变</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;若 这是你手中最后一张法术 并且 是本回合打出的第一张法术，则进攻结束后再开始一次你的进攻回合</t>
+  </si>
+  <si>
+    <t>07</t>
+  </si>
+  <si>
+    <t>鬼火</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;你的生命值 小于等于初始值的一半 时，进攻力量+1</t>
+  </si>
+  <si>
+    <t>&lt;sprite=2&gt;你的生命值减少时，此法术立即冷却完毕</t>
+  </si>
+  <si>
+    <t>08</t>
+  </si>
+  <si>
+    <t>雾隐</t>
+  </si>
+  <si>
+    <t>&lt;sprite=2&gt;此法术冷却完毕时，立即获得加速×2</t>
+  </si>
+  <si>
+    <t>09</t>
+  </si>
+  <si>
+    <t>电力转换</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;可以将手中一张其它法术进入冷却，然后获得连击</t>
   </si>
 </sst>
 </file>
@@ -450,7 +537,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1211,6 +1298,180 @@
         <v>130</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="B41" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="C41" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="0" t="s">
+        <v>133</v>
+      </c>
+      <c r="F41" s="0" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="B42" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="C42" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="D42" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="E42" s="0" t="s">
+        <v>137</v>
+      </c>
+      <c r="F42" s="0" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="B43" s="0" t="s">
+        <v>140</v>
+      </c>
+      <c r="C43" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="D43" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="0" t="s">
+        <v>137</v>
+      </c>
+      <c r="F43" s="0" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="0" t="s">
+        <v>141</v>
+      </c>
+      <c r="B44" s="0" t="s">
+        <v>142</v>
+      </c>
+      <c r="C44" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="D44" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="0" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="0" t="s">
+        <v>144</v>
+      </c>
+      <c r="B45" s="0" t="s">
+        <v>145</v>
+      </c>
+      <c r="C45" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="D45" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="E45" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="F45" s="0" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="B46" s="0" t="s">
+        <v>148</v>
+      </c>
+      <c r="C46" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="D46" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E46" s="0" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="B47" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="C47" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="D47" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="0" t="s">
+        <v>152</v>
+      </c>
+      <c r="F47" s="0" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="0" t="s">
+        <v>154</v>
+      </c>
+      <c r="B48" s="0" t="s">
+        <v>155</v>
+      </c>
+      <c r="C48" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="D48" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E48" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F48" s="0" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="0" t="s">
+        <v>157</v>
+      </c>
+      <c r="B49" s="0" t="s">
+        <v>158</v>
+      </c>
+      <c r="C49" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="D49" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="E49" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="F49" s="0" t="s">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <headerFooter/>
 </worksheet>

--- a/Assets/Resource/MagicFight2/Magic.xlsx
+++ b/Assets/Resource/MagicFight2/Magic.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="158">
   <si>
     <t>a</t>
   </si>
@@ -20,192 +20,189 @@
     <t>暴风雪</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;加速</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;区域减速</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>冰风暴</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;光环：使法术附带防御时力量+2</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>凝固</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;减速×2</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>寒流</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;重置对方一个法术的冷却时间</t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>潮汐</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;加速</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;区域减速</t>
-  </si>
-  <si>
-    <t>b</t>
-  </si>
-  <si>
-    <t>冰风暴</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;光环：使法术附带防御时力量+2</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>凝固</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;减速×2</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;进攻时，冷却时间额外+1</t>
-  </si>
-  <si>
-    <t>d</t>
-  </si>
-  <si>
-    <t>寒流</t>
+    <t>&lt;sprite=2&gt;此法术冷却完毕时，使一个法术也立即冷却完毕</t>
+  </si>
+  <si>
+    <t>&lt;sprite=1&gt;防御时，力量+1</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>滚石冲击</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>&lt;sprite=1&gt;守护</t>
+  </si>
+  <si>
+    <t>g</t>
+  </si>
+  <si>
+    <t>陨石</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;快速回填</t>
+  </si>
+  <si>
+    <t>h</t>
+  </si>
+  <si>
+    <t>沉重打击</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;对方无法防御时，将额外减少一点生命值</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;此法术的进攻力量不能增加</t>
+  </si>
+  <si>
+    <t>i</t>
+  </si>
+  <si>
+    <t>地震</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;减速</t>
+  </si>
+  <si>
+    <t>j</t>
+  </si>
+  <si>
+    <t>闪电</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;连击</t>
+  </si>
+  <si>
+    <t>k</t>
+  </si>
+  <si>
+    <t>电弧</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;随机查看对方一张手牌，力量大于等于7则立即进入冷却</t>
+  </si>
+  <si>
+    <t>l</t>
+  </si>
+  <si>
+    <t>磁暴</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;攻击时可以将手中其它法术进入冷却，每冷却一张进攻力量+3</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>雷鸣</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;区域加速</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>引雷</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;重置对方一个法术的冷却时间</t>
-  </si>
-  <si>
-    <t>e</t>
-  </si>
-  <si>
-    <t>潮汐</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;光环：使一个法术立即冷却完毕</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;此光环仅能在 你的进攻回合内 使用</t>
-  </si>
-  <si>
-    <t>f</t>
-  </si>
-  <si>
-    <t>滚石冲击</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>&lt;sprite=1&gt;守护</t>
-  </si>
-  <si>
-    <t>g</t>
-  </si>
-  <si>
-    <t>陨石</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;快速回填</t>
-  </si>
-  <si>
-    <t>h</t>
-  </si>
-  <si>
-    <t>沉重打击</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;对方无法防御时，将额外减少一点生命值</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;此法术的进攻力量不能增加</t>
-  </si>
-  <si>
-    <t>i</t>
-  </si>
-  <si>
-    <t>地震</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;减速</t>
-  </si>
-  <si>
-    <t>j</t>
-  </si>
-  <si>
-    <t>闪电</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;连击</t>
-  </si>
-  <si>
-    <t>k</t>
-  </si>
-  <si>
-    <t>电弧</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;随机查看对方一张手牌，力量大于等于7则立即进入冷却</t>
-  </si>
-  <si>
-    <t>l</t>
-  </si>
-  <si>
-    <t>磁暴</t>
+    <t>&lt;sprite=0&gt;光环：使你的基础力量小于等于4的法术获得连击（不能叠加）</t>
+  </si>
+  <si>
+    <t>o</t>
+  </si>
+  <si>
+    <t>过载</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;恢复一点生命值，减少一点生命上限[强制]</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>自燃</t>
+  </si>
+  <si>
+    <t>q</t>
+  </si>
+  <si>
+    <t>海涌</t>
+  </si>
+  <si>
+    <t>r</t>
+  </si>
+  <si>
+    <t>水刃</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;攻击时可以将手中其它法术进入冷却，每冷却一张进攻力量+2</t>
-  </si>
-  <si>
-    <t>m</t>
-  </si>
-  <si>
-    <t>雷鸣</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;区域加速</t>
-  </si>
-  <si>
-    <t>n</t>
-  </si>
-  <si>
-    <t>引雷</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;光环：使你的基础力量小于等于4的法术获得连击（不能叠加）</t>
-  </si>
-  <si>
-    <t>o</t>
-  </si>
-  <si>
-    <t>过载</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;恢复一点生命值，减少一点生命上限[强制]</t>
-  </si>
-  <si>
-    <t>p</t>
-  </si>
-  <si>
-    <t>自燃</t>
-  </si>
-  <si>
-    <t>q</t>
-  </si>
-  <si>
-    <t>海涌</t>
-  </si>
-  <si>
-    <t>r</t>
-  </si>
-  <si>
-    <t>水刃</t>
-  </si>
-  <si>
     <t>&lt;sprite=0&gt;使一张法术立即冷却完成</t>
   </si>
   <si>
@@ -257,7 +254,7 @@
     <t>X</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;复制你的冷却区中一个 基础冷却小于等于3且无光环 的法术的力量和效果</t>
+    <t>&lt;sprite=0&gt;复制你的冷却区中一个 基础冷却等于3且无光环 的法术的力量和进攻效果</t>
   </si>
   <si>
     <t>&lt;sprite=2&gt;未复制或其他情况下力量视为1</t>
@@ -278,16 +275,13 @@
     <t>地动波</t>
   </si>
   <si>
-    <t>&lt;sprite=1&gt;防御时，力量+1</t>
-  </si>
-  <si>
     <t>aa</t>
   </si>
   <si>
     <t>漩涡</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;可以将你的冷却区中的一张法术永久移出游戏，获得 加速×该法术的基础冷却值</t>
+    <t>&lt;sprite=0&gt;可以将你的冷却区中的一张法术永久移出游戏，获得 加速×3</t>
   </si>
   <si>
     <t>ab</t>
@@ -588,64 +582,61 @@
         <v>11</v>
       </c>
       <c r="C3" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="0" t="s">
         <v>12</v>
-      </c>
-      <c r="D3" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="0" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="D4" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="0" t="s">
         <v>16</v>
-      </c>
-      <c r="C4" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="0" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="D5" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="0" t="s">
+      <c r="F5" s="0" t="s">
         <v>21</v>
-      </c>
-      <c r="F5" s="0" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="C6" s="0" t="s">
         <v>24</v>
-      </c>
-      <c r="C6" s="0" t="s">
-        <v>25</v>
       </c>
       <c r="D6" s="0" t="s">
         <v>3</v>
@@ -654,203 +645,203 @@
         <v>4</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="C7" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="0" t="s">
         <v>28</v>
-      </c>
-      <c r="C7" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="E7" s="0" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="0" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="C8" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="F8" s="0" t="s">
         <v>32</v>
-      </c>
-      <c r="D8" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8" s="0" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="0" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="D9" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="0" t="s">
         <v>36</v>
-      </c>
-      <c r="C9" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="0" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="0" t="s">
         <v>39</v>
-      </c>
-      <c r="B10" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="C10" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="0" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" s="0" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="0" t="s">
-        <v>44</v>
-      </c>
       <c r="F11" s="0" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="0" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="0" t="s">
-        <v>48</v>
-      </c>
       <c r="F12" s="0" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D13" s="0" t="s">
         <v>3</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="0" t="s">
         <v>52</v>
-      </c>
-      <c r="B14" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="C14" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="0" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="0" t="s">
         <v>55</v>
       </c>
-      <c r="B15" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C15" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" s="0" t="s">
-        <v>57</v>
-      </c>
       <c r="F15" s="0" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C17" s="0" t="s">
         <v>3</v>
@@ -862,115 +853,115 @@
         <v>4</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" s="0" t="s">
         <v>62</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="D18" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="0" t="s">
         <v>63</v>
-      </c>
-      <c r="C18" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="D18" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="E18" s="0" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="B19" s="0" t="s">
-        <v>66</v>
-      </c>
       <c r="C19" s="0" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="B20" s="0" t="s">
         <v>67</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="C20" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="C20" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="D20" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="E20" s="0" t="s">
+      <c r="F20" s="0" t="s">
         <v>69</v>
-      </c>
-      <c r="F20" s="0" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" s="0" t="s">
         <v>71</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="C21" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E21" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="F21" s="0" t="s">
         <v>72</v>
-      </c>
-      <c r="C21" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="D21" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="F21" s="0" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" s="0" t="s">
         <v>74</v>
       </c>
-      <c r="B22" s="0" t="s">
-        <v>75</v>
-      </c>
       <c r="C22" s="0" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="B23" s="0" t="s">
         <v>76</v>
       </c>
-      <c r="B23" s="0" t="s">
-        <v>77</v>
-      </c>
       <c r="C23" s="0" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F23" s="0" t="s">
         <v>4</v>
@@ -978,498 +969,498 @@
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="B24" s="0" t="s">
         <v>78</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="C24" s="0" t="s">
         <v>79</v>
       </c>
-      <c r="C24" s="0" t="s">
+      <c r="D24" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="0" t="s">
         <v>80</v>
       </c>
-      <c r="D24" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="E24" s="0" t="s">
+      <c r="F24" s="0" t="s">
         <v>81</v>
-      </c>
-      <c r="F24" s="0" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="B25" s="0" t="s">
         <v>83</v>
       </c>
-      <c r="B25" s="0" t="s">
-        <v>84</v>
-      </c>
       <c r="C25" s="0" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E25" s="0" t="s">
         <v>4</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="B26" s="0" t="s">
         <v>86</v>
       </c>
-      <c r="B26" s="0" t="s">
-        <v>87</v>
-      </c>
       <c r="C26" s="0" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>88</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
+        <v>87</v>
+      </c>
+      <c r="B27" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="C27" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E27" s="0" t="s">
         <v>89</v>
-      </c>
-      <c r="B27" s="0" t="s">
-        <v>90</v>
-      </c>
-      <c r="C27" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="E27" s="0" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="B28" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="C28" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="D28" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="0" t="s">
         <v>92</v>
-      </c>
-      <c r="B28" s="0" t="s">
-        <v>93</v>
-      </c>
-      <c r="C28" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="D28" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="E28" s="0" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="B29" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="C29" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E29" s="0" t="s">
         <v>95</v>
-      </c>
-      <c r="B29" s="0" t="s">
-        <v>96</v>
-      </c>
-      <c r="C29" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="D29" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="0" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="B30" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="C30" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="D30" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="F30" s="0" t="s">
         <v>98</v>
-      </c>
-      <c r="B30" s="0" t="s">
-        <v>99</v>
-      </c>
-      <c r="C30" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D30" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="E30" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="F30" s="0" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="B31" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="C31" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E31" s="0" t="s">
         <v>101</v>
-      </c>
-      <c r="B31" s="0" t="s">
-        <v>102</v>
-      </c>
-      <c r="C31" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="D31" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E31" s="0" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="B32" s="0" t="s">
+        <v>103</v>
+      </c>
+      <c r="C32" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="D32" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="0" t="s">
         <v>104</v>
       </c>
-      <c r="B32" s="0" t="s">
-        <v>105</v>
-      </c>
-      <c r="C32" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="D32" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="E32" s="0" t="s">
-        <v>106</v>
-      </c>
       <c r="F32" s="0" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
+        <v>105</v>
+      </c>
+      <c r="B33" s="0" t="s">
+        <v>106</v>
+      </c>
+      <c r="C33" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="F33" s="0" t="s">
         <v>107</v>
-      </c>
-      <c r="B33" s="0" t="s">
-        <v>108</v>
-      </c>
-      <c r="C33" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="D33" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="E33" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="F33" s="0" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E34" s="0" t="s">
         <v>4</v>
       </c>
       <c r="F34" s="0" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
+        <v>111</v>
+      </c>
+      <c r="B35" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="C35" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="D35" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="0" t="s">
         <v>113</v>
-      </c>
-      <c r="B35" s="0" t="s">
-        <v>114</v>
-      </c>
-      <c r="C35" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D35" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="E35" s="0" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
+        <v>114</v>
+      </c>
+      <c r="B36" s="0" t="s">
+        <v>115</v>
+      </c>
+      <c r="C36" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="D36" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E36" s="0" t="s">
         <v>116</v>
       </c>
-      <c r="B36" s="0" t="s">
-        <v>117</v>
-      </c>
-      <c r="C36" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="D36" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="E36" s="0" t="s">
-        <v>118</v>
-      </c>
       <c r="F36" s="0" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="B37" s="0" t="s">
+        <v>118</v>
+      </c>
+      <c r="C37" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="D37" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E37" s="0" t="s">
         <v>119</v>
       </c>
-      <c r="B37" s="0" t="s">
-        <v>120</v>
-      </c>
-      <c r="C37" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="D37" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="E37" s="0" t="s">
-        <v>121</v>
-      </c>
       <c r="F37" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
+        <v>120</v>
+      </c>
+      <c r="B38" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="C38" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="D38" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E38" s="0" t="s">
         <v>122</v>
       </c>
-      <c r="B38" s="0" t="s">
-        <v>123</v>
-      </c>
-      <c r="C38" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="D38" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="E38" s="0" t="s">
-        <v>124</v>
-      </c>
       <c r="F38" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E39" s="0" t="s">
         <v>4</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="B40" s="0" t="s">
+        <v>127</v>
+      </c>
+      <c r="C40" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="D40" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="0" t="s">
         <v>128</v>
-      </c>
-      <c r="B40" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="C40" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="D40" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="E40" s="0" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="s">
+        <v>129</v>
+      </c>
+      <c r="B41" s="0" t="s">
+        <v>130</v>
+      </c>
+      <c r="C41" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="D41" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E41" s="0" t="s">
         <v>131</v>
       </c>
-      <c r="B41" s="0" t="s">
+      <c r="F41" s="0" t="s">
         <v>132</v>
-      </c>
-      <c r="C41" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="D41" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="E41" s="0" t="s">
-        <v>133</v>
-      </c>
-      <c r="F41" s="0" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="s">
+        <v>133</v>
+      </c>
+      <c r="B42" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="C42" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="D42" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="0" t="s">
         <v>135</v>
       </c>
-      <c r="B42" s="0" t="s">
+      <c r="F42" s="0" t="s">
         <v>136</v>
-      </c>
-      <c r="C42" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="D42" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="E42" s="0" t="s">
-        <v>137</v>
-      </c>
-      <c r="F42" s="0" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C43" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="D43" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="F43" s="0" t="s">
         <v>25</v>
-      </c>
-      <c r="D43" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="E43" s="0" t="s">
-        <v>137</v>
-      </c>
-      <c r="F43" s="0" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="B44" s="0" t="s">
+        <v>140</v>
+      </c>
+      <c r="C44" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="D44" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="0" t="s">
         <v>141</v>
-      </c>
-      <c r="B44" s="0" t="s">
-        <v>142</v>
-      </c>
-      <c r="C44" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="D44" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="E44" s="0" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="s">
+        <v>142</v>
+      </c>
+      <c r="B45" s="0" t="s">
+        <v>143</v>
+      </c>
+      <c r="C45" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="F45" s="0" t="s">
         <v>144</v>
-      </c>
-      <c r="B45" s="0" t="s">
-        <v>145</v>
-      </c>
-      <c r="C45" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="D45" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="E45" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="F45" s="0" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="s">
+        <v>145</v>
+      </c>
+      <c r="B46" s="0" t="s">
+        <v>146</v>
+      </c>
+      <c r="C46" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="D46" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E46" s="0" t="s">
         <v>147</v>
-      </c>
-      <c r="B46" s="0" t="s">
-        <v>148</v>
-      </c>
-      <c r="C46" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="D46" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="E46" s="0" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="s">
+        <v>148</v>
+      </c>
+      <c r="B47" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="C47" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="D47" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="0" t="s">
         <v>150</v>
       </c>
-      <c r="B47" s="0" t="s">
+      <c r="F47" s="0" t="s">
         <v>151</v>
-      </c>
-      <c r="C47" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="D47" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="E47" s="0" t="s">
-        <v>152</v>
-      </c>
-      <c r="F47" s="0" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="s">
+        <v>152</v>
+      </c>
+      <c r="B48" s="0" t="s">
+        <v>153</v>
+      </c>
+      <c r="C48" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="D48" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E48" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="F48" s="0" t="s">
         <v>154</v>
-      </c>
-      <c r="B48" s="0" t="s">
-        <v>155</v>
-      </c>
-      <c r="C48" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="D48" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="E48" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="F48" s="0" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="s">
+        <v>155</v>
+      </c>
+      <c r="B49" s="0" t="s">
+        <v>156</v>
+      </c>
+      <c r="C49" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="D49" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="0" t="s">
         <v>157</v>
       </c>
-      <c r="B49" s="0" t="s">
-        <v>158</v>
-      </c>
-      <c r="C49" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D49" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="E49" s="0" t="s">
-        <v>159</v>
-      </c>
       <c r="F49" s="0" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resource/MagicFight2/Magic.xlsx
+++ b/Assets/Resource/MagicFight2/Magic.xlsx
@@ -20,36 +20,36 @@
     <t>暴风雪</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;加速</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;区域减速</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>冰风暴</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;光环：使法术附带防御时力量+2</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>凝固</t>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;加速</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;区域减速</t>
-  </si>
-  <si>
-    <t>b</t>
-  </si>
-  <si>
-    <t>冰风暴</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;光环：使法术附带防御时力量+2</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>凝固</t>
-  </si>
-  <si>
     <t>&lt;sprite=0&gt;减速×2</t>
   </si>
   <si>
@@ -140,7 +140,7 @@
     <t>电弧</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;随机查看对方一张手牌，力量大于等于7则立即进入冷却</t>
+    <t>&lt;sprite=0&gt;攻击时可以将手中其它法术进入冷却，每冷却一张获得一次快速回填</t>
   </si>
   <si>
     <t>l</t>
@@ -562,7 +562,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D2" s="0" t="s">
         <v>3</v>
@@ -571,21 +571,21 @@
         <v>5</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="C3" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="0" t="s">
         <v>11</v>
-      </c>
-      <c r="C3" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="0" t="s">
-        <v>2</v>
       </c>
       <c r="E3" s="0" t="s">
         <v>12</v>
@@ -602,7 +602,7 @@
         <v>15</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E4" s="0" t="s">
         <v>16</v>
@@ -619,7 +619,7 @@
         <v>19</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E5" s="0" t="s">
         <v>20</v>
@@ -676,7 +676,7 @@
         <v>15</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E8" s="0" t="s">
         <v>31</v>
@@ -696,7 +696,7 @@
         <v>35</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E9" s="0" t="s">
         <v>36</v>
@@ -727,10 +727,10 @@
         <v>41</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11" s="0" t="s">
         <v>42</v>
@@ -747,10 +747,10 @@
         <v>44</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E12" s="0" t="s">
         <v>45</v>
@@ -790,7 +790,7 @@
         <v>51</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E14" s="0" t="s">
         <v>52</v>
@@ -804,10 +804,10 @@
         <v>54</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E15" s="0" t="s">
         <v>55</v>
@@ -824,10 +824,10 @@
         <v>57</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E16" s="0" t="s">
         <v>55</v>
@@ -844,7 +844,7 @@
         <v>59</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D17" s="0" t="s">
         <v>3</v>
@@ -867,7 +867,7 @@
         <v>62</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E18" s="0" t="s">
         <v>63</v>
@@ -881,10 +881,10 @@
         <v>65</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E19" s="0" t="s">
         <v>48</v>
@@ -898,10 +898,10 @@
         <v>67</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E20" s="0" t="s">
         <v>68</v>
@@ -918,10 +918,10 @@
         <v>71</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E21" s="0" t="s">
         <v>68</v>
@@ -941,7 +941,7 @@
         <v>62</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E22" s="0" t="s">
         <v>68</v>
@@ -958,7 +958,7 @@
         <v>3</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E23" s="0" t="s">
         <v>68</v>
@@ -998,10 +998,10 @@
         <v>51</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="F25" s="0" t="s">
         <v>84</v>
@@ -1018,7 +1018,7 @@
         <v>15</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E26" s="0" t="s">
         <v>28</v>
@@ -1038,7 +1038,7 @@
         <v>3</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E27" s="0" t="s">
         <v>89</v>
@@ -1055,7 +1055,7 @@
         <v>62</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E28" s="0" t="s">
         <v>92</v>
@@ -1072,7 +1072,7 @@
         <v>3</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E29" s="0" t="s">
         <v>95</v>
@@ -1089,7 +1089,7 @@
         <v>51</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E30" s="0" t="s">
         <v>36</v>
@@ -1109,7 +1109,7 @@
         <v>3</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E31" s="0" t="s">
         <v>101</v>
@@ -1126,7 +1126,7 @@
         <v>62</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E32" s="0" t="s">
         <v>104</v>
@@ -1146,7 +1146,7 @@
         <v>15</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E33" s="0" t="s">
         <v>36</v>
@@ -1166,7 +1166,7 @@
         <v>62</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E34" s="0" t="s">
         <v>4</v>
@@ -1186,7 +1186,7 @@
         <v>51</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E35" s="0" t="s">
         <v>113</v>
@@ -1220,7 +1220,7 @@
         <v>118</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="D37" s="0" t="s">
         <v>3</v>
@@ -1263,7 +1263,7 @@
         <v>15</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E39" s="0" t="s">
         <v>4</v>
@@ -1283,7 +1283,7 @@
         <v>51</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E40" s="0" t="s">
         <v>128</v>
@@ -1297,10 +1297,10 @@
         <v>130</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E41" s="0" t="s">
         <v>131</v>
@@ -1320,7 +1320,7 @@
         <v>62</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E42" s="0" t="s">
         <v>135</v>
@@ -1374,10 +1374,10 @@
         <v>143</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E45" s="0" t="s">
         <v>68</v>
@@ -1454,7 +1454,7 @@
         <v>51</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E49" s="0" t="s">
         <v>157</v>

--- a/Assets/Resource/MagicFight2/Magic.xlsx
+++ b/Assets/Resource/MagicFight2/Magic.xlsx
@@ -140,7 +140,10 @@
     <t>电弧</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;攻击时可以将手中其它法术进入冷却，每冷却一张获得一次快速回填</t>
+    <t>6</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;光环：使你的进攻法术获得快速回填</t>
   </si>
   <si>
     <t>l</t>
@@ -167,10 +170,7 @@
     <t>引雷</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;光环：使你的基础力量小于等于4的法术获得连击（不能叠加）</t>
+    <t>&lt;sprite=0&gt;光环：使你的基础力量小于等于6的法术获得连击（不能叠加）</t>
   </si>
   <si>
     <t>o</t>
@@ -727,13 +727,13 @@
         <v>41</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F11" s="0" t="s">
         <v>39</v>
@@ -741,10 +741,10 @@
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C12" s="0" t="s">
         <v>2</v>
@@ -753,7 +753,7 @@
         <v>2</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F12" s="0" t="s">
         <v>39</v>
@@ -761,10 +761,10 @@
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C13" s="0" t="s">
         <v>19</v>
@@ -773,7 +773,7 @@
         <v>3</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F13" s="0" t="s">
         <v>39</v>
@@ -781,13 +781,13 @@
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="D14" s="0" t="s">
         <v>2</v>
@@ -807,7 +807,7 @@
         <v>19</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" s="0" t="s">
         <v>55</v>
@@ -824,7 +824,7 @@
         <v>57</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D16" s="0" t="s">
         <v>11</v>
@@ -833,7 +833,7 @@
         <v>55</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -853,7 +853,7 @@
         <v>4</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -881,13 +881,13 @@
         <v>65</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D19" s="0" t="s">
         <v>11</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20">
@@ -995,7 +995,7 @@
         <v>83</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D25" s="0" t="s">
         <v>2</v>
@@ -1086,7 +1086,7 @@
         <v>97</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D30" s="0" t="s">
         <v>2</v>
@@ -1183,7 +1183,7 @@
         <v>112</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D35" s="0" t="s">
         <v>2</v>
@@ -1280,7 +1280,7 @@
         <v>127</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D40" s="0" t="s">
         <v>2</v>
@@ -1451,7 +1451,7 @@
         <v>156</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D49" s="0" t="s">
         <v>2</v>

--- a/Assets/Resource/MagicFight2/Magic.xlsx
+++ b/Assets/Resource/MagicFight2/Magic.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="160">
   <si>
     <t>a</t>
   </si>
@@ -20,33 +20,33 @@
     <t>暴风雪</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;加速</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;区域减速</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>冰风暴</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;光环：使法术附带防御时力量+2</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>凝固</t>
+  </si>
+  <si>
     <t>3</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;加速</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;区域减速</t>
-  </si>
-  <si>
-    <t>b</t>
-  </si>
-  <si>
-    <t>冰风暴</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;光环：使法术附带防御时力量+2</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>凝固</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
@@ -140,132 +140,138 @@
     <t>电弧</t>
   </si>
   <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;光环：使你的进攻法术获得快速回填</t>
+  </si>
+  <si>
+    <t>l</t>
+  </si>
+  <si>
+    <t>磁暴</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;攻击时可以将手中其它法术进入冷却，每冷却一张进攻力量+3</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>雷鸣</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;区域加速</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>引雷</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;光环：使你的基础力量小于等于6的法术获得连击（不能叠加）</t>
+  </si>
+  <si>
+    <t>o</t>
+  </si>
+  <si>
+    <t>过载</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;恢复一点生命值，减少一点生命上限[强制]</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>自燃</t>
+  </si>
+  <si>
+    <t>q</t>
+  </si>
+  <si>
+    <t>海涌</t>
+  </si>
+  <si>
+    <t>r</t>
+  </si>
+  <si>
+    <t>水刃</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;使一张法术立即冷却完成</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>喷泉</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>荆棘</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;双发</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;对方无法防御时，获得 快速回填×2</t>
+  </si>
+  <si>
+    <t>u</t>
+  </si>
+  <si>
+    <t>飞叶连击</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;此法术获得的额外进攻力量翻倍</t>
+  </si>
+  <si>
+    <t>v</t>
+  </si>
+  <si>
+    <t>藤蔓</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;若这是你手中最后两张法术（或更少），进攻力量+1</t>
+  </si>
+  <si>
+    <t>w</t>
+  </si>
+  <si>
+    <t>狂躁蘑菇</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;随机查看对方一张手牌，力量&gt;=7则立即进入冷却且冷却时间减一</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>模仿</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;复制你的冷却区中一个 基础冷却等于3且无光环 的法术的力量和进攻效果</t>
+  </si>
+  <si>
+    <t>&lt;sprite=2&gt;未复制或其他情况下力量视为1</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>瀑流</t>
+  </si>
+  <si>
     <t>6</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;光环：使你的进攻法术获得快速回填</t>
-  </si>
-  <si>
-    <t>l</t>
-  </si>
-  <si>
-    <t>磁暴</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;攻击时可以将手中其它法术进入冷却，每冷却一张进攻力量+3</t>
-  </si>
-  <si>
-    <t>m</t>
-  </si>
-  <si>
-    <t>雷鸣</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;区域加速</t>
-  </si>
-  <si>
-    <t>n</t>
-  </si>
-  <si>
-    <t>引雷</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;光环：使你的基础力量小于等于6的法术获得连击（不能叠加）</t>
-  </si>
-  <si>
-    <t>o</t>
-  </si>
-  <si>
-    <t>过载</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;恢复一点生命值，减少一点生命上限[强制]</t>
-  </si>
-  <si>
-    <t>p</t>
-  </si>
-  <si>
-    <t>自燃</t>
-  </si>
-  <si>
-    <t>q</t>
-  </si>
-  <si>
-    <t>海涌</t>
-  </si>
-  <si>
-    <t>r</t>
-  </si>
-  <si>
-    <t>水刃</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;使一张法术立即冷却完成</t>
-  </si>
-  <si>
-    <t>s</t>
-  </si>
-  <si>
-    <t>喷泉</t>
-  </si>
-  <si>
-    <t>t</t>
-  </si>
-  <si>
-    <t>荆棘</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;双发</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;对方无法防御时，获得 快速回填×2</t>
-  </si>
-  <si>
-    <t>u</t>
-  </si>
-  <si>
-    <t>飞叶连击</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;此法术获得的 额外进攻力量 翻倍</t>
-  </si>
-  <si>
-    <t>v</t>
-  </si>
-  <si>
-    <t>藤蔓</t>
-  </si>
-  <si>
-    <t>w</t>
-  </si>
-  <si>
-    <t>狂躁蘑菇</t>
-  </si>
-  <si>
-    <t>x</t>
-  </si>
-  <si>
-    <t>模仿</t>
-  </si>
-  <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>&lt;sprite=0&gt;复制你的冷却区中一个 基础冷却等于3且无光环 的法术的力量和进攻效果</t>
-  </si>
-  <si>
-    <t>&lt;sprite=2&gt;未复制或其他情况下力量视为1</t>
-  </si>
-  <si>
-    <t>y</t>
-  </si>
-  <si>
-    <t>瀑流</t>
-  </si>
-  <si>
     <t>&lt;sprite=0&gt;你每损失一点生命值（相较初始值），额外加速一个不同的法术</t>
   </si>
   <si>
@@ -398,7 +404,7 @@
     <t>雪崩</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;使自己和对方的 冷却区中剩余冷却为1的法术 都被减速[强制]</t>
+    <t>&lt;sprite=0&gt;可以选择使自己和对方的 冷却区中剩余冷却为1的法术 都被减速</t>
   </si>
   <si>
     <t>01</t>
@@ -545,44 +551,44 @@
         <v>2</v>
       </c>
       <c r="D1" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="F1" s="0" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" s="0" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="C2" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="0" t="s">
         <v>7</v>
-      </c>
-      <c r="C2" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="0" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="0" t="s">
-        <v>10</v>
-      </c>
       <c r="C3" s="0" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D3" s="0" t="s">
         <v>11</v>
@@ -602,7 +608,7 @@
         <v>15</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E4" s="0" t="s">
         <v>16</v>
@@ -619,7 +625,7 @@
         <v>19</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E5" s="0" t="s">
         <v>20</v>
@@ -639,10 +645,10 @@
         <v>24</v>
       </c>
       <c r="D6" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E6" s="0" t="s">
         <v>3</v>
-      </c>
-      <c r="E6" s="0" t="s">
-        <v>4</v>
       </c>
       <c r="F6" s="0" t="s">
         <v>25</v>
@@ -659,7 +665,7 @@
         <v>24</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7" s="0" t="s">
         <v>28</v>
@@ -676,7 +682,7 @@
         <v>15</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E8" s="0" t="s">
         <v>31</v>
@@ -696,7 +702,7 @@
         <v>35</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E9" s="0" t="s">
         <v>36</v>
@@ -713,7 +719,7 @@
         <v>35</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" s="0" t="s">
         <v>39</v>
@@ -730,7 +736,7 @@
         <v>42</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11" s="0" t="s">
         <v>43</v>
@@ -747,10 +753,10 @@
         <v>45</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E12" s="0" t="s">
         <v>46</v>
@@ -770,7 +776,7 @@
         <v>19</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E13" s="0" t="s">
         <v>49</v>
@@ -790,7 +796,7 @@
         <v>11</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E14" s="0" t="s">
         <v>52</v>
@@ -807,7 +813,7 @@
         <v>19</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" s="0" t="s">
         <v>55</v>
@@ -844,13 +850,13 @@
         <v>59</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D17" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E17" s="0" t="s">
         <v>3</v>
-      </c>
-      <c r="E17" s="0" t="s">
-        <v>4</v>
       </c>
       <c r="F17" s="0" t="s">
         <v>49</v>
@@ -864,24 +870,24 @@
         <v>61</v>
       </c>
       <c r="C18" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="0" t="s">
         <v>62</v>
-      </c>
-      <c r="D18" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="E18" s="0" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="B19" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="B19" s="0" t="s">
-        <v>65</v>
-      </c>
       <c r="C19" s="0" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D19" s="0" t="s">
         <v>11</v>
@@ -892,30 +898,30 @@
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="B20" s="0" t="s">
         <v>66</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="C20" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="0" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="D20" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="E20" s="0" t="s">
+      <c r="F20" s="0" t="s">
         <v>68</v>
-      </c>
-      <c r="F20" s="0" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="B21" s="0" t="s">
         <v>70</v>
-      </c>
-      <c r="B21" s="0" t="s">
-        <v>71</v>
       </c>
       <c r="C21" s="0" t="s">
         <v>11</v>
@@ -924,27 +930,30 @@
         <v>11</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F21" s="0" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="B22" s="0" t="s">
         <v>73</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="C22" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="D22" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="F22" s="0" t="s">
         <v>74</v>
-      </c>
-      <c r="C22" s="0" t="s">
-        <v>62</v>
-      </c>
-      <c r="D22" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="E22" s="0" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="23">
@@ -955,70 +964,70 @@
         <v>76</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F23" s="0" t="s">
-        <v>4</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C26" s="0" t="s">
         <v>15</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E26" s="0" t="s">
         <v>28</v>
@@ -1029,204 +1038,204 @@
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D27" s="0" t="s">
         <v>11</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E28" s="0" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D29" s="0" t="s">
         <v>11</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E30" s="0" t="s">
         <v>36</v>
       </c>
       <c r="F30" s="0" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D31" s="0" t="s">
         <v>11</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E32" s="0" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F32" s="0" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C33" s="0" t="s">
         <v>15</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E33" s="0" t="s">
         <v>36</v>
       </c>
       <c r="F33" s="0" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E34" s="0" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F34" s="0" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E35" s="0" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C36" s="0" t="s">
         <v>35</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E36" s="0" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F36" s="0" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E37" s="0" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F37" s="0" t="s">
         <v>25</v>
@@ -1234,19 +1243,19 @@
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C38" s="0" t="s">
         <v>35</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E38" s="0" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F38" s="0" t="s">
         <v>25</v>
@@ -1254,47 +1263,47 @@
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C39" s="0" t="s">
         <v>15</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E39" s="0" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C41" s="0" t="s">
         <v>11</v>
@@ -1303,47 +1312,47 @@
         <v>11</v>
       </c>
       <c r="E41" s="0" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F41" s="0" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E42" s="0" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F42" s="0" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C43" s="0" t="s">
         <v>24</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E43" s="0" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F43" s="0" t="s">
         <v>25</v>
@@ -1351,113 +1360,113 @@
     </row>
     <row r="44">
       <c r="A44" s="0" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C44" s="0" t="s">
         <v>19</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E44" s="0" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E45" s="0" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F45" s="0" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C46" s="0" t="s">
         <v>35</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E46" s="0" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C47" s="0" t="s">
         <v>15</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E47" s="0" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F47" s="0" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E48" s="0" t="s">
         <v>28</v>
       </c>
       <c r="F48" s="0" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E49" s="0" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F49" s="0" t="s">
         <v>28</v>

--- a/Assets/Resource/MagicFight2/Magic.xlsx
+++ b/Assets/Resource/MagicFight2/Magic.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="159">
   <si>
     <t>a</t>
   </si>
@@ -107,7 +107,7 @@
     <t>沉重打击</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;对方无法防御时，将额外减少一点生命值</t>
+    <t>&lt;sprite=0&gt;对方无法防御时，将额外减少一点生命值和生命上限</t>
   </si>
   <si>
     <t>&lt;sprite=0&gt;此法术的进攻力量不能增加</t>
@@ -218,7 +218,7 @@
     <t>&lt;sprite=0&gt;双发</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;对方无法防御时，获得 快速回填×2</t>
+    <t>&lt;sprite=0&gt;对方无法防御时，此法术冷却时间减2</t>
   </si>
   <si>
     <t>u</t>
@@ -236,9 +236,6 @@
     <t>藤蔓</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;若这是你手中最后两张法术（或更少），进攻力量+1</t>
-  </si>
-  <si>
     <t>w</t>
   </si>
   <si>
@@ -377,7 +374,7 @@
     <t>石化</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;光环：免疫力量大于等于7的攻击（包括双发）</t>
+    <t>&lt;sprite=0&gt;光环：免疫力量大于等于6的攻击（包括双发）</t>
   </si>
   <si>
     <t>al</t>
@@ -890,10 +887,13 @@
         <v>10</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E19" s="0" t="s">
         <v>49</v>
+      </c>
+      <c r="F19" s="0" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -952,16 +952,13 @@
       <c r="E22" s="0" t="s">
         <v>67</v>
       </c>
-      <c r="F22" s="0" t="s">
-        <v>74</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" s="0" t="s">
         <v>75</v>
-      </c>
-      <c r="B23" s="0" t="s">
-        <v>76</v>
       </c>
       <c r="C23" s="0" t="s">
         <v>11</v>
@@ -973,38 +970,38 @@
         <v>67</v>
       </c>
       <c r="F23" s="0" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="B24" s="0" t="s">
         <v>78</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="C24" s="0" t="s">
         <v>79</v>
       </c>
-      <c r="C24" s="0" t="s">
+      <c r="D24" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E24" s="0" t="s">
         <v>80</v>
       </c>
-      <c r="D24" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="E24" s="0" t="s">
+      <c r="F24" s="0" t="s">
         <v>81</v>
-      </c>
-      <c r="F24" s="0" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="B25" s="0" t="s">
         <v>83</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="C25" s="0" t="s">
         <v>84</v>
-      </c>
-      <c r="C25" s="0" t="s">
-        <v>85</v>
       </c>
       <c r="D25" s="0" t="s">
         <v>10</v>
@@ -1013,15 +1010,15 @@
         <v>3</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="B26" s="0" t="s">
         <v>87</v>
-      </c>
-      <c r="B26" s="0" t="s">
-        <v>88</v>
       </c>
       <c r="C26" s="0" t="s">
         <v>15</v>
@@ -1038,10 +1035,10 @@
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="B27" s="0" t="s">
         <v>89</v>
-      </c>
-      <c r="B27" s="0" t="s">
-        <v>90</v>
       </c>
       <c r="C27" s="0" t="s">
         <v>2</v>
@@ -1050,15 +1047,15 @@
         <v>11</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="B28" s="0" t="s">
         <v>92</v>
-      </c>
-      <c r="B28" s="0" t="s">
-        <v>93</v>
       </c>
       <c r="C28" s="0" t="s">
         <v>42</v>
@@ -1067,15 +1064,15 @@
         <v>10</v>
       </c>
       <c r="E28" s="0" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="B29" s="0" t="s">
         <v>95</v>
-      </c>
-      <c r="B29" s="0" t="s">
-        <v>96</v>
       </c>
       <c r="C29" s="0" t="s">
         <v>2</v>
@@ -1084,18 +1081,18 @@
         <v>11</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="B30" s="0" t="s">
         <v>98</v>
       </c>
-      <c r="B30" s="0" t="s">
-        <v>99</v>
-      </c>
       <c r="C30" s="0" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D30" s="0" t="s">
         <v>10</v>
@@ -1104,15 +1101,15 @@
         <v>36</v>
       </c>
       <c r="F30" s="0" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="B31" s="0" t="s">
         <v>101</v>
-      </c>
-      <c r="B31" s="0" t="s">
-        <v>102</v>
       </c>
       <c r="C31" s="0" t="s">
         <v>2</v>
@@ -1121,15 +1118,15 @@
         <v>11</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
+        <v>103</v>
+      </c>
+      <c r="B32" s="0" t="s">
         <v>104</v>
-      </c>
-      <c r="B32" s="0" t="s">
-        <v>105</v>
       </c>
       <c r="C32" s="0" t="s">
         <v>42</v>
@@ -1138,18 +1135,18 @@
         <v>10</v>
       </c>
       <c r="E32" s="0" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F32" s="0" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
+        <v>106</v>
+      </c>
+      <c r="B33" s="0" t="s">
         <v>107</v>
-      </c>
-      <c r="B33" s="0" t="s">
-        <v>108</v>
       </c>
       <c r="C33" s="0" t="s">
         <v>15</v>
@@ -1161,15 +1158,15 @@
         <v>36</v>
       </c>
       <c r="F33" s="0" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
+        <v>109</v>
+      </c>
+      <c r="B34" s="0" t="s">
         <v>110</v>
-      </c>
-      <c r="B34" s="0" t="s">
-        <v>111</v>
       </c>
       <c r="C34" s="0" t="s">
         <v>42</v>
@@ -1181,32 +1178,32 @@
         <v>3</v>
       </c>
       <c r="F34" s="0" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="B35" s="0" t="s">
         <v>113</v>
       </c>
-      <c r="B35" s="0" t="s">
+      <c r="C35" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="D35" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="E35" s="0" t="s">
         <v>114</v>
-      </c>
-      <c r="C35" s="0" t="s">
-        <v>85</v>
-      </c>
-      <c r="D35" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="E35" s="0" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
+        <v>115</v>
+      </c>
+      <c r="B36" s="0" t="s">
         <v>116</v>
-      </c>
-      <c r="B36" s="0" t="s">
-        <v>117</v>
       </c>
       <c r="C36" s="0" t="s">
         <v>35</v>
@@ -1215,27 +1212,27 @@
         <v>2</v>
       </c>
       <c r="E36" s="0" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F36" s="0" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
+        <v>118</v>
+      </c>
+      <c r="B37" s="0" t="s">
         <v>119</v>
       </c>
-      <c r="B37" s="0" t="s">
+      <c r="C37" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="D37" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E37" s="0" t="s">
         <v>120</v>
-      </c>
-      <c r="C37" s="0" t="s">
-        <v>85</v>
-      </c>
-      <c r="D37" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="E37" s="0" t="s">
-        <v>121</v>
       </c>
       <c r="F37" s="0" t="s">
         <v>25</v>
@@ -1243,10 +1240,10 @@
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="B38" s="0" t="s">
         <v>122</v>
-      </c>
-      <c r="B38" s="0" t="s">
-        <v>123</v>
       </c>
       <c r="C38" s="0" t="s">
         <v>35</v>
@@ -1255,7 +1252,7 @@
         <v>2</v>
       </c>
       <c r="E38" s="0" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F38" s="0" t="s">
         <v>25</v>
@@ -1263,10 +1260,10 @@
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="B39" s="0" t="s">
         <v>125</v>
-      </c>
-      <c r="B39" s="0" t="s">
-        <v>126</v>
       </c>
       <c r="C39" s="0" t="s">
         <v>15</v>
@@ -1278,32 +1275,32 @@
         <v>3</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
+        <v>127</v>
+      </c>
+      <c r="B40" s="0" t="s">
         <v>128</v>
       </c>
-      <c r="B40" s="0" t="s">
+      <c r="C40" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="D40" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="E40" s="0" t="s">
         <v>129</v>
-      </c>
-      <c r="C40" s="0" t="s">
-        <v>85</v>
-      </c>
-      <c r="D40" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="E40" s="0" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="s">
+        <v>130</v>
+      </c>
+      <c r="B41" s="0" t="s">
         <v>131</v>
-      </c>
-      <c r="B41" s="0" t="s">
-        <v>132</v>
       </c>
       <c r="C41" s="0" t="s">
         <v>11</v>
@@ -1312,18 +1309,18 @@
         <v>11</v>
       </c>
       <c r="E41" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="F41" s="0" t="s">
         <v>133</v>
-      </c>
-      <c r="F41" s="0" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="B42" s="0" t="s">
         <v>135</v>
-      </c>
-      <c r="B42" s="0" t="s">
-        <v>136</v>
       </c>
       <c r="C42" s="0" t="s">
         <v>42</v>
@@ -1332,18 +1329,18 @@
         <v>10</v>
       </c>
       <c r="E42" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="F42" s="0" t="s">
         <v>137</v>
-      </c>
-      <c r="F42" s="0" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="B43" s="0" t="s">
         <v>139</v>
-      </c>
-      <c r="B43" s="0" t="s">
-        <v>140</v>
       </c>
       <c r="C43" s="0" t="s">
         <v>24</v>
@@ -1352,7 +1349,7 @@
         <v>2</v>
       </c>
       <c r="E43" s="0" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F43" s="0" t="s">
         <v>25</v>
@@ -1360,10 +1357,10 @@
     </row>
     <row r="44">
       <c r="A44" s="0" t="s">
+        <v>140</v>
+      </c>
+      <c r="B44" s="0" t="s">
         <v>141</v>
-      </c>
-      <c r="B44" s="0" t="s">
-        <v>142</v>
       </c>
       <c r="C44" s="0" t="s">
         <v>19</v>
@@ -1372,15 +1369,15 @@
         <v>2</v>
       </c>
       <c r="E44" s="0" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="s">
+        <v>143</v>
+      </c>
+      <c r="B45" s="0" t="s">
         <v>144</v>
-      </c>
-      <c r="B45" s="0" t="s">
-        <v>145</v>
       </c>
       <c r="C45" s="0" t="s">
         <v>10</v>
@@ -1392,15 +1389,15 @@
         <v>67</v>
       </c>
       <c r="F45" s="0" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="s">
+        <v>146</v>
+      </c>
+      <c r="B46" s="0" t="s">
         <v>147</v>
-      </c>
-      <c r="B46" s="0" t="s">
-        <v>148</v>
       </c>
       <c r="C46" s="0" t="s">
         <v>35</v>
@@ -1409,15 +1406,15 @@
         <v>2</v>
       </c>
       <c r="E46" s="0" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="s">
+        <v>149</v>
+      </c>
+      <c r="B47" s="0" t="s">
         <v>150</v>
-      </c>
-      <c r="B47" s="0" t="s">
-        <v>151</v>
       </c>
       <c r="C47" s="0" t="s">
         <v>15</v>
@@ -1426,18 +1423,18 @@
         <v>2</v>
       </c>
       <c r="E47" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="F47" s="0" t="s">
         <v>152</v>
-      </c>
-      <c r="F47" s="0" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="s">
+        <v>153</v>
+      </c>
+      <c r="B48" s="0" t="s">
         <v>154</v>
-      </c>
-      <c r="B48" s="0" t="s">
-        <v>155</v>
       </c>
       <c r="C48" s="0" t="s">
         <v>2</v>
@@ -1449,24 +1446,24 @@
         <v>28</v>
       </c>
       <c r="F48" s="0" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="s">
+        <v>156</v>
+      </c>
+      <c r="B49" s="0" t="s">
         <v>157</v>
       </c>
-      <c r="B49" s="0" t="s">
+      <c r="C49" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="D49" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="E49" s="0" t="s">
         <v>158</v>
-      </c>
-      <c r="C49" s="0" t="s">
-        <v>85</v>
-      </c>
-      <c r="D49" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="E49" s="0" t="s">
-        <v>159</v>
       </c>
       <c r="F49" s="0" t="s">
         <v>28</v>

--- a/Assets/Resource/MagicFight2/Magic.xlsx
+++ b/Assets/Resource/MagicFight2/Magic.xlsx
@@ -35,6 +35,9 @@
     <t>冰风暴</t>
   </si>
   <si>
+    <t>5</t>
+  </si>
+  <si>
     <t>&lt;sprite=0&gt;光环：使法术附带防御时力量+2</t>
   </si>
   <si>
@@ -138,9 +141,6 @@
   </si>
   <si>
     <t>电弧</t>
-  </si>
-  <si>
-    <t>5</t>
   </si>
   <si>
     <t>&lt;sprite=0&gt;光环：使你的进攻法术获得快速回填</t>
@@ -565,7 +565,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D2" s="0" t="s">
         <v>2</v>
@@ -574,72 +574,72 @@
         <v>4</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D6" s="0" t="s">
         <v>2</v>
@@ -648,89 +648,89 @@
         <v>3</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D7" s="0" t="s">
         <v>2</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F8" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D10" s="0" t="s">
         <v>2</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="D11" s="0" t="s">
         <v>2</v>
@@ -739,7 +739,7 @@
         <v>43</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12">
@@ -750,16 +750,16 @@
         <v>45</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E12" s="0" t="s">
         <v>46</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
@@ -770,7 +770,7 @@
         <v>48</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D13" s="0" t="s">
         <v>2</v>
@@ -779,7 +779,7 @@
         <v>49</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
@@ -790,10 +790,10 @@
         <v>51</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E14" s="0" t="s">
         <v>52</v>
@@ -807,7 +807,7 @@
         <v>54</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D15" s="0" t="s">
         <v>2</v>
@@ -816,7 +816,7 @@
         <v>55</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16">
@@ -827,10 +827,10 @@
         <v>57</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E16" s="0" t="s">
         <v>55</v>
@@ -847,7 +847,7 @@
         <v>59</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D17" s="0" t="s">
         <v>2</v>
@@ -867,10 +867,10 @@
         <v>61</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E18" s="0" t="s">
         <v>62</v>
@@ -884,16 +884,16 @@
         <v>64</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E19" s="0" t="s">
         <v>49</v>
       </c>
       <c r="F19" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20">
@@ -904,10 +904,10 @@
         <v>66</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E20" s="0" t="s">
         <v>67</v>
@@ -924,10 +924,10 @@
         <v>70</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E21" s="0" t="s">
         <v>67</v>
@@ -944,10 +944,10 @@
         <v>73</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E22" s="0" t="s">
         <v>67</v>
@@ -961,10 +961,10 @@
         <v>75</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E23" s="0" t="s">
         <v>67</v>
@@ -1004,7 +1004,7 @@
         <v>84</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E25" s="0" t="s">
         <v>3</v>
@@ -1021,16 +1021,16 @@
         <v>87</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27">
@@ -1044,7 +1044,7 @@
         <v>2</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E27" s="0" t="s">
         <v>90</v>
@@ -1058,10 +1058,10 @@
         <v>92</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E28" s="0" t="s">
         <v>93</v>
@@ -1078,7 +1078,7 @@
         <v>2</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E29" s="0" t="s">
         <v>96</v>
@@ -1095,10 +1095,10 @@
         <v>84</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F30" s="0" t="s">
         <v>99</v>
@@ -1115,7 +1115,7 @@
         <v>2</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E31" s="0" t="s">
         <v>102</v>
@@ -1129,10 +1129,10 @@
         <v>104</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E32" s="0" t="s">
         <v>105</v>
@@ -1149,13 +1149,13 @@
         <v>107</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E33" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F33" s="0" t="s">
         <v>108</v>
@@ -1169,10 +1169,10 @@
         <v>110</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E34" s="0" t="s">
         <v>3</v>
@@ -1192,7 +1192,7 @@
         <v>84</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E35" s="0" t="s">
         <v>114</v>
@@ -1206,7 +1206,7 @@
         <v>116</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D36" s="0" t="s">
         <v>2</v>
@@ -1235,7 +1235,7 @@
         <v>120</v>
       </c>
       <c r="F37" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="38">
@@ -1246,7 +1246,7 @@
         <v>122</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D38" s="0" t="s">
         <v>2</v>
@@ -1255,7 +1255,7 @@
         <v>123</v>
       </c>
       <c r="F38" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="39">
@@ -1266,10 +1266,10 @@
         <v>125</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E39" s="0" t="s">
         <v>3</v>
@@ -1289,7 +1289,7 @@
         <v>84</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E40" s="0" t="s">
         <v>129</v>
@@ -1303,10 +1303,10 @@
         <v>131</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E41" s="0" t="s">
         <v>132</v>
@@ -1323,10 +1323,10 @@
         <v>135</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E42" s="0" t="s">
         <v>136</v>
@@ -1343,7 +1343,7 @@
         <v>139</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D43" s="0" t="s">
         <v>2</v>
@@ -1352,7 +1352,7 @@
         <v>136</v>
       </c>
       <c r="F43" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="44">
@@ -1363,7 +1363,7 @@
         <v>141</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D44" s="0" t="s">
         <v>2</v>
@@ -1380,10 +1380,10 @@
         <v>144</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E45" s="0" t="s">
         <v>67</v>
@@ -1400,7 +1400,7 @@
         <v>147</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D46" s="0" t="s">
         <v>2</v>
@@ -1417,7 +1417,7 @@
         <v>150</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D47" s="0" t="s">
         <v>2</v>
@@ -1443,7 +1443,7 @@
         <v>2</v>
       </c>
       <c r="E48" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F48" s="0" t="s">
         <v>155</v>
@@ -1460,13 +1460,13 @@
         <v>84</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E49" s="0" t="s">
         <v>158</v>
       </c>
       <c r="F49" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resource/MagicFight2/Magic.xlsx
+++ b/Assets/Resource/MagicFight2/Magic.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="160">
   <si>
     <t>a</t>
   </si>
@@ -143,7 +143,7 @@
     <t>电弧</t>
   </si>
   <si>
-    <t>&lt;sprite=0&gt;光环：使你的进攻法术获得快速回填</t>
+    <t>&lt;sprite=0&gt;攻击时可以将手中一张其它法术进入冷却，获得连击</t>
   </si>
   <si>
     <t>l</t>
@@ -234,6 +234,9 @@
   </si>
   <si>
     <t>藤蔓</t>
+  </si>
+  <si>
+    <t>&lt;sprite=0&gt;对方无法防御时，获得减速</t>
   </si>
   <si>
     <t>w</t>
@@ -730,16 +733,13 @@
         <v>42</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E11" s="0" t="s">
         <v>43</v>
-      </c>
-      <c r="F11" s="0" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="12">
@@ -847,7 +847,7 @@
         <v>59</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D17" s="0" t="s">
         <v>2</v>
@@ -952,13 +952,16 @@
       <c r="E22" s="0" t="s">
         <v>67</v>
       </c>
+      <c r="F22" s="0" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C23" s="0" t="s">
         <v>12</v>
@@ -970,38 +973,38 @@
         <v>67</v>
       </c>
       <c r="F23" s="0" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D24" s="0" t="s">
         <v>2</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D25" s="0" t="s">
         <v>11</v>
@@ -1010,15 +1013,15 @@
         <v>3</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C26" s="0" t="s">
         <v>16</v>
@@ -1035,10 +1038,10 @@
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C27" s="0" t="s">
         <v>2</v>
@@ -1047,15 +1050,15 @@
         <v>12</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C28" s="0" t="s">
         <v>7</v>
@@ -1064,15 +1067,15 @@
         <v>11</v>
       </c>
       <c r="E28" s="0" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C29" s="0" t="s">
         <v>2</v>
@@ -1081,18 +1084,18 @@
         <v>12</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D30" s="0" t="s">
         <v>11</v>
@@ -1101,15 +1104,15 @@
         <v>37</v>
       </c>
       <c r="F30" s="0" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C31" s="0" t="s">
         <v>2</v>
@@ -1118,15 +1121,15 @@
         <v>12</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C32" s="0" t="s">
         <v>7</v>
@@ -1135,18 +1138,18 @@
         <v>11</v>
       </c>
       <c r="E32" s="0" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F32" s="0" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C33" s="0" t="s">
         <v>16</v>
@@ -1158,15 +1161,15 @@
         <v>37</v>
       </c>
       <c r="F33" s="0" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C34" s="0" t="s">
         <v>7</v>
@@ -1178,32 +1181,32 @@
         <v>3</v>
       </c>
       <c r="F34" s="0" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D35" s="0" t="s">
         <v>11</v>
       </c>
       <c r="E35" s="0" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C36" s="0" t="s">
         <v>36</v>
@@ -1212,27 +1215,27 @@
         <v>2</v>
       </c>
       <c r="E36" s="0" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F36" s="0" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D37" s="0" t="s">
         <v>2</v>
       </c>
       <c r="E37" s="0" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F37" s="0" t="s">
         <v>26</v>
@@ -1240,10 +1243,10 @@
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C38" s="0" t="s">
         <v>36</v>
@@ -1252,7 +1255,7 @@
         <v>2</v>
       </c>
       <c r="E38" s="0" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F38" s="0" t="s">
         <v>26</v>
@@ -1260,10 +1263,10 @@
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C39" s="0" t="s">
         <v>16</v>
@@ -1275,32 +1278,32 @@
         <v>3</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D40" s="0" t="s">
         <v>11</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C41" s="0" t="s">
         <v>12</v>
@@ -1309,18 +1312,18 @@
         <v>12</v>
       </c>
       <c r="E41" s="0" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F41" s="0" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C42" s="0" t="s">
         <v>7</v>
@@ -1329,18 +1332,18 @@
         <v>11</v>
       </c>
       <c r="E42" s="0" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F42" s="0" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C43" s="0" t="s">
         <v>25</v>
@@ -1349,7 +1352,7 @@
         <v>2</v>
       </c>
       <c r="E43" s="0" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F43" s="0" t="s">
         <v>26</v>
@@ -1357,10 +1360,10 @@
     </row>
     <row r="44">
       <c r="A44" s="0" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C44" s="0" t="s">
         <v>20</v>
@@ -1369,15 +1372,15 @@
         <v>2</v>
       </c>
       <c r="E44" s="0" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C45" s="0" t="s">
         <v>11</v>
@@ -1389,15 +1392,15 @@
         <v>67</v>
       </c>
       <c r="F45" s="0" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C46" s="0" t="s">
         <v>36</v>
@@ -1406,15 +1409,15 @@
         <v>2</v>
       </c>
       <c r="E46" s="0" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C47" s="0" t="s">
         <v>16</v>
@@ -1423,18 +1426,18 @@
         <v>2</v>
       </c>
       <c r="E47" s="0" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F47" s="0" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C48" s="0" t="s">
         <v>2</v>
@@ -1446,24 +1449,24 @@
         <v>29</v>
       </c>
       <c r="F48" s="0" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D49" s="0" t="s">
         <v>11</v>
       </c>
       <c r="E49" s="0" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F49" s="0" t="s">
         <v>29</v>
